--- a/data/Heat map 3.xlsx
+++ b/data/Heat map 3.xlsx
@@ -1,12 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A601403A-0876-4EFD-9130-8D6563626362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="30195" yWindow="1395" windowWidth="27000" windowHeight="15735" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Res, Cap, Product" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Res, Cap, Product" sheetId="1" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
@@ -15,141 +22,261 @@
     <definedName name="_Hlk200085589" localSheetId="0">'Res, Cap, Product'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Res, Cap, Product'!$B$1:$O$17</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="34">
+  <si>
+    <t>KPI by $</t>
+  </si>
+  <si>
+    <t>Research Outputs</t>
+  </si>
+  <si>
+    <t>Training and Capacity Building</t>
+  </si>
+  <si>
+    <t>Product Development</t>
+  </si>
+  <si>
+    <t>Thomson indexed publications</t>
+  </si>
+  <si>
+    <t>Publications per IRS</t>
+  </si>
+  <si>
+    <t>High impact publications</t>
+  </si>
+  <si>
+    <t>PhD and MsC  students enrolled</t>
+  </si>
+  <si>
+    <t>PhD and MsC  theses completed</t>
+  </si>
+  <si>
+    <t>Stakeholders trained on innovations</t>
+  </si>
+  <si>
+    <t>Training to NARES by IITA Scientists</t>
+  </si>
+  <si>
+    <t>Varieties released</t>
+  </si>
+  <si>
+    <t>Genetic gain rate</t>
+  </si>
+  <si>
+    <t>Crop Trust compliance rate</t>
+  </si>
+  <si>
+    <t>Innovations in e-Catalogue</t>
+  </si>
+  <si>
+    <t>Innovations taken on by scaling partners</t>
+  </si>
+  <si>
+    <t>GI</t>
+  </si>
+  <si>
+    <t>Biotech</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Breeding</t>
+  </si>
+  <si>
+    <t>Genebanks</t>
+  </si>
+  <si>
+    <t>Seed System</t>
+  </si>
+  <si>
+    <t>RAFS</t>
+  </si>
+  <si>
+    <t>Plant Health</t>
+  </si>
+  <si>
+    <t>Farming Systems Agronomy</t>
+  </si>
+  <si>
+    <t>NRM</t>
+  </si>
+  <si>
+    <t>Mechanization</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>FIAS</t>
+  </si>
+  <si>
+    <t>GeYSI</t>
+  </si>
+  <si>
+    <t>RCA</t>
+  </si>
+  <si>
+    <t>Nutrition</t>
+  </si>
+  <si>
+    <t>VCMA</t>
+  </si>
+  <si>
+    <t>per Program Target (target/13)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="9"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF0070C0"/>
-      <sz val="18"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="14"/>
     </font>
     <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF00B0F0"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF00B0F0"/>
-      <sz val="14"/>
     </font>
     <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF0070C0"/>
-      <sz val="14"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF0070C0"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF0070C0"/>
-      <sz val="9"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF0070C0"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FFFF0000"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.09997863704336681"/>
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -459,249 +586,158 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook r:id="rId1">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="PR 1"/>
       <sheetName val="PR 2"/>
@@ -722,6 +758,8 @@
       <sheetName val="PR 18"/>
       <sheetName val="PR 19"/>
       <sheetName val="PR20"/>
+      <sheetName val="Chart1"/>
+      <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -731,9 +769,18 @@
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
+      <sheetData sheetId="7">
+        <row r="4">
+          <cell r="G4">
+            <v>0.65217391304347827</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="8">
         <row r="4">
+          <cell r="G4">
+            <v>6.521739130434782E-4</v>
+          </cell>
           <cell r="H4">
             <v>1.1792063636465733E-3</v>
           </cell>
@@ -741,6 +788,9 @@
       </sheetData>
       <sheetData sheetId="9">
         <row r="5">
+          <cell r="G5">
+            <v>0.25</v>
+          </cell>
           <cell r="H5">
             <v>0.28541663693576702</v>
           </cell>
@@ -755,6 +805,14 @@
       <sheetData sheetId="16"/>
       <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20">
+        <row r="12">
+          <cell r="I12">
+            <v>1.4999999999999999E-2</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1076,897 +1134,757 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="B1:V22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="3.21875" customWidth="1" style="2" min="2" max="2"/>
-    <col width="24.77734375" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
-    <col width="6.77734375" customWidth="1" style="2" min="4" max="8"/>
-    <col width="11.44140625" bestFit="1" customWidth="1" style="2" min="9" max="9"/>
-    <col width="6.77734375" customWidth="1" style="2" min="10" max="11"/>
-    <col width="7.21875" bestFit="1" customWidth="1" style="2" min="12" max="12"/>
-    <col width="6.77734375" customWidth="1" style="2" min="13" max="15"/>
-    <col width="8.21875" customWidth="1" style="2" min="16" max="16"/>
-    <col width="6.21875" customWidth="1" style="2" min="17" max="17"/>
-    <col width="8.21875" customWidth="1" style="2" min="18" max="22"/>
+    <col min="2" max="2" width="3.21875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="24.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="6.77734375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="6.77734375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="7.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="6.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="8.21875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="6.21875" style="2" customWidth="1"/>
+    <col min="18" max="22" width="8.21875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" thickBot="1">
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="48" t="inlineStr">
-        <is>
-          <t>KPI by $</t>
-        </is>
-      </c>
-      <c r="D1" s="42" t="n"/>
-      <c r="E1" s="42" t="n"/>
-      <c r="F1" s="42" t="n"/>
-      <c r="G1" s="42" t="n"/>
-      <c r="H1" s="42" t="n"/>
-      <c r="I1" s="42" t="n"/>
-      <c r="J1" s="42" t="n"/>
-      <c r="K1" s="42" t="n"/>
-      <c r="L1" s="42" t="n"/>
-      <c r="M1" s="42" t="n"/>
-      <c r="N1" s="42" t="n"/>
-      <c r="O1" s="43" t="n"/>
-      <c r="P1" s="1" t="n"/>
-      <c r="Q1" s="1" t="n"/>
+    <row r="1" spans="2:22" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B1" s="1"/>
+      <c r="C1" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
     </row>
-    <row r="2" ht="18.6" customFormat="1" customHeight="1" s="6" thickBot="1">
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="41" t="inlineStr">
-        <is>
-          <t>Research Outputs</t>
-        </is>
-      </c>
-      <c r="E2" s="42" t="n"/>
-      <c r="F2" s="43" t="n"/>
-      <c r="G2" s="47" t="inlineStr">
-        <is>
-          <t>Training and Capacity Building</t>
-        </is>
-      </c>
-      <c r="H2" s="42" t="n"/>
-      <c r="I2" s="42" t="n"/>
-      <c r="J2" s="43" t="n"/>
-      <c r="K2" s="47" t="inlineStr">
-        <is>
-          <t>Product Development</t>
-        </is>
-      </c>
-      <c r="L2" s="42" t="n"/>
-      <c r="M2" s="42" t="n"/>
-      <c r="N2" s="42" t="n"/>
-      <c r="O2" s="43" t="n"/>
-      <c r="P2" s="3" t="n"/>
-      <c r="Q2" s="3" t="n"/>
-      <c r="R2" s="5" t="n"/>
-      <c r="S2" s="5" t="n"/>
-      <c r="T2" s="5" t="n"/>
-      <c r="U2" s="5" t="n"/>
-      <c r="V2" s="5" t="n"/>
+    <row r="2" spans="2:22" s="6" customFormat="1" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="45"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
     </row>
-    <row r="3" ht="143.55" customFormat="1" customHeight="1" s="14" thickBot="1">
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>Thomson indexed publications</t>
-        </is>
-      </c>
-      <c r="E3" s="10" t="inlineStr">
-        <is>
-          <t>Publications per IRS</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>High impact publications</t>
-        </is>
-      </c>
-      <c r="G3" s="9" t="inlineStr">
-        <is>
-          <t>PhD and MsC  students enrolled</t>
-        </is>
-      </c>
-      <c r="H3" s="10" t="inlineStr">
-        <is>
-          <t>PhD and MsC  theses completed</t>
-        </is>
-      </c>
-      <c r="I3" s="10" t="inlineStr">
-        <is>
-          <t>Stakeholders trained on innovations</t>
-        </is>
-      </c>
-      <c r="J3" s="11" t="inlineStr">
-        <is>
-          <t>Training to NARES by IITA Scientists</t>
-        </is>
-      </c>
-      <c r="K3" s="9" t="inlineStr">
-        <is>
-          <t>Varieties released</t>
-        </is>
-      </c>
-      <c r="L3" s="12" t="inlineStr">
-        <is>
-          <t>Genetic gain rate</t>
-        </is>
-      </c>
-      <c r="M3" s="12" t="inlineStr">
-        <is>
-          <t>Crop Trust compliance rate</t>
-        </is>
-      </c>
-      <c r="N3" s="10" t="inlineStr">
-        <is>
-          <t>Innovations in e-Catalogue</t>
-        </is>
-      </c>
-      <c r="O3" s="11" t="inlineStr">
-        <is>
-          <t>Innovations taken on by scaling partners</t>
-        </is>
-      </c>
-      <c r="P3" s="7" t="n"/>
-      <c r="Q3" s="7" t="n"/>
-      <c r="R3" s="13" t="n"/>
-      <c r="S3" s="13" t="n"/>
-      <c r="T3" s="13" t="n"/>
-      <c r="U3" s="13" t="n"/>
-      <c r="V3" s="13" t="n"/>
+    <row r="3" spans="2:22" s="14" customFormat="1" ht="143.55000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="7"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="M3" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
+      <c r="V3" s="13"/>
     </row>
-    <row r="4" ht="15.45" customHeight="1">
-      <c r="B4" s="44" t="inlineStr">
-        <is>
-          <t>GI</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>Biotech</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="n">
-        <v>6.444811302633521</v>
-      </c>
-      <c r="E4" s="17" t="n">
+    <row r="4" spans="2:22" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="16">
+        <v>6.4448113026335214</v>
+      </c>
+      <c r="E4" s="17">
         <v>0.9185948577454921</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="F4" s="18">
         <v>0.2929459683015237</v>
       </c>
-      <c r="G4" s="16" t="n">
+      <c r="G4" s="16">
         <v>0.2929459683015237</v>
       </c>
-      <c r="H4" s="19" t="n">
+      <c r="H4" s="19">
         <v>0.2929459683015237</v>
       </c>
-      <c r="I4" s="19" t="n">
-        <v>1.992032584450361e-05</v>
-      </c>
-      <c r="J4" s="20" t="n">
-        <v>53.90205816748036</v>
-      </c>
-      <c r="K4" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L4" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M4" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N4" s="19" t="n">
+      <c r="I4" s="19">
+        <v>1.992032584450361E-5</v>
+      </c>
+      <c r="J4" s="20">
+        <v>53.902058167480362</v>
+      </c>
+      <c r="K4" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="N4" s="19">
         <v>0.2929459683015237</v>
       </c>
-      <c r="O4" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="1" t="n"/>
+      <c r="O4" s="20">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1"/>
     </row>
-    <row r="5" ht="15.6" customHeight="1">
-      <c r="B5" s="45" t="n"/>
-      <c r="C5" s="21" t="inlineStr">
-        <is>
-          <t>Breeding</t>
-        </is>
-      </c>
-      <c r="D5" s="22" t="n">
-        <v>4.048608515186568</v>
-      </c>
-      <c r="E5" s="23" t="n">
-        <v>0.1758555577090324</v>
-      </c>
-      <c r="F5" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="22" t="n">
+    <row r="5" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="42"/>
+      <c r="C5" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="22">
+        <v>4.0486085151865678</v>
+      </c>
+      <c r="E5" s="23">
+        <v>0.17585555770903241</v>
+      </c>
+      <c r="F5" s="24">
+        <v>0</v>
+      </c>
+      <c r="G5" s="22">
         <v>1.886730181834517</v>
       </c>
-      <c r="H5" s="25" t="n">
+      <c r="H5" s="25">
         <v>2.20118521214027</v>
       </c>
-      <c r="I5" s="25" t="n">
-        <v>8.490285818255328</v>
-      </c>
-      <c r="J5" s="26" t="n">
-        <v>16.82334412135778</v>
-      </c>
-      <c r="K5" s="22" t="n">
+      <c r="I5" s="25">
+        <v>8.4902858182553285</v>
+      </c>
+      <c r="J5" s="26">
+        <v>16.823344121357781</v>
+      </c>
+      <c r="K5" s="22">
         <v>1.18</v>
       </c>
       <c r="L5" s="25">
         <f>'[1]PR 9'!$H$4</f>
-        <v/>
-      </c>
-      <c r="M5" s="25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" s="25" t="n">
-        <v>0.6289100606115057</v>
-      </c>
-      <c r="O5" s="26" t="n">
-        <v>0.3930687878821911</v>
-      </c>
-      <c r="P5" s="1" t="n"/>
+        <v>1.1792063636465733E-3</v>
+      </c>
+      <c r="M5" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="25">
+        <v>0.62891006061150567</v>
+      </c>
+      <c r="O5" s="26">
+        <v>0.39306878788219107</v>
+      </c>
+      <c r="P5" s="1"/>
     </row>
-    <row r="6" ht="15.6" customHeight="1">
-      <c r="B6" s="45" t="n"/>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>Genebanks</t>
-        </is>
-      </c>
-      <c r="D6" s="22" t="n">
+    <row r="6" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="42"/>
+      <c r="C6" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="22">
         <v>1.427083184678835</v>
       </c>
-      <c r="E6" s="23" t="n">
-        <v>0.3567707961697087</v>
-      </c>
-      <c r="F6" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="22" t="n">
-        <v>7.420832560329942</v>
-      </c>
-      <c r="H6" s="25" t="n">
-        <v>5.422916101779573</v>
-      </c>
-      <c r="I6" s="25" t="n">
+      <c r="E6" s="23">
+        <v>0.35677079616970869</v>
+      </c>
+      <c r="F6" s="24">
+        <v>0</v>
+      </c>
+      <c r="G6" s="22">
+        <v>7.4208325603299423</v>
+      </c>
+      <c r="H6" s="25">
+        <v>5.4229161017795731</v>
+      </c>
+      <c r="I6" s="25">
         <v>1.427083184678835</v>
       </c>
-      <c r="J6" s="26" t="n">
-        <v>32.25207997374167</v>
-      </c>
-      <c r="K6" s="22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="J6" s="26">
+        <v>32.252079973741672</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" s="25" t="s">
+        <v>18</v>
       </c>
       <c r="M6" s="25">
         <f>'[1]PR 10'!$H$5</f>
-        <v/>
-      </c>
-      <c r="N6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="1" t="n"/>
+        <v>0.28541663693576702</v>
+      </c>
+      <c r="N6" s="25">
+        <v>0</v>
+      </c>
+      <c r="O6" s="26">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1"/>
     </row>
-    <row r="7" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B7" s="46" t="n"/>
-      <c r="C7" s="27" t="inlineStr">
-        <is>
-          <t>Seed System</t>
-        </is>
-      </c>
-      <c r="D7" s="28" t="n">
-        <v>0.7228379951589352</v>
-      </c>
-      <c r="E7" s="29" t="n">
-        <v>0.04818919967726234</v>
-      </c>
-      <c r="F7" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="28" t="n">
-        <v>0.234687660765888</v>
-      </c>
-      <c r="H7" s="31" t="n">
-        <v>0.3285627250722432</v>
-      </c>
-      <c r="I7" s="31" t="n">
+    <row r="7" spans="2:22" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="43"/>
+      <c r="C7" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="28">
+        <v>0.72283799515893521</v>
+      </c>
+      <c r="E7" s="29">
+        <v>4.8189199677262338E-2</v>
+      </c>
+      <c r="F7" s="30">
+        <v>0</v>
+      </c>
+      <c r="G7" s="28">
+        <v>0.23468766076588801</v>
+      </c>
+      <c r="H7" s="31">
+        <v>0.32856272507224321</v>
+      </c>
+      <c r="I7" s="31">
         <v>105.4686347481901</v>
       </c>
-      <c r="J7" s="32" t="n">
+      <c r="J7" s="32">
         <v>14.50369743533188</v>
       </c>
-      <c r="K7" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L7" s="31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M7" s="31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N7" s="31" t="n">
-        <v>0.7979380466040193</v>
-      </c>
-      <c r="O7" s="32" t="n">
-        <v>0.09387506430635521</v>
-      </c>
-      <c r="P7" s="1" t="n"/>
+      <c r="K7" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="M7" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" s="31">
+        <v>0.79793804660401935</v>
+      </c>
+      <c r="O7" s="32">
+        <v>9.3875064306355213E-2</v>
+      </c>
+      <c r="P7" s="1"/>
     </row>
-    <row r="8" ht="15.6" customHeight="1">
-      <c r="B8" s="44" t="inlineStr">
-        <is>
-          <t>RAFS</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Plant Health</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="n">
-        <v>5.36837246579725</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>0.4473643721497708</v>
-      </c>
-      <c r="F8" s="18" t="n">
+    <row r="8" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="16">
+        <v>5.3683724657972496</v>
+      </c>
+      <c r="E8" s="17">
+        <v>0.44736437214977082</v>
+      </c>
+      <c r="F8" s="18">
         <v>0.1295144141326236</v>
       </c>
-      <c r="G8" s="16" t="n">
-        <v>1.165629727193613</v>
-      </c>
-      <c r="H8" s="19" t="n">
-        <v>1.165629727193613</v>
-      </c>
-      <c r="I8" s="19" t="n">
-        <v>13.21047024152761</v>
-      </c>
-      <c r="J8" s="20" t="n">
-        <v>1.295144141326236</v>
-      </c>
-      <c r="K8" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="19" t="n">
-        <v>0.7770864847957417</v>
-      </c>
-      <c r="O8" s="20" t="n">
-        <v>0.2590288282652473</v>
-      </c>
-      <c r="P8" s="1" t="n"/>
+      <c r="G8" s="16">
+        <v>1.1656297271936129</v>
+      </c>
+      <c r="H8" s="19">
+        <v>1.1656297271936129</v>
+      </c>
+      <c r="I8" s="19">
+        <v>13.210470241527609</v>
+      </c>
+      <c r="J8" s="20">
+        <v>1.2951441413262359</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="N8" s="19">
+        <v>0.77708648479574172</v>
+      </c>
+      <c r="O8" s="20">
+        <v>0.25902882826524731</v>
+      </c>
+      <c r="P8" s="1"/>
     </row>
-    <row r="9" ht="15.6" customHeight="1">
-      <c r="B9" s="45" t="n"/>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>Farming Systems Agronomy</t>
-        </is>
-      </c>
-      <c r="D9" s="22" t="n">
+    <row r="9" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="42"/>
+      <c r="C9" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="22">
         <v>1.700457326303648</v>
       </c>
-      <c r="E9" s="23" t="n">
-        <v>0.08502286631518242</v>
-      </c>
-      <c r="F9" s="24" t="n">
-        <v>0.06762719601495103</v>
-      </c>
-      <c r="G9" s="22" t="n">
+      <c r="E9" s="23">
+        <v>8.5022866315182424E-2</v>
+      </c>
+      <c r="F9" s="24">
+        <v>6.7627196014951027E-2</v>
+      </c>
+      <c r="G9" s="22">
         <v>1.79252808714328</v>
       </c>
-      <c r="H9" s="25" t="n">
-        <v>1.140699691818451</v>
-      </c>
-      <c r="I9" s="25" t="n">
-        <v>259.5091798886976</v>
-      </c>
-      <c r="J9" s="26" t="n">
-        <v>18.98450201383565</v>
-      </c>
-      <c r="K9" s="22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" s="25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M9" s="25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" s="25" t="n">
-        <v>0.08147854941560366</v>
-      </c>
-      <c r="O9" s="26" t="n">
+      <c r="H9" s="25">
+        <v>1.1406996918184511</v>
+      </c>
+      <c r="I9" s="25">
+        <v>259.50917988869759</v>
+      </c>
+      <c r="J9" s="26">
+        <v>18.984502013835652</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" s="25">
+        <v>8.147854941560366E-2</v>
+      </c>
+      <c r="O9" s="26">
         <v>0.7333069447404329</v>
       </c>
-      <c r="P9" s="1" t="n"/>
+      <c r="P9" s="1"/>
     </row>
-    <row r="10" ht="15.6" customHeight="1">
-      <c r="B10" s="45" t="n"/>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>NRM</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="n">
-        <v>2.158177644184841</v>
-      </c>
-      <c r="E10" s="23" t="n">
-        <v>0.3083110920264058</v>
-      </c>
-      <c r="F10" s="24" t="n">
-        <v>0.2784745347335278</v>
-      </c>
-      <c r="G10" s="22" t="n">
-        <v>0.9746608715673475</v>
-      </c>
-      <c r="H10" s="25" t="n">
+    <row r="10" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="42"/>
+      <c r="C10" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="22">
+        <v>2.1581776441848408</v>
+      </c>
+      <c r="E10" s="23">
+        <v>0.30831109202640578</v>
+      </c>
+      <c r="F10" s="24">
+        <v>0.27847453473352779</v>
+      </c>
+      <c r="G10" s="22">
+        <v>0.97466087156734749</v>
+      </c>
+      <c r="H10" s="25">
         <v>0.4177118021002918</v>
       </c>
-      <c r="I10" s="25" t="n">
-        <v>522.6967016948319</v>
-      </c>
-      <c r="J10" s="26" t="n">
-        <v>2.784745347335279</v>
-      </c>
-      <c r="K10" s="22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L10" s="25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M10" s="25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N10" s="25" t="n">
-        <v>1.392372673667639</v>
-      </c>
-      <c r="O10" s="26" t="n">
-        <v>0.2784745347335278</v>
-      </c>
-      <c r="P10" s="1" t="n"/>
+      <c r="I10" s="25">
+        <v>522.69670169483186</v>
+      </c>
+      <c r="J10" s="26">
+        <v>2.7847453473352788</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="M10" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" s="25">
+        <v>1.3923726736676389</v>
+      </c>
+      <c r="O10" s="26">
+        <v>0.27847453473352779</v>
+      </c>
+      <c r="P10" s="1"/>
     </row>
-    <row r="11" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B11" s="46" t="n"/>
-      <c r="C11" s="27" t="inlineStr">
-        <is>
-          <t>Mechanization</t>
-        </is>
-      </c>
-      <c r="D11" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="28" t="n">
+    <row r="11" spans="2:22" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="43"/>
+      <c r="C11" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="28">
+        <v>0</v>
+      </c>
+      <c r="E11" s="29">
+        <v>0</v>
+      </c>
+      <c r="F11" s="30">
+        <v>0</v>
+      </c>
+      <c r="G11" s="28">
         <v>3.502154700679593</v>
       </c>
-      <c r="H11" s="31" t="n">
-        <v>1.751077350339797</v>
-      </c>
-      <c r="I11" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L11" s="31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M11" s="31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N11" s="31" t="n">
-        <v>5.253232051019389</v>
-      </c>
-      <c r="O11" s="32" t="n">
-        <v>5.253232051019389</v>
-      </c>
-      <c r="P11" s="1" t="n"/>
+      <c r="H11" s="31">
+        <v>1.7510773503397969</v>
+      </c>
+      <c r="I11" s="31">
+        <v>0</v>
+      </c>
+      <c r="J11" s="32">
+        <v>0</v>
+      </c>
+      <c r="K11" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="M11" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="N11" s="31">
+        <v>5.2532320510193893</v>
+      </c>
+      <c r="O11" s="32">
+        <v>5.2532320510193893</v>
+      </c>
+      <c r="P11" s="1"/>
     </row>
-    <row r="12" ht="15.6" customHeight="1">
-      <c r="B12" s="44" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>FIAS</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="n">
+    <row r="12" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="16">
         <v>7.267541157488532</v>
       </c>
-      <c r="E12" s="17" t="n">
-        <v>0.6606855597716847</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="16" t="n">
-        <v>3.663075180185752</v>
-      </c>
-      <c r="H12" s="19" t="n">
-        <v>3.663075180185752</v>
-      </c>
-      <c r="I12" s="19" t="n">
-        <v>68.86581338749214</v>
-      </c>
-      <c r="J12" s="20" t="n">
-        <v>79.8550389280494</v>
-      </c>
-      <c r="K12" s="33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L12" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M12" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N12" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="1" t="n"/>
+      <c r="E12" s="17">
+        <v>0.66068555977168475</v>
+      </c>
+      <c r="F12" s="18">
+        <v>0</v>
+      </c>
+      <c r="G12" s="16">
+        <v>3.6630751801857522</v>
+      </c>
+      <c r="H12" s="19">
+        <v>3.6630751801857522</v>
+      </c>
+      <c r="I12" s="19">
+        <v>68.865813387492139</v>
+      </c>
+      <c r="J12" s="20">
+        <v>79.855038928049396</v>
+      </c>
+      <c r="K12" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="M12" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="N12" s="19">
+        <v>0</v>
+      </c>
+      <c r="O12" s="20">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1"/>
     </row>
-    <row r="13" ht="15.6" customHeight="1">
-      <c r="B13" s="45" t="n"/>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>GeYSI</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="n">
+    <row r="13" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="42"/>
+      <c r="C13" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="22">
         <v>0.8757548637715421</v>
       </c>
-      <c r="E13" s="23" t="n">
-        <v>0.07961407852468565</v>
-      </c>
-      <c r="F13" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="22" t="n">
-        <v>0.5307605234979043</v>
-      </c>
-      <c r="H13" s="25" t="n">
-        <v>0.3980703926234282</v>
-      </c>
-      <c r="I13" s="25" t="n">
-        <v>253.7035302319983</v>
-      </c>
-      <c r="J13" s="26" t="n">
-        <v>20.69966041641827</v>
-      </c>
-      <c r="K13" s="22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L13" s="25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M13" s="25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N13" s="25" t="n">
-        <v>0.3317253271861902</v>
-      </c>
-      <c r="O13" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="1" t="n"/>
+      <c r="E13" s="23">
+        <v>7.9614078524685647E-2</v>
+      </c>
+      <c r="F13" s="24">
+        <v>0</v>
+      </c>
+      <c r="G13" s="22">
+        <v>0.53076052349790426</v>
+      </c>
+      <c r="H13" s="25">
+        <v>0.39807039262342819</v>
+      </c>
+      <c r="I13" s="25">
+        <v>253.70353023199829</v>
+      </c>
+      <c r="J13" s="26">
+        <v>20.699660416418268</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="L13" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="M13" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="N13" s="25">
+        <v>0.33172532718619019</v>
+      </c>
+      <c r="O13" s="26">
+        <v>0</v>
+      </c>
+      <c r="P13" s="1"/>
     </row>
-    <row r="14" ht="15.6" customHeight="1">
-      <c r="B14" s="45" t="n"/>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>RCA</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="n">
-        <v>6.271447834068688</v>
-      </c>
-      <c r="E14" s="23" t="n">
+    <row r="14" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="42"/>
+      <c r="C14" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="22">
+        <v>6.2714478340686881</v>
+      </c>
+      <c r="E14" s="23">
         <v>1.254289566813737</v>
       </c>
-      <c r="F14" s="24" t="n">
-        <v>0.4704762066068032</v>
-      </c>
-      <c r="G14" s="22" t="n">
-        <v>0.4704762066068032</v>
-      </c>
-      <c r="H14" s="25" t="n">
-        <v>0.9409524132136065</v>
-      </c>
-      <c r="I14" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L14" s="25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M14" s="25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N14" s="25" t="n">
-        <v>1.176190516517008</v>
-      </c>
-      <c r="O14" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="1" t="n"/>
+      <c r="F14" s="24">
+        <v>0.47047620660680323</v>
+      </c>
+      <c r="G14" s="22">
+        <v>0.47047620660680323</v>
+      </c>
+      <c r="H14" s="25">
+        <v>0.94095241321360645</v>
+      </c>
+      <c r="I14" s="25">
+        <v>0</v>
+      </c>
+      <c r="J14" s="26">
+        <v>0</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="L14" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="M14" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="N14" s="25">
+        <v>1.1761905165170079</v>
+      </c>
+      <c r="O14" s="26">
+        <v>0</v>
+      </c>
+      <c r="P14" s="1"/>
     </row>
-    <row r="15" ht="15.6" customHeight="1">
-      <c r="B15" s="45" t="n"/>
-      <c r="C15" s="21" t="inlineStr">
-        <is>
-          <t>Nutrition</t>
-        </is>
-      </c>
-      <c r="D15" s="22" t="n">
-        <v>8.579514140878752</v>
-      </c>
-      <c r="E15" s="23" t="n">
+    <row r="15" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="42"/>
+      <c r="C15" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="22">
+        <v>8.5795141408787519</v>
+      </c>
+      <c r="E15" s="23">
         <v>2.144878535219688</v>
       </c>
-      <c r="F15" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="22" t="n">
-        <v>1.3727222625406</v>
-      </c>
-      <c r="H15" s="25" t="n">
-        <v>5.490889050162401</v>
-      </c>
-      <c r="I15" s="25" t="n">
-        <v>89.22694706513903</v>
-      </c>
-      <c r="J15" s="26" t="n">
+      <c r="F15" s="24">
+        <v>0</v>
+      </c>
+      <c r="G15" s="22">
+        <v>1.3727222625405999</v>
+      </c>
+      <c r="H15" s="25">
+        <v>5.4908890501624006</v>
+      </c>
+      <c r="I15" s="25">
+        <v>89.226947065139029</v>
+      </c>
+      <c r="J15" s="26">
         <v>10.2954169690545</v>
       </c>
-      <c r="K15" s="22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L15" s="25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M15" s="25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N15" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="1" t="n"/>
+      <c r="K15" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="L15" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="M15" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="N15" s="25">
+        <v>0</v>
+      </c>
+      <c r="O15" s="26">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1"/>
     </row>
-    <row r="16" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B16" s="46" t="n"/>
-      <c r="C16" s="27" t="inlineStr">
-        <is>
-          <t>VCMA</t>
-        </is>
-      </c>
-      <c r="D16" s="28" t="n">
-        <v>0.5172799951538452</v>
-      </c>
-      <c r="E16" s="29" t="n">
-        <v>0.05172799951538452</v>
-      </c>
-      <c r="F16" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="28" t="n">
-        <v>0.8621333252564086</v>
-      </c>
-      <c r="H16" s="31" t="n">
-        <v>0.5172799951538452</v>
-      </c>
-      <c r="I16" s="31" t="n">
-        <v>173.6336517066407</v>
-      </c>
-      <c r="J16" s="32" t="n">
-        <v>13.96655986915382</v>
-      </c>
-      <c r="K16" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L16" s="31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M16" s="31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N16" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="1" t="n"/>
+    <row r="16" spans="2:22" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="43"/>
+      <c r="C16" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="28">
+        <v>0.51727999515384515</v>
+      </c>
+      <c r="E16" s="29">
+        <v>5.1727999515384523E-2</v>
+      </c>
+      <c r="F16" s="30">
+        <v>0</v>
+      </c>
+      <c r="G16" s="28">
+        <v>0.86213332525640862</v>
+      </c>
+      <c r="H16" s="31">
+        <v>0.51727999515384515</v>
+      </c>
+      <c r="I16" s="31">
+        <v>173.63365170664071</v>
+      </c>
+      <c r="J16" s="32">
+        <v>13.966559869153819</v>
+      </c>
+      <c r="K16" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="L16" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="M16" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="N16" s="31">
+        <v>0</v>
+      </c>
+      <c r="O16" s="32">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1"/>
     </row>
-    <row r="17" customFormat="1" s="35">
-      <c r="B17" s="34" t="n"/>
-      <c r="C17" s="36" t="inlineStr">
-        <is>
-          <t>per Program Target (target/13)</t>
-        </is>
-      </c>
-      <c r="D17" s="49" t="n">
-        <v>3.127395810403509</v>
-      </c>
-      <c r="E17" s="49" t="n">
-        <v>0.02299555742943757</v>
-      </c>
-      <c r="F17" s="49" t="n">
-        <v>0.1494711232913442</v>
-      </c>
-      <c r="G17" s="49" t="n">
+    <row r="17" spans="2:22" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="34"/>
+      <c r="C17" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="37">
+        <v>3.1273958104035091</v>
+      </c>
+      <c r="E17" s="37">
+        <v>2.2995557429437569E-2</v>
+      </c>
+      <c r="F17" s="37">
+        <v>0.14947112329134421</v>
+      </c>
+      <c r="G17" s="37">
         <v>1.724666807207818</v>
       </c>
-      <c r="H17" s="49" t="n">
+      <c r="H17" s="37">
         <v>0.689866722883127</v>
       </c>
-      <c r="I17" s="49" t="n">
-        <v>137.9733445766254</v>
-      </c>
-      <c r="J17" s="49" t="n">
+      <c r="I17" s="37">
+        <v>137.97334457662541</v>
+      </c>
+      <c r="J17" s="37">
         <v>1.724666807207818</v>
       </c>
-      <c r="K17" s="49" t="n">
-        <v>0.06898667228831269</v>
-      </c>
-      <c r="L17" s="49" t="n">
-        <v>0.0001724666807207817</v>
-      </c>
-      <c r="M17" s="49" t="n">
-        <v>0.01149777871471878</v>
-      </c>
-      <c r="N17" s="49" t="n">
-        <v>0.2299555742943757</v>
-      </c>
-      <c r="O17" s="49" t="n">
+      <c r="K17" s="37">
+        <v>6.8986672288312692E-2</v>
+      </c>
+      <c r="L17" s="37">
+        <v>1.7246668072078169E-4</v>
+      </c>
+      <c r="M17" s="37">
+        <v>1.1497778714718781E-2</v>
+      </c>
+      <c r="N17" s="37">
+        <v>0.22995557429437569</v>
+      </c>
+      <c r="O17" s="37">
         <v>0.3449333614415635</v>
       </c>
-      <c r="P17" s="34" t="n"/>
-      <c r="Q17" s="34" t="n"/>
-      <c r="R17" s="34" t="n"/>
-      <c r="S17" s="34" t="n"/>
-      <c r="T17" s="34" t="n"/>
-      <c r="U17" s="34" t="n"/>
-      <c r="V17" s="34" t="n"/>
+      <c r="P17" s="34"/>
+      <c r="Q17" s="34"/>
+      <c r="R17" s="34"/>
+      <c r="S17" s="34"/>
+      <c r="T17" s="34"/>
+      <c r="U17" s="34"/>
+      <c r="V17" s="34"/>
     </row>
-    <row r="18"/>
-    <row r="19" hidden="1">
-      <c r="C19" s="38" t="n"/>
+    <row r="19" spans="2:22" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C19" s="38"/>
     </row>
-    <row r="20" hidden="1">
-      <c r="C20" s="39" t="n"/>
+    <row r="20" spans="2:22" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C20" s="39"/>
     </row>
-    <row r="21" hidden="1">
-      <c r="C21" s="40" t="n"/>
+    <row r="21" spans="2:22" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="40"/>
     </row>
-    <row r="22" hidden="1"/>
+    <row r="22" spans="2:22" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="C1:O1"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="B4:B7"/>
     <mergeCell ref="K2:O2"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="C1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D16">
     <cfRule type="colorScale" priority="108">
@@ -2527,6 +2445,12 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="8" scale="60"/>
+  <pageSetup paperSize="8" scale="60" orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{9d258917-277f-42cd-a3cd-14c4e9ee58bc}" enabled="1" method="Standard" siteId="{38ae3bcd-9579-4fd4-adda-b42e1495d55a}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/data/Heat map 3.xlsx
+++ b/data/Heat map 3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A601403A-0876-4EFD-9130-8D6563626362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C86B21-3552-4677-BE62-E5E026807779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{45B3C54E-DB58-4340-A914-7AEE103F004F}"/>
   </bookViews>
   <sheets>
     <sheet name="Res, Cap, Product" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,13 @@
   </externalReferences>
   <definedNames>
     <definedName name="_Hlk200085589" localSheetId="0">'Res, Cap, Product'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Res, Cap, Product'!$B$1:$O$17</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Res, Cap, Product'!$B$1:$P$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="35">
   <si>
     <t>KPI by $</t>
   </si>
@@ -54,105 +57,110 @@
     <t>Product Development</t>
   </si>
   <si>
-    <t>Thomson indexed publications</t>
+    <t>Varieties released</t>
+  </si>
+  <si>
+    <t>Annual rate of genetic gain, by crop (%)</t>
+  </si>
+  <si>
+    <t>GI</t>
+  </si>
+  <si>
+    <t>Biotech</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Breeding</t>
+  </si>
+  <si>
+    <t>Genebanks</t>
+  </si>
+  <si>
+    <t>Seed System</t>
+  </si>
+  <si>
+    <t>RAFS</t>
+  </si>
+  <si>
+    <t>Plant Health</t>
+  </si>
+  <si>
+    <t>Farming Systems Agronomy</t>
+  </si>
+  <si>
+    <t>Mechanization</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>per Program Target (target/13)</t>
+  </si>
+  <si>
+    <t>Thompson indexed publications</t>
   </si>
   <si>
     <t>Publications per IRS</t>
   </si>
   <si>
-    <t>High impact publications</t>
-  </si>
-  <si>
-    <t>PhD and MsC  students enrolled</t>
-  </si>
-  <si>
-    <t>PhD and MsC  theses completed</t>
-  </si>
-  <si>
-    <t>Stakeholders trained on innovations</t>
-  </si>
-  <si>
-    <t>Training to NARES by IITA Scientists</t>
-  </si>
-  <si>
-    <t>Varieties released</t>
-  </si>
-  <si>
-    <t>Genetic gain rate</t>
-  </si>
-  <si>
-    <t>Crop Trust compliance rate</t>
-  </si>
-  <si>
-    <t>Innovations in e-Catalogue</t>
+    <t>High impact publications &gt;10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PhD and MsC students enrolled </t>
+  </si>
+  <si>
+    <t>PhD and MSc thesis accepted</t>
+  </si>
+  <si>
+    <t>Delivery partners trained</t>
+  </si>
+  <si>
+    <t>National scientists trained</t>
+  </si>
+  <si>
+    <t>Crop Trust performance compliance rate</t>
+  </si>
+  <si>
+    <t>Innovations in TAAT e-catalog</t>
   </si>
   <si>
     <t>Innovations taken on by scaling partners</t>
   </si>
   <si>
-    <t>GI</t>
-  </si>
-  <si>
-    <t>Biotech</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Breeding</t>
-  </si>
-  <si>
-    <t>Genebanks</t>
-  </si>
-  <si>
-    <t>Seed System</t>
-  </si>
-  <si>
-    <t>RAFS</t>
-  </si>
-  <si>
-    <t>Plant Health</t>
-  </si>
-  <si>
-    <t>Farming Systems Agronomy</t>
-  </si>
-  <si>
-    <t>NRM</t>
-  </si>
-  <si>
-    <t>Mechanization</t>
-  </si>
-  <si>
-    <t>ST</t>
-  </si>
-  <si>
-    <t>FIAS</t>
-  </si>
-  <si>
-    <t>GeYSI</t>
-  </si>
-  <si>
-    <t>RCA</t>
-  </si>
-  <si>
-    <t>Nutrition</t>
-  </si>
-  <si>
-    <t>VCMA</t>
-  </si>
-  <si>
-    <t>per Program Target (target/13)</t>
+    <t>Natural Resource Management</t>
+  </si>
+  <si>
+    <t>Foresight &amp; Impact Assessment</t>
+  </si>
+  <si>
+    <t>Gender, Youth &amp; Social Inclusion</t>
+  </si>
+  <si>
+    <t>Reslience &amp; Climate Adaptation</t>
+  </si>
+  <si>
+    <t>Nutrition and Health</t>
+  </si>
+  <si>
+    <t>Value Chain Markets and Agribusiness</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="0.0"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -174,13 +182,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FF0070C0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -189,20 +190,6 @@
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF00B0F0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -228,20 +215,6 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FF0070C0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF0070C0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
       <name val="Aptos Narrow"/>
@@ -261,8 +234,16 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -275,8 +256,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="23">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -285,6 +272,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -586,135 +586,274 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -738,6 +877,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="PR 1"/>
       <sheetName val="PR 2"/>
@@ -758,17 +900,15 @@
       <sheetName val="PR 18"/>
       <sheetName val="PR 19"/>
       <sheetName val="PR20"/>
-      <sheetName val="Chart1"/>
-      <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
       <sheetData sheetId="7">
         <row r="4">
           <cell r="G4">
@@ -796,23 +936,15 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20">
-        <row r="12">
-          <cell r="I12">
-            <v>1.4999999999999999E-2</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1134,792 +1266,811 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C488F41-317A-416A-97E9-EC5FF06475CE}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:V22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:W22"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="3.21875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="24.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="6.77734375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="11.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="6.77734375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="7.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="6.77734375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="8.21875" style="2" customWidth="1"/>
-    <col min="17" max="17" width="6.21875" style="2" customWidth="1"/>
-    <col min="18" max="22" width="8.21875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="3.21875" style="27" customWidth="1"/>
+    <col min="3" max="3" width="37.109375" style="12" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" style="12" customWidth="1"/>
+    <col min="5" max="9" width="6.77734375" style="12" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="6.77734375" style="12" customWidth="1"/>
+    <col min="13" max="13" width="8.33203125" style="12" customWidth="1"/>
+    <col min="14" max="16" width="6.77734375" style="12" customWidth="1"/>
+    <col min="17" max="17" width="8.21875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="6.21875" style="2" customWidth="1"/>
+    <col min="19" max="23" width="8.21875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B1" s="1"/>
-      <c r="C1" s="47" t="s">
+    <row r="1" spans="2:23" ht="15" thickBot="1">
+      <c r="B1" s="6"/>
+      <c r="C1" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="46"/>
-      <c r="P1" s="1"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
+      <c r="O1" s="61"/>
+      <c r="P1" s="62"/>
       <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
     </row>
-    <row r="2" spans="2:22" s="6" customFormat="1" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="3"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="48" t="s">
+    <row r="2" spans="2:23" s="5" customFormat="1" ht="18.600000000000001" thickBot="1">
+      <c r="B2" s="24"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="44" t="s">
+      <c r="F2" s="64"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="44" t="s">
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="46"/>
-      <c r="P2" s="3"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="68"/>
       <c r="Q2" s="3"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
     </row>
-    <row r="3" spans="2:22" s="14" customFormat="1" ht="143.55000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="7"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="9" t="s">
+    <row r="3" spans="2:23" s="13" customFormat="1" ht="143.55000000000001" customHeight="1" thickBot="1">
+      <c r="B3" s="23"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="M3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="N3" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+      <c r="V3" s="12"/>
+      <c r="W3" s="12"/>
+    </row>
+    <row r="4" spans="2:23" ht="15.45" customHeight="1">
+      <c r="B4" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="C4" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" s="10" t="s">
+      <c r="D4" s="50">
+        <v>3.4135987800000001</v>
+      </c>
+      <c r="E4" s="28">
+        <v>6.4448113026335205</v>
+      </c>
+      <c r="F4" s="29">
+        <v>0.9185948577454921</v>
+      </c>
+      <c r="G4" s="30">
+        <v>0.2929459683015237</v>
+      </c>
+      <c r="H4" s="28">
+        <v>0.2929459683015237</v>
+      </c>
+      <c r="I4" s="31">
+        <v>0.2929459683015237</v>
+      </c>
+      <c r="J4" s="31">
+        <v>19.920325844503608</v>
+      </c>
+      <c r="K4" s="32">
+        <v>53.902058167480362</v>
+      </c>
+      <c r="L4" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="N4" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="O4" s="31">
+        <v>0.2929459683015237</v>
+      </c>
+      <c r="P4" s="32">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1"/>
+    </row>
+    <row r="5" spans="2:23" ht="15.6" customHeight="1">
+      <c r="B5" s="58"/>
+      <c r="C5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="L3" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="M3" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="N3" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="13"/>
-    </row>
-    <row r="4" spans="2:22" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="16">
-        <v>6.4448113026335214</v>
-      </c>
-      <c r="E4" s="17">
-        <v>0.9185948577454921</v>
-      </c>
-      <c r="F4" s="18">
-        <v>0.2929459683015237</v>
-      </c>
-      <c r="G4" s="16">
-        <v>0.2929459683015237</v>
-      </c>
-      <c r="H4" s="19">
-        <v>0.2929459683015237</v>
-      </c>
-      <c r="I4" s="19">
-        <v>1.992032584450361E-5</v>
-      </c>
-      <c r="J4" s="20">
-        <v>53.902058167480362</v>
-      </c>
-      <c r="K4" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="L4" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="M4" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="N4" s="19">
-        <v>0.2929459683015237</v>
-      </c>
-      <c r="O4" s="20">
+      <c r="D5" s="51">
+        <v>12.720419820000002</v>
+      </c>
+      <c r="E5" s="33">
+        <v>4.0486085151865678</v>
+      </c>
+      <c r="F5" s="34">
+        <v>0.17585555770903244</v>
+      </c>
+      <c r="G5" s="35">
         <v>0</v>
       </c>
-      <c r="P4" s="1"/>
-    </row>
-    <row r="5" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="42"/>
-      <c r="C5" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="22">
-        <v>4.0486085151865678</v>
-      </c>
-      <c r="E5" s="23">
-        <v>0.17585555770903241</v>
-      </c>
-      <c r="F5" s="24">
-        <v>0</v>
-      </c>
-      <c r="G5" s="22">
-        <v>1.886730181834517</v>
-      </c>
-      <c r="H5" s="25">
+      <c r="H5" s="33">
+        <v>1.8867301818345172</v>
+      </c>
+      <c r="I5" s="36">
         <v>2.20118521214027</v>
       </c>
-      <c r="I5" s="25">
+      <c r="J5" s="36">
         <v>8.4902858182553285</v>
       </c>
-      <c r="J5" s="26">
-        <v>16.823344121357781</v>
-      </c>
-      <c r="K5" s="22">
+      <c r="K5" s="37">
+        <v>16.823344121357778</v>
+      </c>
+      <c r="L5" s="33">
         <v>1.18</v>
       </c>
-      <c r="L5" s="25">
+      <c r="M5" s="47">
         <f>'[1]PR 9'!$H$4</f>
         <v>1.1792063636465733E-3</v>
       </c>
-      <c r="M5" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="N5" s="25">
+      <c r="N5" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="O5" s="36">
         <v>0.62891006061150567</v>
       </c>
-      <c r="O5" s="26">
+      <c r="P5" s="37">
         <v>0.39306878788219107</v>
       </c>
-      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="42"/>
-      <c r="C6" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="22">
+    <row r="6" spans="2:23" ht="15.6" customHeight="1">
+      <c r="B6" s="58"/>
+      <c r="C6" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="51">
+        <v>3.5036499999999999</v>
+      </c>
+      <c r="E6" s="33">
         <v>1.427083184678835</v>
       </c>
-      <c r="E6" s="23">
-        <v>0.35677079616970869</v>
-      </c>
-      <c r="F6" s="24">
+      <c r="F6" s="34">
+        <v>0.35677079616970875</v>
+      </c>
+      <c r="G6" s="35">
         <v>0</v>
       </c>
-      <c r="G6" s="22">
+      <c r="H6" s="33">
         <v>7.4208325603299423</v>
       </c>
-      <c r="H6" s="25">
+      <c r="I6" s="36">
         <v>5.4229161017795731</v>
       </c>
-      <c r="I6" s="25">
+      <c r="J6" s="36">
         <v>1.427083184678835</v>
       </c>
-      <c r="J6" s="26">
-        <v>32.252079973741672</v>
-      </c>
-      <c r="K6" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="L6" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="M6" s="25">
+      <c r="K6" s="37">
+        <v>32.252079973741665</v>
+      </c>
+      <c r="L6" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="M6" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="N6" s="36">
         <f>'[1]PR 10'!$H$5</f>
         <v>0.28541663693576702</v>
       </c>
-      <c r="N6" s="25">
+      <c r="O6" s="36">
         <v>0</v>
       </c>
-      <c r="O6" s="26">
+      <c r="P6" s="37">
         <v>0</v>
       </c>
-      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="2:22" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="43"/>
-      <c r="C7" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="28">
+    <row r="7" spans="2:23" ht="15.6" customHeight="1" thickBot="1">
+      <c r="B7" s="59"/>
+      <c r="C7" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="52">
+        <v>21.304912170000001</v>
+      </c>
+      <c r="E7" s="38">
         <v>0.72283799515893521</v>
       </c>
-      <c r="E7" s="29">
+      <c r="F7" s="39">
         <v>4.8189199677262338E-2</v>
       </c>
-      <c r="F7" s="30">
+      <c r="G7" s="40">
         <v>0</v>
       </c>
-      <c r="G7" s="28">
-        <v>0.23468766076588801</v>
-      </c>
-      <c r="H7" s="31">
+      <c r="H7" s="38">
+        <v>0.23468766076588804</v>
+      </c>
+      <c r="I7" s="41">
         <v>0.32856272507224321</v>
       </c>
-      <c r="I7" s="31">
-        <v>105.4686347481901</v>
-      </c>
-      <c r="J7" s="32">
+      <c r="J7" s="41">
+        <v>105.46863474819008</v>
+      </c>
+      <c r="K7" s="42">
         <v>14.50369743533188</v>
       </c>
-      <c r="K7" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="L7" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="M7" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="N7" s="31">
+      <c r="L7" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="M7" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="N7" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="O7" s="41">
         <v>0.79793804660401935</v>
       </c>
-      <c r="O7" s="32">
+      <c r="P7" s="42">
         <v>9.3875064306355213E-2</v>
       </c>
-      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="16">
+    <row r="8" spans="2:23" ht="15.6" customHeight="1">
+      <c r="B8" s="57" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="50">
+        <v>7.721148311538462</v>
+      </c>
+      <c r="E8" s="28">
         <v>5.3683724657972496</v>
       </c>
-      <c r="E8" s="17">
+      <c r="F8" s="29">
         <v>0.44736437214977082</v>
       </c>
-      <c r="F8" s="18">
-        <v>0.1295144141326236</v>
-      </c>
-      <c r="G8" s="16">
-        <v>1.1656297271936129</v>
-      </c>
-      <c r="H8" s="19">
-        <v>1.1656297271936129</v>
-      </c>
-      <c r="I8" s="19">
-        <v>13.210470241527609</v>
-      </c>
-      <c r="J8" s="20">
-        <v>1.2951441413262359</v>
-      </c>
-      <c r="K8" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="L8" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="M8" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="N8" s="19">
+      <c r="G8" s="30">
+        <v>0.12951441413262363</v>
+      </c>
+      <c r="H8" s="28">
+        <v>1.1656297271936127</v>
+      </c>
+      <c r="I8" s="31">
+        <v>1.1656297271936127</v>
+      </c>
+      <c r="J8" s="31">
+        <v>13.210470241527611</v>
+      </c>
+      <c r="K8" s="32">
+        <v>1.2951441413262363</v>
+      </c>
+      <c r="L8" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="O8" s="31">
         <v>0.77708648479574172</v>
       </c>
-      <c r="O8" s="20">
-        <v>0.25902882826524731</v>
-      </c>
-      <c r="P8" s="1"/>
+      <c r="P8" s="32">
+        <v>0.25902882826524726</v>
+      </c>
+      <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="42"/>
-      <c r="C9" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="22">
-        <v>1.700457326303648</v>
-      </c>
-      <c r="E9" s="23">
+    <row r="9" spans="2:23" ht="15.6" customHeight="1">
+      <c r="B9" s="58"/>
+      <c r="C9" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="51">
+        <v>12.273168915897436</v>
+      </c>
+      <c r="E9" s="33">
+        <v>1.7004573263036482</v>
+      </c>
+      <c r="F9" s="34">
         <v>8.5022866315182424E-2</v>
       </c>
-      <c r="F9" s="24">
+      <c r="G9" s="35">
         <v>6.7627196014951027E-2</v>
       </c>
-      <c r="G9" s="22">
-        <v>1.79252808714328</v>
-      </c>
-      <c r="H9" s="25">
+      <c r="H9" s="33">
+        <v>1.7925280871432805</v>
+      </c>
+      <c r="I9" s="36">
         <v>1.1406996918184511</v>
       </c>
-      <c r="I9" s="25">
-        <v>259.50917988869759</v>
-      </c>
-      <c r="J9" s="26">
+      <c r="J9" s="36">
+        <v>259.50917988869764</v>
+      </c>
+      <c r="K9" s="37">
         <v>18.984502013835652</v>
       </c>
-      <c r="K9" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="L9" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="M9" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="N9" s="25">
+      <c r="L9" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="O9" s="36">
         <v>8.147854941560366E-2</v>
       </c>
-      <c r="O9" s="26">
+      <c r="P9" s="37">
         <v>0.7333069447404329</v>
       </c>
-      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="42"/>
-      <c r="C10" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="22">
+    <row r="10" spans="2:23" ht="15.6" customHeight="1">
+      <c r="B10" s="58"/>
+      <c r="C10" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="51">
+        <v>7.1819852465641034</v>
+      </c>
+      <c r="E10" s="33">
         <v>2.1581776441848408</v>
       </c>
-      <c r="E10" s="23">
-        <v>0.30831109202640578</v>
-      </c>
-      <c r="F10" s="24">
-        <v>0.27847453473352779</v>
-      </c>
-      <c r="G10" s="22">
+      <c r="F10" s="34">
+        <v>0.30831109202640583</v>
+      </c>
+      <c r="G10" s="35">
+        <v>0.27847453473352785</v>
+      </c>
+      <c r="H10" s="33">
         <v>0.97466087156734749</v>
       </c>
-      <c r="H10" s="25">
+      <c r="I10" s="36">
         <v>0.4177118021002918</v>
       </c>
-      <c r="I10" s="25">
+      <c r="J10" s="36">
         <v>522.69670169483186</v>
       </c>
-      <c r="J10" s="26">
+      <c r="K10" s="37">
         <v>2.7847453473352788</v>
       </c>
-      <c r="K10" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="L10" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="M10" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="N10" s="25">
-        <v>1.3923726736676389</v>
-      </c>
-      <c r="O10" s="26">
-        <v>0.27847453473352779</v>
-      </c>
-      <c r="P10" s="1"/>
+      <c r="L10" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="O10" s="36">
+        <v>1.3923726736676394</v>
+      </c>
+      <c r="P10" s="37">
+        <v>0.27847453473352785</v>
+      </c>
+      <c r="Q10" s="1"/>
     </row>
-    <row r="11" spans="2:22" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="43"/>
-      <c r="C11" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="28">
+    <row r="11" spans="2:23" ht="15.6" customHeight="1" thickBot="1">
+      <c r="B11" s="59"/>
+      <c r="C11" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="52">
+        <v>0.57107699999999995</v>
+      </c>
+      <c r="E11" s="38">
         <v>0</v>
       </c>
-      <c r="E11" s="29">
+      <c r="F11" s="39">
         <v>0</v>
       </c>
-      <c r="F11" s="30">
+      <c r="G11" s="40">
         <v>0</v>
       </c>
-      <c r="G11" s="28">
-        <v>3.502154700679593</v>
-      </c>
-      <c r="H11" s="31">
-        <v>1.7510773503397969</v>
-      </c>
-      <c r="I11" s="31">
+      <c r="H11" s="38">
+        <v>3.5021547006795934</v>
+      </c>
+      <c r="I11" s="41">
+        <v>1.7510773503397967</v>
+      </c>
+      <c r="J11" s="41">
         <v>0</v>
       </c>
-      <c r="J11" s="32">
+      <c r="K11" s="42">
         <v>0</v>
       </c>
-      <c r="K11" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="L11" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="M11" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="N11" s="31">
+      <c r="L11" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="M11" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="N11" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="O11" s="41">
         <v>5.2532320510193893</v>
       </c>
-      <c r="O11" s="32">
+      <c r="P11" s="42">
         <v>5.2532320510193893</v>
       </c>
-      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="16">
+    <row r="12" spans="2:23" ht="15.6" customHeight="1">
+      <c r="B12" s="57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="53">
+        <v>1.3649733500000001</v>
+      </c>
+      <c r="E12" s="28">
         <v>7.267541157488532</v>
       </c>
-      <c r="E12" s="17">
+      <c r="F12" s="29">
         <v>0.66068555977168475</v>
       </c>
-      <c r="F12" s="18">
+      <c r="G12" s="30">
         <v>0</v>
       </c>
-      <c r="G12" s="16">
+      <c r="H12" s="28">
         <v>3.6630751801857522</v>
       </c>
-      <c r="H12" s="19">
+      <c r="I12" s="31">
         <v>3.6630751801857522</v>
       </c>
-      <c r="I12" s="19">
+      <c r="J12" s="31">
         <v>68.865813387492139</v>
       </c>
-      <c r="J12" s="20">
+      <c r="K12" s="32">
         <v>79.855038928049396</v>
       </c>
-      <c r="K12" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="L12" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="M12" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="N12" s="19">
+      <c r="L12" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="31">
         <v>0</v>
       </c>
-      <c r="O12" s="20">
+      <c r="P12" s="32">
         <v>0</v>
       </c>
-      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="42"/>
-      <c r="C13" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="22">
+    <row r="13" spans="2:23" ht="15.6" customHeight="1">
+      <c r="B13" s="58"/>
+      <c r="C13" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="54">
+        <v>7.5363555180000006</v>
+      </c>
+      <c r="E13" s="33">
         <v>0.8757548637715421</v>
       </c>
-      <c r="E13" s="23">
+      <c r="F13" s="34">
         <v>7.9614078524685647E-2</v>
       </c>
-      <c r="F13" s="24">
+      <c r="G13" s="35">
         <v>0</v>
       </c>
-      <c r="G13" s="22">
+      <c r="H13" s="33">
         <v>0.53076052349790426</v>
       </c>
-      <c r="H13" s="25">
-        <v>0.39807039262342819</v>
-      </c>
-      <c r="I13" s="25">
-        <v>253.70353023199829</v>
-      </c>
-      <c r="J13" s="26">
+      <c r="I13" s="36">
+        <v>0.39807039262342825</v>
+      </c>
+      <c r="J13" s="36">
+        <v>253.70353023199826</v>
+      </c>
+      <c r="K13" s="37">
         <v>20.699660416418268</v>
       </c>
-      <c r="K13" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="L13" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="M13" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="N13" s="25">
+      <c r="L13" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="36">
         <v>0.33172532718619019</v>
       </c>
-      <c r="O13" s="26">
+      <c r="P13" s="37">
         <v>0</v>
       </c>
-      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
     </row>
-    <row r="14" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="42"/>
-      <c r="C14" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="22">
+    <row r="14" spans="2:23" ht="15.6" customHeight="1">
+      <c r="B14" s="58"/>
+      <c r="C14" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="54">
+        <v>2.1255060000000001</v>
+      </c>
+      <c r="E14" s="33">
         <v>6.2714478340686881</v>
       </c>
-      <c r="E14" s="23">
-        <v>1.254289566813737</v>
-      </c>
-      <c r="F14" s="24">
+      <c r="F14" s="34">
+        <v>1.2542895668137375</v>
+      </c>
+      <c r="G14" s="35">
         <v>0.47047620660680323</v>
       </c>
-      <c r="G14" s="22">
+      <c r="H14" s="33">
         <v>0.47047620660680323</v>
       </c>
-      <c r="H14" s="25">
+      <c r="I14" s="36">
         <v>0.94095241321360645</v>
       </c>
-      <c r="I14" s="25">
+      <c r="J14" s="36">
         <v>0</v>
       </c>
-      <c r="J14" s="26">
+      <c r="K14" s="37">
         <v>0</v>
       </c>
-      <c r="K14" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="L14" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="M14" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="N14" s="25">
-        <v>1.1761905165170079</v>
-      </c>
-      <c r="O14" s="26">
+      <c r="L14" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="36">
+        <v>1.1761905165170081</v>
+      </c>
+      <c r="P14" s="37">
         <v>0</v>
       </c>
-      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
     </row>
-    <row r="15" spans="2:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="42"/>
-      <c r="C15" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="22">
+    <row r="15" spans="2:23" ht="15.6" customHeight="1">
+      <c r="B15" s="58"/>
+      <c r="C15" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="54">
+        <v>1.4569589599999999</v>
+      </c>
+      <c r="E15" s="33">
         <v>8.5795141408787519</v>
       </c>
-      <c r="E15" s="23">
+      <c r="F15" s="34">
         <v>2.144878535219688</v>
       </c>
-      <c r="F15" s="24">
+      <c r="G15" s="35">
         <v>0</v>
       </c>
-      <c r="G15" s="22">
-        <v>1.3727222625405999</v>
-      </c>
-      <c r="H15" s="25">
-        <v>5.4908890501624006</v>
-      </c>
-      <c r="I15" s="25">
+      <c r="H15" s="33">
+        <v>1.3727222625406004</v>
+      </c>
+      <c r="I15" s="36">
+        <v>5.4908890501624015</v>
+      </c>
+      <c r="J15" s="36">
         <v>89.226947065139029</v>
       </c>
-      <c r="J15" s="26">
-        <v>10.2954169690545</v>
-      </c>
-      <c r="K15" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="L15" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="M15" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="N15" s="25">
+      <c r="K15" s="37">
+        <v>10.295416969054504</v>
+      </c>
+      <c r="L15" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="36">
         <v>0</v>
       </c>
-      <c r="O15" s="26">
+      <c r="P15" s="37">
         <v>0</v>
       </c>
-      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
     </row>
-    <row r="16" spans="2:22" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="43"/>
-      <c r="C16" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="28">
+    <row r="16" spans="2:23" ht="15.6" customHeight="1" thickBot="1">
+      <c r="B16" s="59"/>
+      <c r="C16" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="55">
+        <v>5.7995670199999996</v>
+      </c>
+      <c r="E16" s="38">
         <v>0.51727999515384515</v>
       </c>
-      <c r="E16" s="29">
-        <v>5.1727999515384523E-2</v>
-      </c>
-      <c r="F16" s="30">
+      <c r="F16" s="39">
+        <v>5.1727999515384517E-2</v>
+      </c>
+      <c r="G16" s="40">
         <v>0</v>
       </c>
-      <c r="G16" s="28">
+      <c r="H16" s="38">
         <v>0.86213332525640862</v>
       </c>
-      <c r="H16" s="31">
+      <c r="I16" s="41">
         <v>0.51727999515384515</v>
       </c>
-      <c r="I16" s="31">
-        <v>173.63365170664071</v>
-      </c>
-      <c r="J16" s="32">
+      <c r="J16" s="41">
+        <v>173.63365170664068</v>
+      </c>
+      <c r="K16" s="42">
         <v>13.966559869153819</v>
       </c>
-      <c r="K16" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="L16" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="M16" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="N16" s="31">
+      <c r="L16" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="41">
         <v>0</v>
       </c>
-      <c r="O16" s="32">
+      <c r="P16" s="42">
         <v>0</v>
       </c>
-      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
     </row>
-    <row r="17" spans="2:22" s="35" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="34"/>
-      <c r="C17" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="37">
+    <row r="17" spans="2:23" s="18" customFormat="1">
+      <c r="B17" s="26"/>
+      <c r="C17" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="56">
+        <v>86.97332109200002</v>
+      </c>
+      <c r="E17" s="44">
         <v>3.1273958104035091</v>
       </c>
-      <c r="E17" s="37">
-        <v>2.2995557429437569E-2</v>
-      </c>
-      <c r="F17" s="37">
-        <v>0.14947112329134421</v>
-      </c>
-      <c r="G17" s="37">
-        <v>1.724666807207818</v>
-      </c>
-      <c r="H17" s="37">
+      <c r="F17" s="44">
+        <v>2.2995557429437565E-2</v>
+      </c>
+      <c r="G17" s="44">
+        <v>0.14947112329134418</v>
+      </c>
+      <c r="H17" s="44">
+        <v>1.7246668072078175</v>
+      </c>
+      <c r="I17" s="44">
         <v>0.689866722883127</v>
       </c>
-      <c r="I17" s="37">
+      <c r="J17" s="44">
         <v>137.97334457662541</v>
       </c>
-      <c r="J17" s="37">
-        <v>1.724666807207818</v>
-      </c>
-      <c r="K17" s="37">
-        <v>6.8986672288312692E-2</v>
-      </c>
-      <c r="L17" s="37">
-        <v>1.7246668072078169E-4</v>
-      </c>
-      <c r="M17" s="37">
-        <v>1.1497778714718781E-2</v>
-      </c>
-      <c r="N17" s="37">
-        <v>0.22995557429437569</v>
-      </c>
-      <c r="O17" s="37">
+      <c r="K17" s="44">
+        <v>1.7246668072078175</v>
+      </c>
+      <c r="L17" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="44">
+        <v>0.22995557429437566</v>
+      </c>
+      <c r="P17" s="44">
         <v>0.3449333614415635</v>
       </c>
-      <c r="P17" s="34"/>
-      <c r="Q17" s="34"/>
-      <c r="R17" s="34"/>
-      <c r="S17" s="34"/>
-      <c r="T17" s="34"/>
-      <c r="U17" s="34"/>
-      <c r="V17" s="34"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="17"/>
+      <c r="T17" s="17"/>
+      <c r="U17" s="17"/>
+      <c r="V17" s="17"/>
+      <c r="W17" s="17"/>
     </row>
-    <row r="19" spans="2:22" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="38"/>
+    <row r="19" spans="2:23" hidden="1">
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
     </row>
-    <row r="20" spans="2:22" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="39"/>
+    <row r="20" spans="2:23" hidden="1">
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
     </row>
-    <row r="21" spans="2:22" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="40"/>
+    <row r="21" spans="2:23" hidden="1">
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
     </row>
-    <row r="22" spans="2:22" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="2:23" hidden="1"/>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="B8:B11"/>
     <mergeCell ref="B12:B16"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="C1:O1"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="K2:O2"/>
+    <mergeCell ref="C1:P1"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="L2:P2"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:D16">
+  <conditionalFormatting sqref="E4:E16">
     <cfRule type="colorScale" priority="108">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="formula" val="$D$17/2"/>
-        <cfvo type="formula" val="$D$17"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E16">
-    <cfRule type="colorScale" priority="111">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="110">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="109">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$E$17/2"/>
@@ -1931,27 +2082,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F16">
-    <cfRule type="colorScale" priority="114">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="113">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="112">
+    <cfRule type="colorScale" priority="109">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$F$17/2"/>
@@ -1961,29 +2092,29 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="110">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="111">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G16">
-    <cfRule type="colorScale" priority="117">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="116">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="115">
+    <cfRule type="colorScale" priority="112">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$G$17/2"/>
@@ -1993,9 +2124,29 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="113">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="114">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H16">
-    <cfRule type="colorScale" priority="118">
+    <cfRule type="colorScale" priority="115">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$H$17/2"/>
@@ -2005,9 +2156,29 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="116">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="117">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:I16">
-    <cfRule type="colorScale" priority="119">
+    <cfRule type="colorScale" priority="118">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$I$17/2"/>
@@ -2017,19 +2188,9 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="120">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J16">
-    <cfRule type="colorScale" priority="121">
+    <cfRule type="colorScale" priority="119">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$J$17/2"/>
@@ -2039,7 +2200,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="122">
+    <cfRule type="colorScale" priority="120">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2051,30 +2212,52 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:K16">
-    <cfRule type="colorScale" priority="123">
+    <cfRule type="colorScale" priority="121">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$K$17/2"/>
         <cfvo type="formula" val="$K$17"/>
         <color rgb="FFFF0000"/>
-        <color rgb="FFFFEB84"/>
+        <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="122">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4:L16">
+    <cfRule type="colorScale" priority="123">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="formula" val="1.18"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M4:M16">
     <cfRule type="colorScale" priority="124">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$L$17/2"/>
-        <cfvo type="formula" val="$L$17"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1E-3"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:M5">
+  <conditionalFormatting sqref="N4:N5">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -2186,11 +2369,11 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M6">
+  <conditionalFormatting sqref="N6">
     <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="MAX($M$4:$M$16)/2"/>
+        <cfvo type="formula" val="MAX($N$4:$N$16)/2"/>
         <cfvo type="max"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
@@ -2248,7 +2431,47 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M7:M16">
+  <conditionalFormatting sqref="N7:N16">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="MAX(#REF!)/2"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2259,40 +2482,50 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="14">
+    <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="MAX(#REF!)/2"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="MAX(#REF!)/2"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
@@ -2309,91 +2542,9 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="formula" val="MAX(#REF!)/2"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="23">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="formula" val="MAX(#REF!)/2"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N4:N16">
-    <cfRule type="colorScale" priority="125">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="formula" val="$N$17/2"/>
-        <cfvo type="formula" val="$N$17"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="126">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="127">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O4:O16">
-    <cfRule type="colorScale" priority="128">
+    <cfRule type="colorScale" priority="125">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$O$17/2"/>
@@ -2403,6 +2554,38 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="126">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="127">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P4:P16">
+    <cfRule type="colorScale" priority="128">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$P$17/2"/>
+        <cfvo type="formula" val="$P$17"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="129">
       <colorScale>
         <cfvo type="min"/>
@@ -2445,7 +2628,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="8" scale="60" orientation="landscape"/>
+  <pageSetup paperSize="8" scale="60" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/data/Heat map 3.xlsx
+++ b/data/Heat map 3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C86B21-3552-4677-BE62-E5E026807779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{240C0ABD-DD08-429B-B166-D979D8ECE3B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{45B3C54E-DB58-4340-A914-7AEE103F004F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{45B3C54E-DB58-4340-A914-7AEE103F004F}"/>
   </bookViews>
   <sheets>
     <sheet name="Res, Cap, Product" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="35">
   <si>
     <t>KPI by $</t>
   </si>
@@ -160,7 +160,7 @@
     <numFmt numFmtId="166" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,18 +177,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -671,69 +659,60 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -782,7 +761,7 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -800,32 +779,32 @@
     <xf numFmtId="167" fontId="2" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -920,9 +899,6 @@
         <row r="4">
           <cell r="G4">
             <v>6.521739130434782E-4</v>
-          </cell>
-          <cell r="H4">
-            <v>1.1792063636465733E-3</v>
           </cell>
         </row>
       </sheetData>
@@ -1271,794 +1247,754 @@
     <tabColor rgb="FFFF0000"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:W22"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="B1:P22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="3.21875" style="27" customWidth="1"/>
-    <col min="3" max="3" width="37.109375" style="12" customWidth="1"/>
-    <col min="4" max="4" width="5.77734375" style="12" customWidth="1"/>
-    <col min="5" max="9" width="6.77734375" style="12" customWidth="1"/>
-    <col min="10" max="10" width="11.44140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="6.77734375" style="12" customWidth="1"/>
-    <col min="13" max="13" width="8.33203125" style="12" customWidth="1"/>
-    <col min="14" max="16" width="6.77734375" style="12" customWidth="1"/>
-    <col min="17" max="17" width="8.21875" style="2" customWidth="1"/>
-    <col min="18" max="18" width="6.21875" style="2" customWidth="1"/>
-    <col min="19" max="23" width="8.21875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="3.21875" style="22" customWidth="1"/>
+    <col min="3" max="3" width="37.109375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" style="8" customWidth="1"/>
+    <col min="5" max="9" width="6.77734375" style="8" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="6.77734375" style="8" customWidth="1"/>
+    <col min="13" max="13" width="8.33203125" style="8" customWidth="1"/>
+    <col min="14" max="16" width="6.77734375" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:23" ht="15" thickBot="1">
-      <c r="B1" s="6"/>
-      <c r="C1" s="60" t="s">
+    <row r="1" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="2"/>
+      <c r="C1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
-      <c r="N1" s="61"/>
-      <c r="O1" s="61"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="57"/>
     </row>
-    <row r="2" spans="2:23" s="5" customFormat="1" ht="18.600000000000001" thickBot="1">
-      <c r="B2" s="24"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="63" t="s">
+    <row r="2" spans="2:16" s="1" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="19"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="64"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="66" t="s">
+      <c r="F2" s="59"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="66" t="s">
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="68"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
+      <c r="M2" s="62"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="63"/>
     </row>
-    <row r="3" spans="2:23" s="13" customFormat="1" ht="143.55000000000001" customHeight="1" thickBot="1">
-      <c r="B3" s="23"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="49" t="s">
+    <row r="3" spans="2:16" s="9" customFormat="1" ht="143.55000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="18"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="N3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="O3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="P3" s="10" t="s">
+      <c r="P3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="12"/>
-      <c r="T3" s="12"/>
-      <c r="U3" s="12"/>
-      <c r="V3" s="12"/>
-      <c r="W3" s="12"/>
     </row>
-    <row r="4" spans="2:23" ht="15.45" customHeight="1">
-      <c r="B4" s="57" t="s">
+    <row r="4" spans="2:16" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="50">
+      <c r="D4" s="45">
         <v>3.4135987800000001</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="23">
         <v>6.4448113026335205</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="24">
         <v>0.9185948577454921</v>
       </c>
-      <c r="G4" s="30">
+      <c r="G4" s="25">
         <v>0.2929459683015237</v>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="23">
         <v>0.2929459683015237</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="26">
         <v>0.2929459683015237</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="26">
         <v>19.920325844503608</v>
       </c>
-      <c r="K4" s="32">
+      <c r="K4" s="27">
         <v>53.902058167480362</v>
       </c>
-      <c r="L4" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="M4" s="46" t="s">
-        <v>8</v>
-      </c>
-      <c r="N4" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="O4" s="31">
+      <c r="L4" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="N4" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="O4" s="26">
         <v>0.2929459683015237</v>
       </c>
-      <c r="P4" s="32">
+      <c r="P4" s="27">
         <v>0</v>
       </c>
-      <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="2:23" ht="15.6" customHeight="1">
-      <c r="B5" s="58"/>
-      <c r="C5" s="15" t="s">
+    <row r="5" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="53"/>
+      <c r="C5" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="51">
+      <c r="D5" s="46">
         <v>12.720419820000002</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="28">
         <v>4.0486085151865678</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="29">
         <v>0.17585555770903244</v>
       </c>
-      <c r="G5" s="35">
+      <c r="G5" s="30">
         <v>0</v>
       </c>
-      <c r="H5" s="33">
+      <c r="H5" s="28">
         <v>1.8867301818345172</v>
       </c>
-      <c r="I5" s="36">
+      <c r="I5" s="31">
         <v>2.20118521214027</v>
       </c>
-      <c r="J5" s="36">
+      <c r="J5" s="31">
         <v>8.4902858182553285</v>
       </c>
-      <c r="K5" s="37">
+      <c r="K5" s="32">
         <v>16.823344121357778</v>
       </c>
-      <c r="L5" s="33">
+      <c r="L5" s="28">
         <v>1.18</v>
       </c>
-      <c r="M5" s="47">
-        <f>'[1]PR 9'!$H$4</f>
-        <v>1.1792063636465733E-3</v>
-      </c>
-      <c r="N5" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="O5" s="36">
+      <c r="M5" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="N5" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="O5" s="31">
         <v>0.62891006061150567</v>
       </c>
-      <c r="P5" s="37">
+      <c r="P5" s="32">
         <v>0.39306878788219107</v>
       </c>
-      <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="2:23" ht="15.6" customHeight="1">
-      <c r="B6" s="58"/>
-      <c r="C6" s="15" t="s">
+    <row r="6" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="53"/>
+      <c r="C6" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="51">
+      <c r="D6" s="46">
         <v>3.5036499999999999</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="28">
         <v>1.427083184678835</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="29">
         <v>0.35677079616970875</v>
       </c>
-      <c r="G6" s="35">
+      <c r="G6" s="30">
         <v>0</v>
       </c>
-      <c r="H6" s="33">
+      <c r="H6" s="28">
         <v>7.4208325603299423</v>
       </c>
-      <c r="I6" s="36">
+      <c r="I6" s="31">
         <v>5.4229161017795731</v>
       </c>
-      <c r="J6" s="36">
+      <c r="J6" s="31">
         <v>1.427083184678835</v>
       </c>
-      <c r="K6" s="37">
+      <c r="K6" s="32">
         <v>32.252079973741665</v>
       </c>
-      <c r="L6" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="M6" s="47" t="s">
-        <v>8</v>
-      </c>
-      <c r="N6" s="36">
+      <c r="L6" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="M6" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="N6" s="31">
         <f>'[1]PR 10'!$H$5</f>
         <v>0.28541663693576702</v>
       </c>
-      <c r="O6" s="36">
+      <c r="O6" s="31">
         <v>0</v>
       </c>
-      <c r="P6" s="37">
+      <c r="P6" s="32">
         <v>0</v>
       </c>
-      <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="2:23" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B7" s="59"/>
-      <c r="C7" s="16" t="s">
+    <row r="7" spans="2:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="54"/>
+      <c r="C7" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="52">
+      <c r="D7" s="47">
         <v>21.304912170000001</v>
       </c>
-      <c r="E7" s="38">
+      <c r="E7" s="33">
         <v>0.72283799515893521</v>
       </c>
-      <c r="F7" s="39">
+      <c r="F7" s="34">
         <v>4.8189199677262338E-2</v>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="35">
         <v>0</v>
       </c>
-      <c r="H7" s="38">
+      <c r="H7" s="33">
         <v>0.23468766076588804</v>
       </c>
-      <c r="I7" s="41">
+      <c r="I7" s="36">
         <v>0.32856272507224321</v>
       </c>
-      <c r="J7" s="41">
+      <c r="J7" s="36">
         <v>105.46863474819008</v>
       </c>
-      <c r="K7" s="42">
+      <c r="K7" s="37">
         <v>14.50369743533188</v>
       </c>
-      <c r="L7" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="M7" s="48" t="s">
-        <v>8</v>
-      </c>
-      <c r="N7" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="O7" s="41">
+      <c r="L7" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="M7" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="N7" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="O7" s="36">
         <v>0.79793804660401935</v>
       </c>
-      <c r="P7" s="42">
+      <c r="P7" s="37">
         <v>9.3875064306355213E-2</v>
       </c>
-      <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="2:23" ht="15.6" customHeight="1">
-      <c r="B8" s="57" t="s">
+    <row r="8" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="50">
+      <c r="D8" s="45">
         <v>7.721148311538462</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="23">
         <v>5.3683724657972496</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="24">
         <v>0.44736437214977082</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="25">
         <v>0.12951441413262363</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="23">
         <v>1.1656297271936127</v>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="26">
         <v>1.1656297271936127</v>
       </c>
-      <c r="J8" s="31">
+      <c r="J8" s="26">
         <v>13.210470241527611</v>
       </c>
-      <c r="K8" s="32">
+      <c r="K8" s="27">
         <v>1.2951441413262363</v>
       </c>
-      <c r="L8" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="M8" s="46" t="s">
-        <v>8</v>
-      </c>
-      <c r="N8" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="O8" s="31">
+      <c r="L8" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="O8" s="26">
         <v>0.77708648479574172</v>
       </c>
-      <c r="P8" s="32">
+      <c r="P8" s="27">
         <v>0.25902882826524726</v>
       </c>
-      <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="2:23" ht="15.6" customHeight="1">
-      <c r="B9" s="58"/>
-      <c r="C9" s="15" t="s">
+    <row r="9" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="53"/>
+      <c r="C9" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="51">
+      <c r="D9" s="46">
         <v>12.273168915897436</v>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="28">
         <v>1.7004573263036482</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="29">
         <v>8.5022866315182424E-2</v>
       </c>
-      <c r="G9" s="35">
+      <c r="G9" s="30">
         <v>6.7627196014951027E-2</v>
       </c>
-      <c r="H9" s="33">
+      <c r="H9" s="28">
         <v>1.7925280871432805</v>
       </c>
-      <c r="I9" s="36">
+      <c r="I9" s="31">
         <v>1.1406996918184511</v>
       </c>
-      <c r="J9" s="36">
+      <c r="J9" s="31">
         <v>259.50917988869764</v>
       </c>
-      <c r="K9" s="37">
+      <c r="K9" s="32">
         <v>18.984502013835652</v>
       </c>
-      <c r="L9" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="M9" s="47" t="s">
-        <v>8</v>
-      </c>
-      <c r="N9" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="O9" s="36">
+      <c r="L9" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="O9" s="31">
         <v>8.147854941560366E-2</v>
       </c>
-      <c r="P9" s="37">
+      <c r="P9" s="32">
         <v>0.7333069447404329</v>
       </c>
-      <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="2:23" ht="15.6" customHeight="1">
-      <c r="B10" s="58"/>
-      <c r="C10" s="15" t="s">
+    <row r="10" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="53"/>
+      <c r="C10" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="51">
+      <c r="D10" s="46">
         <v>7.1819852465641034</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="28">
         <v>2.1581776441848408</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="29">
         <v>0.30831109202640583</v>
       </c>
-      <c r="G10" s="35">
+      <c r="G10" s="30">
         <v>0.27847453473352785</v>
       </c>
-      <c r="H10" s="33">
+      <c r="H10" s="28">
         <v>0.97466087156734749</v>
       </c>
-      <c r="I10" s="36">
+      <c r="I10" s="31">
         <v>0.4177118021002918</v>
       </c>
-      <c r="J10" s="36">
+      <c r="J10" s="31">
         <v>522.69670169483186</v>
       </c>
-      <c r="K10" s="37">
+      <c r="K10" s="32">
         <v>2.7847453473352788</v>
       </c>
-      <c r="L10" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="M10" s="47" t="s">
-        <v>8</v>
-      </c>
-      <c r="N10" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="O10" s="36">
+      <c r="L10" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="O10" s="31">
         <v>1.3923726736676394</v>
       </c>
-      <c r="P10" s="37">
+      <c r="P10" s="32">
         <v>0.27847453473352785</v>
       </c>
-      <c r="Q10" s="1"/>
     </row>
-    <row r="11" spans="2:23" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B11" s="59"/>
-      <c r="C11" s="16" t="s">
+    <row r="11" spans="2:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="54"/>
+      <c r="C11" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="52">
+      <c r="D11" s="47">
         <v>0.57107699999999995</v>
       </c>
-      <c r="E11" s="38">
+      <c r="E11" s="33">
         <v>0</v>
       </c>
-      <c r="F11" s="39">
+      <c r="F11" s="34">
         <v>0</v>
       </c>
-      <c r="G11" s="40">
+      <c r="G11" s="35">
         <v>0</v>
       </c>
-      <c r="H11" s="38">
+      <c r="H11" s="33">
         <v>3.5021547006795934</v>
       </c>
-      <c r="I11" s="41">
+      <c r="I11" s="36">
         <v>1.7510773503397967</v>
       </c>
-      <c r="J11" s="41">
+      <c r="J11" s="36">
         <v>0</v>
       </c>
-      <c r="K11" s="42">
+      <c r="K11" s="37">
         <v>0</v>
       </c>
-      <c r="L11" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="M11" s="48" t="s">
-        <v>8</v>
-      </c>
-      <c r="N11" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="O11" s="41">
+      <c r="L11" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="M11" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="N11" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="O11" s="36">
         <v>5.2532320510193893</v>
       </c>
-      <c r="P11" s="42">
+      <c r="P11" s="37">
         <v>5.2532320510193893</v>
       </c>
-      <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="2:23" ht="15.6" customHeight="1">
-      <c r="B12" s="57" t="s">
+    <row r="12" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="53">
+      <c r="D12" s="48">
         <v>1.3649733500000001</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="23">
         <v>7.267541157488532</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="24">
         <v>0.66068555977168475</v>
       </c>
-      <c r="G12" s="30">
+      <c r="G12" s="25">
         <v>0</v>
       </c>
-      <c r="H12" s="28">
+      <c r="H12" s="23">
         <v>3.6630751801857522</v>
       </c>
-      <c r="I12" s="31">
+      <c r="I12" s="26">
         <v>3.6630751801857522</v>
       </c>
-      <c r="J12" s="31">
+      <c r="J12" s="26">
         <v>68.865813387492139</v>
       </c>
-      <c r="K12" s="32">
+      <c r="K12" s="27">
         <v>79.855038928049396</v>
       </c>
-      <c r="L12" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="M12" s="46" t="s">
-        <v>8</v>
-      </c>
-      <c r="N12" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="O12" s="31">
+      <c r="L12" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="26">
         <v>0</v>
       </c>
-      <c r="P12" s="32">
+      <c r="P12" s="27">
         <v>0</v>
       </c>
-      <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="2:23" ht="15.6" customHeight="1">
-      <c r="B13" s="58"/>
-      <c r="C13" s="15" t="s">
+    <row r="13" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="53"/>
+      <c r="C13" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="54">
+      <c r="D13" s="49">
         <v>7.5363555180000006</v>
       </c>
-      <c r="E13" s="33">
+      <c r="E13" s="28">
         <v>0.8757548637715421</v>
       </c>
-      <c r="F13" s="34">
+      <c r="F13" s="29">
         <v>7.9614078524685647E-2</v>
       </c>
-      <c r="G13" s="35">
+      <c r="G13" s="30">
         <v>0</v>
       </c>
-      <c r="H13" s="33">
+      <c r="H13" s="28">
         <v>0.53076052349790426</v>
       </c>
-      <c r="I13" s="36">
+      <c r="I13" s="31">
         <v>0.39807039262342825</v>
       </c>
-      <c r="J13" s="36">
+      <c r="J13" s="31">
         <v>253.70353023199826</v>
       </c>
-      <c r="K13" s="37">
+      <c r="K13" s="32">
         <v>20.699660416418268</v>
       </c>
-      <c r="L13" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="M13" s="47" t="s">
-        <v>8</v>
-      </c>
-      <c r="N13" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="O13" s="36">
+      <c r="L13" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="31">
         <v>0.33172532718619019</v>
       </c>
-      <c r="P13" s="37">
+      <c r="P13" s="32">
         <v>0</v>
       </c>
-      <c r="Q13" s="1"/>
     </row>
-    <row r="14" spans="2:23" ht="15.6" customHeight="1">
-      <c r="B14" s="58"/>
-      <c r="C14" s="15" t="s">
+    <row r="14" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="53"/>
+      <c r="C14" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="54">
+      <c r="D14" s="49">
         <v>2.1255060000000001</v>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="28">
         <v>6.2714478340686881</v>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="29">
         <v>1.2542895668137375</v>
       </c>
-      <c r="G14" s="35">
+      <c r="G14" s="30">
         <v>0.47047620660680323</v>
       </c>
-      <c r="H14" s="33">
+      <c r="H14" s="28">
         <v>0.47047620660680323</v>
       </c>
-      <c r="I14" s="36">
+      <c r="I14" s="31">
         <v>0.94095241321360645</v>
       </c>
-      <c r="J14" s="36">
+      <c r="J14" s="31">
         <v>0</v>
       </c>
-      <c r="K14" s="37">
+      <c r="K14" s="32">
         <v>0</v>
       </c>
-      <c r="L14" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="47" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="36">
+      <c r="L14" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="31">
         <v>1.1761905165170081</v>
       </c>
-      <c r="P14" s="37">
+      <c r="P14" s="32">
         <v>0</v>
       </c>
-      <c r="Q14" s="1"/>
     </row>
-    <row r="15" spans="2:23" ht="15.6" customHeight="1">
-      <c r="B15" s="58"/>
-      <c r="C15" s="15" t="s">
+    <row r="15" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="53"/>
+      <c r="C15" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="54">
+      <c r="D15" s="49">
         <v>1.4569589599999999</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="28">
         <v>8.5795141408787519</v>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="29">
         <v>2.144878535219688</v>
       </c>
-      <c r="G15" s="35">
+      <c r="G15" s="30">
         <v>0</v>
       </c>
-      <c r="H15" s="33">
+      <c r="H15" s="28">
         <v>1.3727222625406004</v>
       </c>
-      <c r="I15" s="36">
+      <c r="I15" s="31">
         <v>5.4908890501624015</v>
       </c>
-      <c r="J15" s="36">
+      <c r="J15" s="31">
         <v>89.226947065139029</v>
       </c>
-      <c r="K15" s="37">
+      <c r="K15" s="32">
         <v>10.295416969054504</v>
       </c>
-      <c r="L15" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="M15" s="47" t="s">
-        <v>8</v>
-      </c>
-      <c r="N15" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="O15" s="36">
+      <c r="L15" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="31">
         <v>0</v>
       </c>
-      <c r="P15" s="37">
+      <c r="P15" s="32">
         <v>0</v>
       </c>
-      <c r="Q15" s="1"/>
     </row>
-    <row r="16" spans="2:23" ht="15.6" customHeight="1" thickBot="1">
-      <c r="B16" s="59"/>
-      <c r="C16" s="16" t="s">
+    <row r="16" spans="2:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="54"/>
+      <c r="C16" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="55">
+      <c r="D16" s="50">
         <v>5.7995670199999996</v>
       </c>
-      <c r="E16" s="38">
+      <c r="E16" s="33">
         <v>0.51727999515384515</v>
       </c>
-      <c r="F16" s="39">
+      <c r="F16" s="34">
         <v>5.1727999515384517E-2</v>
       </c>
-      <c r="G16" s="40">
+      <c r="G16" s="35">
         <v>0</v>
       </c>
-      <c r="H16" s="38">
+      <c r="H16" s="33">
         <v>0.86213332525640862</v>
       </c>
-      <c r="I16" s="41">
+      <c r="I16" s="36">
         <v>0.51727999515384515</v>
       </c>
-      <c r="J16" s="41">
+      <c r="J16" s="36">
         <v>173.63365170664068</v>
       </c>
-      <c r="K16" s="42">
+      <c r="K16" s="37">
         <v>13.966559869153819</v>
       </c>
-      <c r="L16" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="M16" s="48" t="s">
-        <v>8</v>
-      </c>
-      <c r="N16" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="O16" s="41">
+      <c r="L16" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="36">
         <v>0</v>
       </c>
-      <c r="P16" s="42">
+      <c r="P16" s="37">
         <v>0</v>
       </c>
-      <c r="Q16" s="1"/>
     </row>
-    <row r="17" spans="2:23" s="18" customFormat="1">
-      <c r="B17" s="26"/>
-      <c r="C17" s="22" t="s">
+    <row r="17" spans="2:16" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="21"/>
+      <c r="C17" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="56">
+      <c r="D17" s="51">
         <v>86.97332109200002</v>
       </c>
-      <c r="E17" s="44">
+      <c r="E17" s="39">
         <v>3.1273958104035091</v>
       </c>
-      <c r="F17" s="44">
+      <c r="F17" s="39">
         <v>2.2995557429437565E-2</v>
       </c>
-      <c r="G17" s="44">
+      <c r="G17" s="39">
         <v>0.14947112329134418</v>
       </c>
-      <c r="H17" s="44">
+      <c r="H17" s="39">
         <v>1.7246668072078175</v>
       </c>
-      <c r="I17" s="44">
+      <c r="I17" s="39">
         <v>0.689866722883127</v>
       </c>
-      <c r="J17" s="44">
+      <c r="J17" s="39">
         <v>137.97334457662541</v>
       </c>
-      <c r="K17" s="44">
+      <c r="K17" s="39">
         <v>1.7246668072078175</v>
       </c>
-      <c r="L17" s="44" t="s">
-        <v>8</v>
-      </c>
-      <c r="M17" s="44" t="s">
-        <v>8</v>
-      </c>
-      <c r="N17" s="44" t="s">
-        <v>8</v>
-      </c>
-      <c r="O17" s="44">
+      <c r="L17" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="39">
         <v>0.22995557429437566</v>
       </c>
-      <c r="P17" s="44">
+      <c r="P17" s="39">
         <v>0.3449333614415635</v>
       </c>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="17"/>
-      <c r="S17" s="17"/>
-      <c r="T17" s="17"/>
-      <c r="U17" s="17"/>
-      <c r="V17" s="17"/>
-      <c r="W17" s="17"/>
     </row>
-    <row r="19" spans="2:23" hidden="1">
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
+    <row r="19" spans="2:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
     </row>
-    <row r="20" spans="2:23" hidden="1">
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
+    <row r="20" spans="2:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
     </row>
-    <row r="21" spans="2:23" hidden="1">
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
+    <row r="21" spans="2:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
     </row>
-    <row r="22" spans="2:23" hidden="1"/>
+    <row r="22" spans="2:16" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="B4:B7"/>
@@ -2082,6 +2018,26 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F16">
+    <cfRule type="colorScale" priority="111">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="110">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="109">
       <colorScale>
         <cfvo type="min"/>
@@ -2092,28 +2048,28 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="110">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="111">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G16">
+    <cfRule type="colorScale" priority="114">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="113">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="112">
       <colorScale>
         <cfvo type="min"/>
@@ -2124,28 +2080,28 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="113">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="114">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H16">
+    <cfRule type="colorScale" priority="117">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="116">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="115">
       <colorScale>
         <cfvo type="min"/>
@@ -2156,26 +2112,6 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="116">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="117">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:I16">
     <cfRule type="colorScale" priority="118">
@@ -2432,46 +2368,6 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N7:N16">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="formula" val="MAX(#REF!)/2"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2482,50 +2378,40 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="19">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="MAX(#REF!)/2"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="formula" val="MAX(#REF!)/2"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="23">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
@@ -2540,6 +2426,56 @@
         <color rgb="FF63BE7B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="MAX(#REF!)/2"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="MAX(#REF!)/2"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>

--- a/data/Heat map 3.xlsx
+++ b/data/Heat map 3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{240C0ABD-DD08-429B-B166-D979D8ECE3B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C4D2029-8E53-4738-86CE-07E1C790DDC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{45B3C54E-DB58-4340-A914-7AEE103F004F}"/>
   </bookViews>
@@ -63,9 +63,6 @@
     <t>Annual rate of genetic gain, by crop (%)</t>
   </si>
   <si>
-    <t>GI</t>
-  </si>
-  <si>
     <t>Biotech</t>
   </si>
   <si>
@@ -81,9 +78,6 @@
     <t>Seed System</t>
   </si>
   <si>
-    <t>RAFS</t>
-  </si>
-  <si>
     <t>Plant Health</t>
   </si>
   <si>
@@ -93,9 +87,6 @@
     <t>Mechanization</t>
   </si>
   <si>
-    <t>ST</t>
-  </si>
-  <si>
     <t>per Program Target (target/13)</t>
   </si>
   <si>
@@ -147,7 +138,16 @@
     <t>Value Chain Markets and Agribusiness</t>
   </si>
   <si>
-    <t>USD</t>
+    <t>Genetic Innovation</t>
+  </si>
+  <si>
+    <t>Resilient Agrifood Systems</t>
+  </si>
+  <si>
+    <t>Systems Transformation</t>
+  </si>
+  <si>
+    <t>USD (million)</t>
   </si>
 </sst>
 </file>
@@ -251,7 +251,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -572,15 +572,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -659,7 +650,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -776,8 +767,8 @@
     <xf numFmtId="166" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -792,9 +783,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1262,72 +1250,72 @@
   <sheetData>
     <row r="1" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="2"/>
-      <c r="C1" s="55" t="s">
+      <c r="C1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="57"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
+      <c r="P1" s="56"/>
     </row>
     <row r="2" spans="2:16" s="1" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="19"/>
       <c r="C2" s="20"/>
       <c r="D2" s="40"/>
-      <c r="E2" s="58" t="s">
+      <c r="E2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="59"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="61" t="s">
+      <c r="F2" s="58"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="63"/>
-      <c r="L2" s="61" t="s">
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="62"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="63"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="62"/>
     </row>
     <row r="3" spans="2:16" s="9" customFormat="1" ht="143.55000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="18"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="J3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="K3" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="L3" s="4" t="s">
         <v>4</v>
@@ -1336,23 +1324,23 @@
         <v>5</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="2:16" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="45">
+      <c r="D4" s="44">
         <v>3.4135987800000001</v>
       </c>
       <c r="E4" s="23">
@@ -1377,13 +1365,13 @@
         <v>53.902058167480362</v>
       </c>
       <c r="L4" s="23" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M4" s="41" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N4" s="26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O4" s="26">
         <v>0.2929459683015237</v>
@@ -1393,11 +1381,11 @@
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="53"/>
+      <c r="B5" s="52"/>
       <c r="C5" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="46">
+        <v>8</v>
+      </c>
+      <c r="D5" s="45">
         <v>12.720419820000002</v>
       </c>
       <c r="E5" s="28">
@@ -1425,10 +1413,10 @@
         <v>1.18</v>
       </c>
       <c r="M5" s="42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N5" s="31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O5" s="31">
         <v>0.62891006061150567</v>
@@ -1438,11 +1426,11 @@
       </c>
     </row>
     <row r="6" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="53"/>
+      <c r="B6" s="52"/>
       <c r="C6" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="46">
+        <v>9</v>
+      </c>
+      <c r="D6" s="45">
         <v>3.5036499999999999</v>
       </c>
       <c r="E6" s="28">
@@ -1467,10 +1455,10 @@
         <v>32.252079973741665</v>
       </c>
       <c r="L6" s="28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M6" s="42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N6" s="31">
         <f>'[1]PR 10'!$H$5</f>
@@ -1484,11 +1472,11 @@
       </c>
     </row>
     <row r="7" spans="2:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="54"/>
+      <c r="B7" s="53"/>
       <c r="C7" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="47">
+        <v>10</v>
+      </c>
+      <c r="D7" s="46">
         <v>21.304912170000001</v>
       </c>
       <c r="E7" s="33">
@@ -1513,13 +1501,13 @@
         <v>14.50369743533188</v>
       </c>
       <c r="L7" s="33" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M7" s="43" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N7" s="36" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O7" s="36">
         <v>0.79793804660401935</v>
@@ -1529,13 +1517,13 @@
       </c>
     </row>
     <row r="8" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="52" t="s">
-        <v>12</v>
+      <c r="B8" s="51" t="s">
+        <v>32</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="45">
+        <v>11</v>
+      </c>
+      <c r="D8" s="44">
         <v>7.721148311538462</v>
       </c>
       <c r="E8" s="23">
@@ -1560,13 +1548,13 @@
         <v>1.2951441413262363</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M8" s="41" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N8" s="26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O8" s="26">
         <v>0.77708648479574172</v>
@@ -1576,11 +1564,11 @@
       </c>
     </row>
     <row r="9" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="53"/>
+      <c r="B9" s="52"/>
       <c r="C9" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="46">
+        <v>12</v>
+      </c>
+      <c r="D9" s="45">
         <v>12.273168915897436</v>
       </c>
       <c r="E9" s="28">
@@ -1605,13 +1593,13 @@
         <v>18.984502013835652</v>
       </c>
       <c r="L9" s="28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M9" s="42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N9" s="31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O9" s="31">
         <v>8.147854941560366E-2</v>
@@ -1621,11 +1609,11 @@
       </c>
     </row>
     <row r="10" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="53"/>
+      <c r="B10" s="52"/>
       <c r="C10" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="46">
+        <v>25</v>
+      </c>
+      <c r="D10" s="45">
         <v>7.1819852465641034</v>
       </c>
       <c r="E10" s="28">
@@ -1650,13 +1638,13 @@
         <v>2.7847453473352788</v>
       </c>
       <c r="L10" s="28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M10" s="42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N10" s="31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O10" s="31">
         <v>1.3923726736676394</v>
@@ -1666,11 +1654,11 @@
       </c>
     </row>
     <row r="11" spans="2:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="54"/>
+      <c r="B11" s="53"/>
       <c r="C11" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="47">
+        <v>13</v>
+      </c>
+      <c r="D11" s="46">
         <v>0.57107699999999995</v>
       </c>
       <c r="E11" s="33">
@@ -1695,13 +1683,13 @@
         <v>0</v>
       </c>
       <c r="L11" s="33" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M11" s="43" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N11" s="36" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O11" s="36">
         <v>5.2532320510193893</v>
@@ -1711,13 +1699,13 @@
       </c>
     </row>
     <row r="12" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="52" t="s">
-        <v>16</v>
+      <c r="B12" s="51" t="s">
+        <v>33</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="48">
+        <v>26</v>
+      </c>
+      <c r="D12" s="47">
         <v>1.3649733500000001</v>
       </c>
       <c r="E12" s="23">
@@ -1742,13 +1730,13 @@
         <v>79.855038928049396</v>
       </c>
       <c r="L12" s="38" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M12" s="41" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N12" s="26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O12" s="26">
         <v>0</v>
@@ -1758,11 +1746,11 @@
       </c>
     </row>
     <row r="13" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="53"/>
+      <c r="B13" s="52"/>
       <c r="C13" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="49">
+        <v>27</v>
+      </c>
+      <c r="D13" s="48">
         <v>7.5363555180000006</v>
       </c>
       <c r="E13" s="28">
@@ -1787,13 +1775,13 @@
         <v>20.699660416418268</v>
       </c>
       <c r="L13" s="28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M13" s="42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N13" s="31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O13" s="31">
         <v>0.33172532718619019</v>
@@ -1803,11 +1791,11 @@
       </c>
     </row>
     <row r="14" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="53"/>
+      <c r="B14" s="52"/>
       <c r="C14" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="49">
+        <v>28</v>
+      </c>
+      <c r="D14" s="48">
         <v>2.1255060000000001</v>
       </c>
       <c r="E14" s="28">
@@ -1832,13 +1820,13 @@
         <v>0</v>
       </c>
       <c r="L14" s="28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M14" s="42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N14" s="31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O14" s="31">
         <v>1.1761905165170081</v>
@@ -1848,11 +1836,11 @@
       </c>
     </row>
     <row r="15" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="53"/>
+      <c r="B15" s="52"/>
       <c r="C15" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="49">
+        <v>29</v>
+      </c>
+      <c r="D15" s="48">
         <v>1.4569589599999999</v>
       </c>
       <c r="E15" s="28">
@@ -1877,13 +1865,13 @@
         <v>10.295416969054504</v>
       </c>
       <c r="L15" s="28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M15" s="42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N15" s="31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O15" s="31">
         <v>0</v>
@@ -1893,11 +1881,11 @@
       </c>
     </row>
     <row r="16" spans="2:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="54"/>
+      <c r="B16" s="53"/>
       <c r="C16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="50">
+        <v>30</v>
+      </c>
+      <c r="D16" s="49">
         <v>5.7995670199999996</v>
       </c>
       <c r="E16" s="33">
@@ -1922,13 +1910,13 @@
         <v>13.966559869153819</v>
       </c>
       <c r="L16" s="33" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M16" s="43" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N16" s="36" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O16" s="36">
         <v>0</v>
@@ -1940,9 +1928,9 @@
     <row r="17" spans="2:16" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B17" s="21"/>
       <c r="C17" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="51">
+        <v>14</v>
+      </c>
+      <c r="D17" s="50">
         <v>86.97332109200002</v>
       </c>
       <c r="E17" s="39">
@@ -1967,13 +1955,13 @@
         <v>1.7246668072078175</v>
       </c>
       <c r="L17" s="39" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M17" s="39" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N17" s="39" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O17" s="39">
         <v>0.22995557429437566</v>

--- a/data/Heat map 3.xlsx
+++ b/data/Heat map 3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C4D2029-8E53-4738-86CE-07E1C790DDC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702F4278-B797-4B6C-9590-2B301637BEFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{45B3C54E-DB58-4340-A914-7AEE103F004F}"/>
   </bookViews>
@@ -160,7 +160,7 @@
     <numFmt numFmtId="166" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1236,7 +1236,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:P22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="3.21875" style="22" customWidth="1"/>
     <col min="3" max="3" width="37.109375" style="8" customWidth="1"/>
@@ -1248,7 +1248,7 @@
     <col min="14" max="16" width="6.77734375" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:16" ht="15" thickBot="1">
       <c r="B1" s="2"/>
       <c r="C1" s="54" t="s">
         <v>0</v>
@@ -1267,7 +1267,7 @@
       <c r="O1" s="55"/>
       <c r="P1" s="56"/>
     </row>
-    <row r="2" spans="2:16" s="1" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:16" s="1" customFormat="1" ht="18.600000000000001" thickBot="1">
       <c r="B2" s="19"/>
       <c r="C2" s="20"/>
       <c r="D2" s="40"/>
@@ -1290,7 +1290,7 @@
       <c r="O2" s="61"/>
       <c r="P2" s="62"/>
     </row>
-    <row r="3" spans="2:16" s="9" customFormat="1" ht="143.55000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:16" s="9" customFormat="1" ht="143.55000000000001" customHeight="1" thickBot="1">
       <c r="B3" s="18"/>
       <c r="C3" s="3"/>
       <c r="D3" s="4" t="s">
@@ -1333,7 +1333,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:16" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:16" ht="15.45" customHeight="1">
       <c r="B4" s="51" t="s">
         <v>31</v>
       </c>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:16" ht="15.6" customHeight="1">
       <c r="B5" s="52"/>
       <c r="C5" s="11" t="s">
         <v>8</v>
@@ -1425,7 +1425,7 @@
         <v>0.39306878788219107</v>
       </c>
     </row>
-    <row r="6" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:16" ht="15.6" customHeight="1">
       <c r="B6" s="52"/>
       <c r="C6" s="11" t="s">
         <v>9</v>
@@ -1471,7 +1471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:16" ht="15.6" customHeight="1" thickBot="1">
       <c r="B7" s="53"/>
       <c r="C7" s="12" t="s">
         <v>10</v>
@@ -1516,7 +1516,7 @@
         <v>9.3875064306355213E-2</v>
       </c>
     </row>
-    <row r="8" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:16" ht="15.6" customHeight="1">
       <c r="B8" s="51" t="s">
         <v>32</v>
       </c>
@@ -1563,7 +1563,7 @@
         <v>0.25902882826524726</v>
       </c>
     </row>
-    <row r="9" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16" ht="15.6" customHeight="1">
       <c r="B9" s="52"/>
       <c r="C9" s="11" t="s">
         <v>12</v>
@@ -1608,7 +1608,7 @@
         <v>0.7333069447404329</v>
       </c>
     </row>
-    <row r="10" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:16" ht="15.6" customHeight="1">
       <c r="B10" s="52"/>
       <c r="C10" s="11" t="s">
         <v>25</v>
@@ -1653,7 +1653,7 @@
         <v>0.27847453473352785</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:16" ht="15.6" customHeight="1" thickBot="1">
       <c r="B11" s="53"/>
       <c r="C11" s="12" t="s">
         <v>13</v>
@@ -1698,7 +1698,7 @@
         <v>5.2532320510193893</v>
       </c>
     </row>
-    <row r="12" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:16" ht="15.6" customHeight="1">
       <c r="B12" s="51" t="s">
         <v>33</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:16" ht="15.6" customHeight="1">
       <c r="B13" s="52"/>
       <c r="C13" s="11" t="s">
         <v>27</v>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:16" ht="15.6" customHeight="1">
       <c r="B14" s="52"/>
       <c r="C14" s="11" t="s">
         <v>28</v>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:16" ht="15.6" customHeight="1">
       <c r="B15" s="52"/>
       <c r="C15" s="11" t="s">
         <v>29</v>
@@ -1880,7 +1880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:16" ht="15.6" customHeight="1" thickBot="1">
       <c r="B16" s="53"/>
       <c r="C16" s="12" t="s">
         <v>30</v>
@@ -1925,7 +1925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:16" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:16" s="13" customFormat="1">
       <c r="B17" s="21"/>
       <c r="C17" s="17" t="s">
         <v>14</v>
@@ -1970,19 +1970,19 @@
         <v>0.3449333614415635</v>
       </c>
     </row>
-    <row r="19" spans="2:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:16" hidden="1">
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
     </row>
-    <row r="20" spans="2:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:16" hidden="1">
       <c r="C20" s="15"/>
       <c r="D20" s="15"/>
     </row>
-    <row r="21" spans="2:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:16" hidden="1">
       <c r="C21" s="16"/>
       <c r="D21" s="16"/>
     </row>
-    <row r="22" spans="2:16" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="2:16" hidden="1"/>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="B4:B7"/>

--- a/data/Heat map 3.xlsx
+++ b/data/Heat map 3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702F4278-B797-4B6C-9590-2B301637BEFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42E6BD61-7D11-4229-BCCC-10050A18A44D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{45B3C54E-DB58-4340-A914-7AEE103F004F}"/>
+    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="9960" xr2:uid="{45B3C54E-DB58-4340-A914-7AEE103F004F}"/>
   </bookViews>
   <sheets>
     <sheet name="Res, Cap, Product" sheetId="1" r:id="rId1"/>
@@ -160,7 +160,7 @@
     <numFmt numFmtId="166" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1236,7 +1236,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:P22"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="3.21875" style="22" customWidth="1"/>
     <col min="3" max="3" width="37.109375" style="8" customWidth="1"/>
@@ -1248,7 +1248,7 @@
     <col min="14" max="16" width="6.77734375" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="15" thickBot="1">
+    <row r="1" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="2"/>
       <c r="C1" s="54" t="s">
         <v>0</v>
@@ -1267,7 +1267,7 @@
       <c r="O1" s="55"/>
       <c r="P1" s="56"/>
     </row>
-    <row r="2" spans="2:16" s="1" customFormat="1" ht="18.600000000000001" thickBot="1">
+    <row r="2" spans="2:16" s="1" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="19"/>
       <c r="C2" s="20"/>
       <c r="D2" s="40"/>
@@ -1290,7 +1290,7 @@
       <c r="O2" s="61"/>
       <c r="P2" s="62"/>
     </row>
-    <row r="3" spans="2:16" s="9" customFormat="1" ht="143.55000000000001" customHeight="1" thickBot="1">
+    <row r="3" spans="2:16" s="9" customFormat="1" ht="143.55000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="18"/>
       <c r="C3" s="3"/>
       <c r="D3" s="4" t="s">
@@ -1333,7 +1333,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:16" ht="15.45" customHeight="1">
+    <row r="4" spans="2:16" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="51" t="s">
         <v>31</v>
       </c>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:16" ht="15.6" customHeight="1">
+    <row r="5" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="52"/>
       <c r="C5" s="11" t="s">
         <v>8</v>
@@ -1425,7 +1425,7 @@
         <v>0.39306878788219107</v>
       </c>
     </row>
-    <row r="6" spans="2:16" ht="15.6" customHeight="1">
+    <row r="6" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="52"/>
       <c r="C6" s="11" t="s">
         <v>9</v>
@@ -1471,7 +1471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="15.6" customHeight="1" thickBot="1">
+    <row r="7" spans="2:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="53"/>
       <c r="C7" s="12" t="s">
         <v>10</v>
@@ -1516,7 +1516,7 @@
         <v>9.3875064306355213E-2</v>
       </c>
     </row>
-    <row r="8" spans="2:16" ht="15.6" customHeight="1">
+    <row r="8" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="51" t="s">
         <v>32</v>
       </c>
@@ -1563,7 +1563,7 @@
         <v>0.25902882826524726</v>
       </c>
     </row>
-    <row r="9" spans="2:16" ht="15.6" customHeight="1">
+    <row r="9" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="52"/>
       <c r="C9" s="11" t="s">
         <v>12</v>
@@ -1608,7 +1608,7 @@
         <v>0.7333069447404329</v>
       </c>
     </row>
-    <row r="10" spans="2:16" ht="15.6" customHeight="1">
+    <row r="10" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="52"/>
       <c r="C10" s="11" t="s">
         <v>25</v>
@@ -1653,7 +1653,7 @@
         <v>0.27847453473352785</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="15.6" customHeight="1" thickBot="1">
+    <row r="11" spans="2:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="53"/>
       <c r="C11" s="12" t="s">
         <v>13</v>
@@ -1698,7 +1698,7 @@
         <v>5.2532320510193893</v>
       </c>
     </row>
-    <row r="12" spans="2:16" ht="15.6" customHeight="1">
+    <row r="12" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="51" t="s">
         <v>33</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:16" ht="15.6" customHeight="1">
+    <row r="13" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="52"/>
       <c r="C13" s="11" t="s">
         <v>27</v>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:16" ht="15.6" customHeight="1">
+    <row r="14" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="52"/>
       <c r="C14" s="11" t="s">
         <v>28</v>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:16" ht="15.6" customHeight="1">
+    <row r="15" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="52"/>
       <c r="C15" s="11" t="s">
         <v>29</v>
@@ -1880,7 +1880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:16" ht="15.6" customHeight="1" thickBot="1">
+    <row r="16" spans="2:16" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="53"/>
       <c r="C16" s="12" t="s">
         <v>30</v>
@@ -1925,7 +1925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:16" s="13" customFormat="1">
+    <row r="17" spans="2:16" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B17" s="21"/>
       <c r="C17" s="17" t="s">
         <v>14</v>
@@ -1970,19 +1970,19 @@
         <v>0.3449333614415635</v>
       </c>
     </row>
-    <row r="19" spans="2:16" hidden="1">
+    <row r="19" spans="2:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
     </row>
-    <row r="20" spans="2:16" hidden="1">
+    <row r="20" spans="2:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="C20" s="15"/>
       <c r="D20" s="15"/>
     </row>
-    <row r="21" spans="2:16" hidden="1">
+    <row r="21" spans="2:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="C21" s="16"/>
       <c r="D21" s="16"/>
     </row>
-    <row r="22" spans="2:16" hidden="1"/>
+    <row r="22" spans="2:16" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="B4:B7"/>

--- a/data/Heat map 3.xlsx
+++ b/data/Heat map 3.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68CECEC4-8248-407C-AA5F-3C4824E51D87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED46C07-14CD-4828-98D6-D162F69AA74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{45B3C54E-DB58-4340-A914-7AEE103F004F}"/>
   </bookViews>
   <sheets>
     <sheet name="Res, Cap, Product" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_Hlk200085589" localSheetId="0">'Res, Cap, Product'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Res, Cap, Product'!$A$1:$O$17</definedName>
@@ -43,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="36">
   <si>
     <t>KPI by $</t>
   </si>
@@ -148,6 +145,9 @@
   </si>
   <si>
     <t>Biotechnology</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
 </sst>
 </file>
@@ -157,7 +157,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -257,7 +257,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="35">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -698,6 +698,26 @@
       <top/>
       <bottom style="medium">
         <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color theme="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -707,11 +727,8 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" readingOrder="1"/>
@@ -737,10 +754,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -748,20 +761,96 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -772,111 +861,38 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="3" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -895,79 +911,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="PR 1"/>
-      <sheetName val="PR 2"/>
-      <sheetName val="PR 3"/>
-      <sheetName val="PR 4"/>
-      <sheetName val="PR 5"/>
-      <sheetName val="PR 6"/>
-      <sheetName val="PR 7"/>
-      <sheetName val="PR 8"/>
-      <sheetName val="PR 9"/>
-      <sheetName val="PR 10"/>
-      <sheetName val="PR 11"/>
-      <sheetName val="PR 12"/>
-      <sheetName val="PR 13"/>
-      <sheetName val="PR 14"/>
-      <sheetName val="PR15"/>
-      <sheetName val="PR 16"/>
-      <sheetName val="PR 18"/>
-      <sheetName val="PR 19"/>
-      <sheetName val="PR20"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7">
-        <row r="4">
-          <cell r="G4">
-            <v>0.65217391304347827</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="8">
-        <row r="4">
-          <cell r="G4">
-            <v>6.521739130434782E-4</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="9">
-        <row r="5">
-          <cell r="G5">
-            <v>0.25</v>
-          </cell>
-          <cell r="H5">
-            <v>0.28541663693576702</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1294,758 +1237,757 @@
   <dimension ref="A1:O22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8" style="15" customWidth="1"/>
-    <col min="2" max="2" width="37.109375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="5.77734375" style="4" customWidth="1"/>
-    <col min="4" max="8" width="6.77734375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="11.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="6.77734375" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8.33203125" style="4" customWidth="1"/>
-    <col min="13" max="15" width="6.77734375" style="4" customWidth="1"/>
+    <col min="1" max="1" width="8" style="12" customWidth="1"/>
+    <col min="2" max="2" width="37.109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="5.77734375" style="3" customWidth="1"/>
+    <col min="4" max="8" width="6.77734375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="6.77734375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="8.33203125" style="3" customWidth="1"/>
+    <col min="13" max="15" width="6.77734375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2"/>
-      <c r="B1" s="23" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="25"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="48"/>
     </row>
-    <row r="2" spans="1:15" s="1" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="14"/>
-      <c r="B2" s="35" t="s">
+    <row r="2" spans="1:15" s="57" customFormat="1" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="58"/>
+      <c r="B2" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="37" t="s">
+      <c r="C2" s="50"/>
+      <c r="D2" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="38"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="40" t="s">
+      <c r="E2" s="52"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="40" t="s">
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="42"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="56"/>
     </row>
-    <row r="3" spans="1:15" s="5" customFormat="1" ht="143.55000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="13"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="31" t="s">
+    <row r="3" spans="1:15" s="4" customFormat="1" ht="143.55000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="59"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="F3" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="32" t="s">
+      <c r="I3" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="33" t="s">
+      <c r="J3" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="31" t="s">
+      <c r="K3" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="34" t="s">
+      <c r="L3" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="34" t="s">
+      <c r="M3" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="32" t="s">
+      <c r="N3" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="33" t="s">
+      <c r="O3" s="22" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="26" t="s">
+    <row r="4" spans="1:15" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="15">
         <v>3.4135987800000001</v>
       </c>
-      <c r="D4" s="43">
+      <c r="D4" s="24">
         <v>6.4448113026335205</v>
       </c>
-      <c r="E4" s="44">
+      <c r="E4" s="25">
         <v>0.9185948577454921</v>
       </c>
-      <c r="F4" s="45">
+      <c r="F4" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="24">
         <v>0.2929459683015237</v>
       </c>
-      <c r="G4" s="43">
+      <c r="H4" s="30">
         <v>0.2929459683015237</v>
       </c>
-      <c r="H4" s="51">
+      <c r="I4" s="30">
+        <v>19.920325844503608</v>
+      </c>
+      <c r="J4" s="31">
+        <v>53.902058167480362</v>
+      </c>
+      <c r="K4" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="N4" s="30">
         <v>0.2929459683015237</v>
       </c>
-      <c r="I4" s="51">
-        <v>19.920325844503608</v>
-      </c>
-      <c r="J4" s="52">
-        <v>53.902058167480362</v>
-      </c>
-      <c r="K4" s="43">
+      <c r="O4" s="31">
         <v>0</v>
       </c>
-      <c r="L4" s="51">
+    </row>
+    <row r="5" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="44"/>
+      <c r="B5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="16">
+        <v>12.720419820000002</v>
+      </c>
+      <c r="D5" s="26">
+        <v>4.0486085151865678</v>
+      </c>
+      <c r="E5" s="13">
+        <v>0.17585555770903244</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="26">
+        <v>1.8867301818345172</v>
+      </c>
+      <c r="H5" s="14">
+        <v>2.20118521214027</v>
+      </c>
+      <c r="I5" s="14">
+        <v>8.4902858182553285</v>
+      </c>
+      <c r="J5" s="32">
+        <v>16.823344121357778</v>
+      </c>
+      <c r="K5" s="26">
+        <v>1.18</v>
+      </c>
+      <c r="L5" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="M5" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5" s="14">
+        <v>0.62891006061150567</v>
+      </c>
+      <c r="O5" s="32">
+        <v>0.39306878788219107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="44"/>
+      <c r="B6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="16">
+        <v>3.5036499999999999</v>
+      </c>
+      <c r="D6" s="26">
+        <v>1.427083184678835</v>
+      </c>
+      <c r="E6" s="13">
+        <v>0.35677079616970875</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="26">
+        <v>7.4208325603299423</v>
+      </c>
+      <c r="H6" s="14">
+        <v>5.4229161017795731</v>
+      </c>
+      <c r="I6" s="14">
+        <v>1.427083184678835</v>
+      </c>
+      <c r="J6" s="32">
+        <v>32.252079973741665</v>
+      </c>
+      <c r="K6" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="N6" s="14">
         <v>0</v>
       </c>
-      <c r="M4" s="51">
-        <v>0</v>
-      </c>
-      <c r="N4" s="51">
-        <v>0.2929459683015237</v>
-      </c>
-      <c r="O4" s="52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="27"/>
-      <c r="B5" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="19">
-        <v>12.720419820000002</v>
-      </c>
-      <c r="D5" s="46">
-        <v>4.0486085151865678</v>
-      </c>
-      <c r="E5" s="16">
-        <v>0.17585555770903244</v>
-      </c>
-      <c r="F5" s="47">
-        <v>0</v>
-      </c>
-      <c r="G5" s="46">
-        <v>1.8867301818345172</v>
-      </c>
-      <c r="H5" s="17">
-        <v>2.20118521214027</v>
-      </c>
-      <c r="I5" s="17">
-        <v>8.4902858182553285</v>
-      </c>
-      <c r="J5" s="53">
-        <v>16.823344121357778</v>
-      </c>
-      <c r="K5" s="46">
-        <v>1.18</v>
-      </c>
-      <c r="L5" s="17">
-        <v>0</v>
-      </c>
-      <c r="M5" s="17">
-        <v>0</v>
-      </c>
-      <c r="N5" s="17">
-        <v>0.62891006061150567</v>
-      </c>
-      <c r="O5" s="53">
-        <v>0.39306878788219107</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="27"/>
-      <c r="B6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="19">
-        <v>3.5036499999999999</v>
-      </c>
-      <c r="D6" s="46">
-        <v>1.427083184678835</v>
-      </c>
-      <c r="E6" s="16">
-        <v>0.35677079616970875</v>
-      </c>
-      <c r="F6" s="47">
-        <v>0</v>
-      </c>
-      <c r="G6" s="46">
-        <v>7.4208325603299423</v>
-      </c>
-      <c r="H6" s="17">
-        <v>5.4229161017795731</v>
-      </c>
-      <c r="I6" s="17">
-        <v>1.427083184678835</v>
-      </c>
-      <c r="J6" s="53">
-        <v>32.252079973741665</v>
-      </c>
-      <c r="K6" s="46">
-        <v>0</v>
-      </c>
-      <c r="L6" s="17">
-        <v>0</v>
-      </c>
-      <c r="M6" s="17">
-        <f>'[1]PR 10'!$H$5</f>
-        <v>0.28541663693576702</v>
-      </c>
-      <c r="N6" s="17">
-        <v>0</v>
-      </c>
-      <c r="O6" s="53">
+      <c r="O6" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="28"/>
-      <c r="B7" s="8" t="s">
+      <c r="A7" s="45"/>
+      <c r="B7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="17">
         <v>21.304912170000001</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="26">
         <v>0.72283799515893521</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="13">
         <v>4.8189199677262338E-2</v>
       </c>
-      <c r="F7" s="47">
-        <v>0</v>
-      </c>
-      <c r="G7" s="46">
+      <c r="F7" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="26">
         <v>0.23468766076588804</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="14">
         <v>0.32856272507224321</v>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="14">
         <v>105.46863474819008</v>
       </c>
-      <c r="J7" s="53">
+      <c r="J7" s="32">
         <v>14.50369743533188</v>
       </c>
-      <c r="K7" s="46">
-        <v>0</v>
-      </c>
-      <c r="L7" s="17">
-        <v>0</v>
-      </c>
-      <c r="M7" s="17">
-        <v>0</v>
-      </c>
-      <c r="N7" s="17">
+      <c r="K7" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="N7" s="14">
         <v>0.79793804660401935</v>
       </c>
-      <c r="O7" s="53">
+      <c r="O7" s="32">
         <v>9.3875064306355213E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="26" t="s">
+    <row r="8" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="15">
         <v>7.721148311538462</v>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="26">
         <v>5.3683724657972496</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="13">
         <v>0.44736437214977082</v>
       </c>
-      <c r="F8" s="47">
-        <v>0.12951441413262363</v>
-      </c>
-      <c r="G8" s="46">
+      <c r="F8" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="26">
         <v>1.1656297271936127</v>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="14">
         <v>1.1656297271936127</v>
       </c>
-      <c r="I8" s="17">
+      <c r="I8" s="14">
         <v>13.210470241527611</v>
       </c>
-      <c r="J8" s="53">
+      <c r="J8" s="32">
         <v>1.2951441413262363</v>
       </c>
-      <c r="K8" s="46">
-        <v>0</v>
-      </c>
-      <c r="L8" s="17">
-        <v>0</v>
-      </c>
-      <c r="M8" s="17">
-        <v>0</v>
-      </c>
-      <c r="N8" s="17">
+      <c r="K8" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="L8" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="M8" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="N8" s="14">
         <v>0.77708648479574172</v>
       </c>
-      <c r="O8" s="53">
+      <c r="O8" s="32">
         <v>0.25902882826524726</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27"/>
-      <c r="B9" s="7" t="s">
+    <row r="9" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="44"/>
+      <c r="B9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="16">
         <v>12.273168915897436</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="26">
         <v>1.7004573263036482</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="13">
         <v>8.5022866315182424E-2</v>
       </c>
-      <c r="F9" s="47">
-        <v>6.7627196014951027E-2</v>
-      </c>
-      <c r="G9" s="46">
+      <c r="F9" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="26">
         <v>1.7925280871432805</v>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="14">
         <v>1.1406996918184511</v>
       </c>
-      <c r="I9" s="17">
+      <c r="I9" s="14">
         <v>259.50917988869764</v>
       </c>
-      <c r="J9" s="53">
+      <c r="J9" s="32">
         <v>18.984502013835652</v>
       </c>
-      <c r="K9" s="46">
-        <v>0</v>
-      </c>
-      <c r="L9" s="17">
-        <v>0</v>
-      </c>
-      <c r="M9" s="17">
-        <v>0</v>
-      </c>
-      <c r="N9" s="17">
+      <c r="K9" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="L9" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="M9" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="N9" s="14">
         <v>8.147854941560366E-2</v>
       </c>
-      <c r="O9" s="53">
+      <c r="O9" s="32">
         <v>0.7333069447404329</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="27"/>
-      <c r="B10" s="7" t="s">
+    <row r="10" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="44"/>
+      <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="16">
         <v>7.1819852465641034</v>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="26">
         <v>2.1581776441848408</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="13">
         <v>0.30831109202640583</v>
       </c>
-      <c r="F10" s="47">
-        <v>0.27847453473352785</v>
-      </c>
-      <c r="G10" s="46">
+      <c r="F10" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="26">
         <v>0.97466087156734749</v>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="14">
         <v>0.4177118021002918</v>
       </c>
-      <c r="I10" s="17">
+      <c r="I10" s="14">
         <v>522.69670169483186</v>
       </c>
-      <c r="J10" s="53">
+      <c r="J10" s="32">
         <v>2.7847453473352788</v>
       </c>
-      <c r="K10" s="46">
-        <v>0</v>
-      </c>
-      <c r="L10" s="17">
-        <v>0</v>
-      </c>
-      <c r="M10" s="17">
-        <v>0</v>
-      </c>
-      <c r="N10" s="17">
+      <c r="K10" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="L10" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="M10" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="N10" s="14">
         <v>1.3923726736676394</v>
       </c>
-      <c r="O10" s="53">
+      <c r="O10" s="32">
         <v>0.27847453473352785</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="28"/>
-      <c r="B11" s="8" t="s">
+      <c r="A11" s="45"/>
+      <c r="B11" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="17">
         <v>0.57107699999999995</v>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="26">
         <v>0</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="13">
         <v>0</v>
       </c>
-      <c r="F11" s="47">
+      <c r="F11" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="26">
+        <v>3.5021547006795934</v>
+      </c>
+      <c r="H11" s="14">
+        <v>1.7510773503397967</v>
+      </c>
+      <c r="I11" s="14">
         <v>0</v>
       </c>
-      <c r="G11" s="46">
-        <v>3.5021547006795934</v>
-      </c>
-      <c r="H11" s="17">
-        <v>1.7510773503397967</v>
-      </c>
-      <c r="I11" s="17">
+      <c r="J11" s="32">
         <v>0</v>
       </c>
-      <c r="J11" s="53">
+      <c r="K11" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="M11" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="N11" s="14">
+        <v>5.2532320510193893</v>
+      </c>
+      <c r="O11" s="32">
+        <v>5.2532320510193893</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="18">
+        <v>1.3649733500000001</v>
+      </c>
+      <c r="D12" s="26">
+        <v>7.267541157488532</v>
+      </c>
+      <c r="E12" s="13">
+        <v>0.66068555977168475</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="26">
+        <v>3.6630751801857522</v>
+      </c>
+      <c r="H12" s="14">
+        <v>3.6630751801857522</v>
+      </c>
+      <c r="I12" s="14">
+        <v>68.865813387492139</v>
+      </c>
+      <c r="J12" s="32">
+        <v>79.855038928049396</v>
+      </c>
+      <c r="K12" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="L12" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="M12" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="N12" s="14">
         <v>0</v>
       </c>
-      <c r="K11" s="46">
+      <c r="O12" s="32">
         <v>0</v>
       </c>
-      <c r="L11" s="17">
+    </row>
+    <row r="13" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="44"/>
+      <c r="B13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="19">
+        <v>7.5363555180000006</v>
+      </c>
+      <c r="D13" s="26">
+        <v>0.8757548637715421</v>
+      </c>
+      <c r="E13" s="13">
+        <v>7.9614078524685647E-2</v>
+      </c>
+      <c r="F13" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="26">
+        <v>0.53076052349790426</v>
+      </c>
+      <c r="H13" s="14">
+        <v>0.39807039262342825</v>
+      </c>
+      <c r="I13" s="14">
+        <v>253.70353023199826</v>
+      </c>
+      <c r="J13" s="32">
+        <v>20.699660416418268</v>
+      </c>
+      <c r="K13" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="L13" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="M13" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="N13" s="14">
+        <v>0.33172532718619019</v>
+      </c>
+      <c r="O13" s="32">
         <v>0</v>
       </c>
-      <c r="M11" s="17">
+    </row>
+    <row r="14" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="44"/>
+      <c r="B14" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="19">
+        <v>2.1255060000000001</v>
+      </c>
+      <c r="D14" s="26">
+        <v>6.2714478340686881</v>
+      </c>
+      <c r="E14" s="13">
+        <v>1.2542895668137375</v>
+      </c>
+      <c r="F14" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="26">
+        <v>0.47047620660680323</v>
+      </c>
+      <c r="H14" s="14">
+        <v>0.94095241321360645</v>
+      </c>
+      <c r="I14" s="14">
         <v>0</v>
       </c>
-      <c r="N11" s="17">
-        <v>5.2532320510193893</v>
-      </c>
-      <c r="O11" s="53">
-        <v>5.2532320510193893</v>
+      <c r="J14" s="32">
+        <v>0</v>
+      </c>
+      <c r="K14" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="L14" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="M14" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="N14" s="14">
+        <v>1.1761905165170081</v>
+      </c>
+      <c r="O14" s="32">
+        <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="21">
-        <v>1.3649733500000001</v>
-      </c>
-      <c r="D12" s="46">
-        <v>7.267541157488532</v>
-      </c>
-      <c r="E12" s="16">
-        <v>0.66068555977168475</v>
-      </c>
-      <c r="F12" s="47">
+    <row r="15" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="44"/>
+      <c r="B15" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="19">
+        <v>1.4569589599999999</v>
+      </c>
+      <c r="D15" s="26">
+        <v>8.5795141408787519</v>
+      </c>
+      <c r="E15" s="13">
+        <v>2.144878535219688</v>
+      </c>
+      <c r="F15" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="26">
+        <v>1.3727222625406004</v>
+      </c>
+      <c r="H15" s="14">
+        <v>5.4908890501624015</v>
+      </c>
+      <c r="I15" s="14">
+        <v>89.226947065139029</v>
+      </c>
+      <c r="J15" s="32">
+        <v>10.295416969054504</v>
+      </c>
+      <c r="K15" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="L15" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="M15" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="N15" s="14">
         <v>0</v>
       </c>
-      <c r="G12" s="46">
-        <v>3.6630751801857522</v>
-      </c>
-      <c r="H12" s="17">
-        <v>3.6630751801857522</v>
-      </c>
-      <c r="I12" s="17">
-        <v>68.865813387492139</v>
-      </c>
-      <c r="J12" s="53">
-        <v>79.855038928049396</v>
-      </c>
-      <c r="K12" s="46">
-        <v>0</v>
-      </c>
-      <c r="L12" s="17">
-        <v>0</v>
-      </c>
-      <c r="M12" s="17">
-        <v>0</v>
-      </c>
-      <c r="N12" s="17">
-        <v>0</v>
-      </c>
-      <c r="O12" s="53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="27"/>
-      <c r="B13" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="22">
-        <v>7.5363555180000006</v>
-      </c>
-      <c r="D13" s="46">
-        <v>0.8757548637715421</v>
-      </c>
-      <c r="E13" s="16">
-        <v>7.9614078524685647E-2</v>
-      </c>
-      <c r="F13" s="47">
-        <v>0</v>
-      </c>
-      <c r="G13" s="46">
-        <v>0.53076052349790426</v>
-      </c>
-      <c r="H13" s="17">
-        <v>0.39807039262342825</v>
-      </c>
-      <c r="I13" s="17">
-        <v>253.70353023199826</v>
-      </c>
-      <c r="J13" s="53">
-        <v>20.699660416418268</v>
-      </c>
-      <c r="K13" s="46">
-        <v>0</v>
-      </c>
-      <c r="L13" s="17">
-        <v>0</v>
-      </c>
-      <c r="M13" s="17">
-        <v>0</v>
-      </c>
-      <c r="N13" s="17">
-        <v>0.33172532718619019</v>
-      </c>
-      <c r="O13" s="53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="27"/>
-      <c r="B14" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="22">
-        <v>2.1255060000000001</v>
-      </c>
-      <c r="D14" s="46">
-        <v>6.2714478340686881</v>
-      </c>
-      <c r="E14" s="16">
-        <v>1.2542895668137375</v>
-      </c>
-      <c r="F14" s="47">
-        <v>0.47047620660680323</v>
-      </c>
-      <c r="G14" s="46">
-        <v>0.47047620660680323</v>
-      </c>
-      <c r="H14" s="17">
-        <v>0.94095241321360645</v>
-      </c>
-      <c r="I14" s="17">
-        <v>0</v>
-      </c>
-      <c r="J14" s="53">
-        <v>0</v>
-      </c>
-      <c r="K14" s="46">
-        <v>0</v>
-      </c>
-      <c r="L14" s="17">
-        <v>0</v>
-      </c>
-      <c r="M14" s="17">
-        <v>0</v>
-      </c>
-      <c r="N14" s="17">
-        <v>1.1761905165170081</v>
-      </c>
-      <c r="O14" s="53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="27"/>
-      <c r="B15" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="22">
-        <v>1.4569589599999999</v>
-      </c>
-      <c r="D15" s="46">
-        <v>8.5795141408787519</v>
-      </c>
-      <c r="E15" s="16">
-        <v>2.144878535219688</v>
-      </c>
-      <c r="F15" s="47">
-        <v>0</v>
-      </c>
-      <c r="G15" s="46">
-        <v>1.3727222625406004</v>
-      </c>
-      <c r="H15" s="17">
-        <v>5.4908890501624015</v>
-      </c>
-      <c r="I15" s="17">
-        <v>89.226947065139029</v>
-      </c>
-      <c r="J15" s="53">
-        <v>10.295416969054504</v>
-      </c>
-      <c r="K15" s="46">
-        <v>0</v>
-      </c>
-      <c r="L15" s="17">
-        <v>0</v>
-      </c>
-      <c r="M15" s="17">
-        <v>0</v>
-      </c>
-      <c r="N15" s="17">
-        <v>0</v>
-      </c>
-      <c r="O15" s="53">
+      <c r="O15" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="28"/>
-      <c r="B16" s="56" t="s">
+      <c r="A16" s="45"/>
+      <c r="B16" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="57">
+      <c r="C16" s="36">
         <v>5.7995670199999996</v>
       </c>
-      <c r="D16" s="48">
+      <c r="D16" s="27">
         <v>0.51727999515384515</v>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="28">
         <v>5.1727999515384517E-2</v>
       </c>
-      <c r="F16" s="50">
+      <c r="F16" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="27">
+        <v>0.86213332525640862</v>
+      </c>
+      <c r="H16" s="33">
+        <v>0.51727999515384515</v>
+      </c>
+      <c r="I16" s="33">
+        <v>173.63365170664068</v>
+      </c>
+      <c r="J16" s="34">
+        <v>13.966559869153819</v>
+      </c>
+      <c r="K16" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="M16" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="N16" s="33">
         <v>0</v>
       </c>
-      <c r="G16" s="48">
-        <v>0.86213332525640862</v>
-      </c>
-      <c r="H16" s="54">
-        <v>0.51727999515384515</v>
-      </c>
-      <c r="I16" s="54">
-        <v>173.63365170664068</v>
-      </c>
-      <c r="J16" s="55">
-        <v>13.966559869153819</v>
-      </c>
-      <c r="K16" s="48">
+      <c r="O16" s="34">
         <v>0</v>
       </c>
-      <c r="L16" s="54">
-        <v>0</v>
-      </c>
-      <c r="M16" s="54">
-        <v>0</v>
-      </c>
-      <c r="N16" s="54">
-        <v>0</v>
-      </c>
-      <c r="O16" s="55">
-        <v>0</v>
-      </c>
     </row>
-    <row r="17" spans="1:15" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="30"/>
-      <c r="B17" s="58" t="s">
+    <row r="17" spans="1:15" s="8" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="41"/>
+      <c r="B17" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="59">
+      <c r="C17" s="38">
         <v>86.97332109200002</v>
       </c>
-      <c r="D17" s="60">
+      <c r="D17" s="39">
         <v>3.1273958104035091</v>
       </c>
-      <c r="E17" s="60">
+      <c r="E17" s="39">
         <v>2.2995557429437565E-2</v>
       </c>
-      <c r="F17" s="60">
-        <v>0.14947112329134418</v>
-      </c>
-      <c r="G17" s="60">
+      <c r="F17" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="39">
         <v>1.7246668072078175</v>
       </c>
-      <c r="H17" s="60">
+      <c r="H17" s="39">
         <v>0.689866722883127</v>
       </c>
-      <c r="I17" s="60">
+      <c r="I17" s="39">
         <v>137.97334457662541</v>
       </c>
-      <c r="J17" s="60">
+      <c r="J17" s="39">
         <v>1.7246668072078175</v>
       </c>
-      <c r="K17" s="60">
-        <v>0</v>
-      </c>
-      <c r="L17" s="60">
-        <v>0</v>
-      </c>
-      <c r="M17" s="60">
-        <v>0</v>
-      </c>
-      <c r="N17" s="60">
+      <c r="K17" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="L17" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="M17" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="N17" s="39">
         <v>0.22995557429437566</v>
       </c>
-      <c r="O17" s="61">
+      <c r="O17" s="40">
         <v>0.3449333614415635</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="29"/>
+      <c r="A18" s="42"/>
     </row>
     <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
     </row>
     <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
     </row>
     <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
     </row>
     <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A8:A11"/>
@@ -2054,9 +1996,10 @@
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:J2"/>
     <mergeCell ref="K2:O2"/>
+    <mergeCell ref="A2:A3"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D16">
-    <cfRule type="colorScale" priority="113">
+    <cfRule type="colorScale" priority="116">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$D$17/2"/>
@@ -2068,7 +2011,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E16">
-    <cfRule type="colorScale" priority="114">
+    <cfRule type="colorScale" priority="117">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$E$17/2"/>
@@ -2078,7 +2021,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="115">
+    <cfRule type="colorScale" priority="118">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2088,7 +2031,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="116">
+    <cfRule type="colorScale" priority="119">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2100,7 +2043,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F16">
-    <cfRule type="colorScale" priority="117">
+    <cfRule type="colorScale" priority="120">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$F$17/2"/>
@@ -2110,7 +2053,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="118">
+    <cfRule type="colorScale" priority="121">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2120,7 +2063,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="119">
+    <cfRule type="colorScale" priority="122">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2132,7 +2075,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G16">
-    <cfRule type="colorScale" priority="120">
+    <cfRule type="colorScale" priority="123">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$G$17/2"/>
@@ -2142,7 +2085,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="121">
+    <cfRule type="colorScale" priority="124">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2152,7 +2095,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="122">
+    <cfRule type="colorScale" priority="125">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2164,7 +2107,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H16">
-    <cfRule type="colorScale" priority="123">
+    <cfRule type="colorScale" priority="126">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$H$17/2"/>
@@ -2176,7 +2119,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:I16">
-    <cfRule type="colorScale" priority="124">
+    <cfRule type="colorScale" priority="127">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$I$17/2"/>
@@ -2186,7 +2129,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="125">
+    <cfRule type="colorScale" priority="128">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2198,7 +2141,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J16">
-    <cfRule type="colorScale" priority="126">
+    <cfRule type="colorScale" priority="129">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$J$17/2"/>
@@ -2208,7 +2151,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="127">
+    <cfRule type="colorScale" priority="130">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2220,7 +2163,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:K16">
-    <cfRule type="colorScale" priority="128">
+    <cfRule type="colorScale" priority="131">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="num" val="0"/>
@@ -2231,8 +2174,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:N16">
-    <cfRule type="colorScale" priority="130">
+  <conditionalFormatting sqref="M6">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$N$17/2"/>
@@ -2242,7 +2185,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="131">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2252,7 +2195,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="132">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2263,8 +2206,40 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="N4:N16">
+    <cfRule type="colorScale" priority="133">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$N$17/2"/>
+        <cfvo type="formula" val="$N$17"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="134">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="135">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="O4:O16">
-    <cfRule type="colorScale" priority="133">
+    <cfRule type="colorScale" priority="136">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$O$17/2"/>
@@ -2274,7 +2249,7 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="134">
+    <cfRule type="colorScale" priority="137">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2284,7 +2259,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="135">
+    <cfRule type="colorScale" priority="138">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2294,7 +2269,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="136">
+    <cfRule type="colorScale" priority="139">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2304,7 +2279,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="137">
+    <cfRule type="colorScale" priority="140">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0"/>
@@ -2316,7 +2291,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4:L16">
-    <cfRule type="colorScale" priority="5">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="num" val="0"/>
@@ -2327,8 +2302,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:M5 M7:M16">
-    <cfRule type="colorScale" priority="4">
+  <conditionalFormatting sqref="M4:M5">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="num" val="0"/>
@@ -2339,35 +2314,15 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M6">
+  <conditionalFormatting sqref="M7:M16">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$N$17/2"/>
-        <cfvo type="formula" val="$N$17"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="formula" val="1.18"/>
         <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
+        <color rgb="FFFFEB84"/>
         <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>

--- a/data/Heat map 3.xlsx
+++ b/data/Heat map 3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED46C07-14CD-4828-98D6-D162F69AA74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2081A6-1E57-4649-98D1-6554BDADCE2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{45B3C54E-DB58-4340-A914-7AEE103F004F}"/>
   </bookViews>
@@ -159,7 +159,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -229,13 +229,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -776,18 +769,6 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -837,6 +818,15 @@
     <xf numFmtId="164" fontId="7" fillId="3" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -861,15 +851,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -885,14 +869,23 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1239,103 +1232,98 @@
   <cols>
     <col min="1" max="1" width="8" style="12" customWidth="1"/>
     <col min="2" max="2" width="37.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="5.77734375" style="3" customWidth="1"/>
-    <col min="4" max="8" width="6.77734375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="11.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="6.77734375" style="3" customWidth="1"/>
-    <col min="12" max="12" width="8.33203125" style="3" customWidth="1"/>
-    <col min="13" max="15" width="6.77734375" style="3" customWidth="1"/>
+    <col min="3" max="15" width="7.5546875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="48"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="47"/>
     </row>
-    <row r="2" spans="1:15" s="57" customFormat="1" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="58"/>
-      <c r="B2" s="49" t="s">
+    <row r="2" spans="1:15" s="39" customFormat="1" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="54"/>
+      <c r="B2" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="51" t="s">
+      <c r="C2" s="38"/>
+      <c r="D2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="52"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="54" t="s">
+      <c r="E2" s="49"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="54" t="s">
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="56"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="53"/>
     </row>
     <row r="3" spans="1:15" s="4" customFormat="1" ht="143.55000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="59"/>
+      <c r="A3" s="55"/>
       <c r="B3" s="2"/>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="22" t="s">
+      <c r="J3" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="20" t="s">
+      <c r="K3" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="23" t="s">
+      <c r="L3" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="23" t="s">
+      <c r="M3" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="21" t="s">
+      <c r="N3" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="22" t="s">
+      <c r="O3" s="58" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="42" t="s">
         <v>29</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -1344,61 +1332,61 @@
       <c r="C4" s="15">
         <v>3.4135987800000001</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="20">
         <v>6.4448113026335205</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="21">
         <v>0.9185948577454921</v>
       </c>
-      <c r="F4" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="24">
+      <c r="F4" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="20">
         <v>0.2929459683015237</v>
       </c>
-      <c r="H4" s="30">
+      <c r="H4" s="26">
         <v>0.2929459683015237</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="26">
         <v>19.920325844503608</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="27">
         <v>53.902058167480362</v>
       </c>
-      <c r="K4" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="N4" s="30">
+      <c r="K4" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="N4" s="26">
         <v>0.2929459683015237</v>
       </c>
-      <c r="O4" s="31">
+      <c r="O4" s="27">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="44"/>
+      <c r="A5" s="43"/>
       <c r="B5" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="16">
         <v>12.720419820000002</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="22">
         <v>4.0486085151865678</v>
       </c>
       <c r="E5" s="13">
         <v>0.17585555770903244</v>
       </c>
-      <c r="F5" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="26">
+      <c r="F5" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="22">
         <v>1.8867301818345172</v>
       </c>
       <c r="H5" s="14">
@@ -1407,43 +1395,43 @@
       <c r="I5" s="14">
         <v>8.4902858182553285</v>
       </c>
-      <c r="J5" s="32">
+      <c r="J5" s="28">
         <v>16.823344121357778</v>
       </c>
-      <c r="K5" s="26">
+      <c r="K5" s="22">
         <v>1.18</v>
       </c>
-      <c r="L5" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="M5" s="26" t="s">
+      <c r="L5" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="M5" s="22" t="s">
         <v>35</v>
       </c>
       <c r="N5" s="14">
         <v>0.62891006061150567</v>
       </c>
-      <c r="O5" s="32">
+      <c r="O5" s="28">
         <v>0.39306878788219107</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="44"/>
+      <c r="A6" s="43"/>
       <c r="B6" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="16">
         <v>3.5036499999999999</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="22">
         <v>1.427083184678835</v>
       </c>
       <c r="E6" s="13">
         <v>0.35677079616970875</v>
       </c>
-      <c r="F6" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="26">
+      <c r="F6" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="22">
         <v>7.4208325603299423</v>
       </c>
       <c r="H6" s="14">
@@ -1452,13 +1440,13 @@
       <c r="I6" s="14">
         <v>1.427083184678835</v>
       </c>
-      <c r="J6" s="32">
+      <c r="J6" s="28">
         <v>32.252079973741665</v>
       </c>
-      <c r="K6" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L6" s="26" t="s">
+      <c r="K6" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" s="22" t="s">
         <v>35</v>
       </c>
       <c r="M6" s="14" t="s">
@@ -1467,28 +1455,28 @@
       <c r="N6" s="14">
         <v>0</v>
       </c>
-      <c r="O6" s="32">
+      <c r="O6" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="45"/>
+      <c r="A7" s="44"/>
       <c r="B7" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="17">
         <v>21.304912170000001</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="22">
         <v>0.72283799515893521</v>
       </c>
       <c r="E7" s="13">
         <v>4.8189199677262338E-2</v>
       </c>
-      <c r="F7" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="26">
+      <c r="F7" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="22">
         <v>0.23468766076588804</v>
       </c>
       <c r="H7" s="14">
@@ -1497,27 +1485,27 @@
       <c r="I7" s="14">
         <v>105.46863474819008</v>
       </c>
-      <c r="J7" s="32">
+      <c r="J7" s="28">
         <v>14.50369743533188</v>
       </c>
-      <c r="K7" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="M7" s="26" t="s">
+      <c r="K7" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7" s="22" t="s">
         <v>35</v>
       </c>
       <c r="N7" s="14">
         <v>0.79793804660401935</v>
       </c>
-      <c r="O7" s="32">
+      <c r="O7" s="28">
         <v>9.3875064306355213E-2</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="43" t="s">
+      <c r="A8" s="42" t="s">
         <v>30</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -1526,16 +1514,16 @@
       <c r="C8" s="15">
         <v>7.721148311538462</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="22">
         <v>5.3683724657972496</v>
       </c>
       <c r="E8" s="13">
         <v>0.44736437214977082</v>
       </c>
-      <c r="F8" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="26">
+      <c r="F8" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="22">
         <v>1.1656297271936127</v>
       </c>
       <c r="H8" s="14">
@@ -1544,43 +1532,43 @@
       <c r="I8" s="14">
         <v>13.210470241527611</v>
       </c>
-      <c r="J8" s="32">
+      <c r="J8" s="28">
         <v>1.2951441413262363</v>
       </c>
-      <c r="K8" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L8" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="M8" s="26" t="s">
+      <c r="K8" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="M8" s="22" t="s">
         <v>35</v>
       </c>
       <c r="N8" s="14">
         <v>0.77708648479574172</v>
       </c>
-      <c r="O8" s="32">
+      <c r="O8" s="28">
         <v>0.25902882826524726</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="44"/>
+      <c r="A9" s="43"/>
       <c r="B9" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="16">
         <v>12.273168915897436</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="22">
         <v>1.7004573263036482</v>
       </c>
       <c r="E9" s="13">
         <v>8.5022866315182424E-2</v>
       </c>
-      <c r="F9" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="26">
+      <c r="F9" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="22">
         <v>1.7925280871432805</v>
       </c>
       <c r="H9" s="14">
@@ -1589,43 +1577,43 @@
       <c r="I9" s="14">
         <v>259.50917988869764</v>
       </c>
-      <c r="J9" s="32">
+      <c r="J9" s="28">
         <v>18.984502013835652</v>
       </c>
-      <c r="K9" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L9" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="M9" s="26" t="s">
+      <c r="K9" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="M9" s="22" t="s">
         <v>35</v>
       </c>
       <c r="N9" s="14">
         <v>8.147854941560366E-2</v>
       </c>
-      <c r="O9" s="32">
+      <c r="O9" s="28">
         <v>0.7333069447404329</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="44"/>
+      <c r="A10" s="43"/>
       <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="16">
         <v>7.1819852465641034</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="22">
         <v>2.1581776441848408</v>
       </c>
       <c r="E10" s="13">
         <v>0.30831109202640583</v>
       </c>
-      <c r="F10" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="26">
+      <c r="F10" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="22">
         <v>0.97466087156734749</v>
       </c>
       <c r="H10" s="14">
@@ -1634,43 +1622,43 @@
       <c r="I10" s="14">
         <v>522.69670169483186</v>
       </c>
-      <c r="J10" s="32">
+      <c r="J10" s="28">
         <v>2.7847453473352788</v>
       </c>
-      <c r="K10" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L10" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="M10" s="26" t="s">
+      <c r="K10" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="M10" s="22" t="s">
         <v>35</v>
       </c>
       <c r="N10" s="14">
         <v>1.3923726736676394</v>
       </c>
-      <c r="O10" s="32">
+      <c r="O10" s="28">
         <v>0.27847453473352785</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="45"/>
+      <c r="A11" s="44"/>
       <c r="B11" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="17">
         <v>0.57107699999999995</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="22">
         <v>0</v>
       </c>
       <c r="E11" s="13">
         <v>0</v>
       </c>
-      <c r="F11" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" s="26">
+      <c r="F11" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="22">
         <v>3.5021547006795934</v>
       </c>
       <c r="H11" s="14">
@@ -1679,27 +1667,27 @@
       <c r="I11" s="14">
         <v>0</v>
       </c>
-      <c r="J11" s="32">
+      <c r="J11" s="28">
         <v>0</v>
       </c>
-      <c r="K11" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L11" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="M11" s="26" t="s">
+      <c r="K11" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="M11" s="22" t="s">
         <v>35</v>
       </c>
       <c r="N11" s="14">
         <v>5.2532320510193893</v>
       </c>
-      <c r="O11" s="32">
+      <c r="O11" s="28">
         <v>5.2532320510193893</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="42" t="s">
         <v>31</v>
       </c>
       <c r="B12" s="5" t="s">
@@ -1708,16 +1696,16 @@
       <c r="C12" s="18">
         <v>1.3649733500000001</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="22">
         <v>7.267541157488532</v>
       </c>
       <c r="E12" s="13">
         <v>0.66068555977168475</v>
       </c>
-      <c r="F12" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12" s="26">
+      <c r="F12" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="22">
         <v>3.6630751801857522</v>
       </c>
       <c r="H12" s="14">
@@ -1726,43 +1714,43 @@
       <c r="I12" s="14">
         <v>68.865813387492139</v>
       </c>
-      <c r="J12" s="32">
+      <c r="J12" s="28">
         <v>79.855038928049396</v>
       </c>
-      <c r="K12" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L12" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="M12" s="26" t="s">
+      <c r="K12" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="M12" s="22" t="s">
         <v>35</v>
       </c>
       <c r="N12" s="14">
         <v>0</v>
       </c>
-      <c r="O12" s="32">
+      <c r="O12" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="44"/>
+      <c r="A13" s="43"/>
       <c r="B13" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="19">
         <v>7.5363555180000006</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="22">
         <v>0.8757548637715421</v>
       </c>
       <c r="E13" s="13">
         <v>7.9614078524685647E-2</v>
       </c>
-      <c r="F13" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="26">
+      <c r="F13" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="22">
         <v>0.53076052349790426</v>
       </c>
       <c r="H13" s="14">
@@ -1771,43 +1759,43 @@
       <c r="I13" s="14">
         <v>253.70353023199826</v>
       </c>
-      <c r="J13" s="32">
+      <c r="J13" s="28">
         <v>20.699660416418268</v>
       </c>
-      <c r="K13" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L13" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="M13" s="26" t="s">
+      <c r="K13" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="M13" s="22" t="s">
         <v>35</v>
       </c>
       <c r="N13" s="14">
         <v>0.33172532718619019</v>
       </c>
-      <c r="O13" s="32">
+      <c r="O13" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="44"/>
+      <c r="A14" s="43"/>
       <c r="B14" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C14" s="19">
         <v>2.1255060000000001</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="22">
         <v>6.2714478340686881</v>
       </c>
       <c r="E14" s="13">
         <v>1.2542895668137375</v>
       </c>
-      <c r="F14" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="26">
+      <c r="F14" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="22">
         <v>0.47047620660680323</v>
       </c>
       <c r="H14" s="14">
@@ -1816,43 +1804,43 @@
       <c r="I14" s="14">
         <v>0</v>
       </c>
-      <c r="J14" s="32">
+      <c r="J14" s="28">
         <v>0</v>
       </c>
-      <c r="K14" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L14" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="M14" s="26" t="s">
+      <c r="K14" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="M14" s="22" t="s">
         <v>35</v>
       </c>
       <c r="N14" s="14">
         <v>1.1761905165170081</v>
       </c>
-      <c r="O14" s="32">
+      <c r="O14" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="44"/>
+      <c r="A15" s="43"/>
       <c r="B15" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C15" s="19">
         <v>1.4569589599999999</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="22">
         <v>8.5795141408787519</v>
       </c>
       <c r="E15" s="13">
         <v>2.144878535219688</v>
       </c>
-      <c r="F15" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15" s="26">
+      <c r="F15" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="22">
         <v>1.3727222625406004</v>
       </c>
       <c r="H15" s="14">
@@ -1861,117 +1849,117 @@
       <c r="I15" s="14">
         <v>89.226947065139029</v>
       </c>
-      <c r="J15" s="32">
+      <c r="J15" s="28">
         <v>10.295416969054504</v>
       </c>
-      <c r="K15" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L15" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="M15" s="26" t="s">
+      <c r="K15" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="L15" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="M15" s="22" t="s">
         <v>35</v>
       </c>
       <c r="N15" s="14">
         <v>0</v>
       </c>
-      <c r="O15" s="32">
+      <c r="O15" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="45"/>
-      <c r="B16" s="35" t="s">
+      <c r="A16" s="44"/>
+      <c r="B16" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="32">
         <v>5.7995670199999996</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="23">
         <v>0.51727999515384515</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="24">
         <v>5.1727999515384517E-2</v>
       </c>
-      <c r="F16" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" s="27">
+      <c r="F16" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="23">
         <v>0.86213332525640862</v>
       </c>
-      <c r="H16" s="33">
+      <c r="H16" s="29">
         <v>0.51727999515384515</v>
       </c>
-      <c r="I16" s="33">
+      <c r="I16" s="29">
         <v>173.63365170664068</v>
       </c>
-      <c r="J16" s="34">
+      <c r="J16" s="30">
         <v>13.966559869153819</v>
       </c>
-      <c r="K16" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L16" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="M16" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="N16" s="33">
+      <c r="K16" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="M16" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="N16" s="29">
         <v>0</v>
       </c>
-      <c r="O16" s="34">
+      <c r="O16" s="30">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:15" s="8" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="41"/>
-      <c r="B17" s="37" t="s">
+      <c r="A17" s="40"/>
+      <c r="B17" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="38">
+      <c r="C17" s="34">
         <v>86.97332109200002</v>
       </c>
-      <c r="D17" s="39">
+      <c r="D17" s="35">
         <v>3.1273958104035091</v>
       </c>
-      <c r="E17" s="39">
+      <c r="E17" s="35">
         <v>2.2995557429437565E-2</v>
       </c>
-      <c r="F17" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" s="39">
+      <c r="F17" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="35">
         <v>1.7246668072078175</v>
       </c>
-      <c r="H17" s="39">
+      <c r="H17" s="35">
         <v>0.689866722883127</v>
       </c>
-      <c r="I17" s="39">
+      <c r="I17" s="35">
         <v>137.97334457662541</v>
       </c>
-      <c r="J17" s="39">
+      <c r="J17" s="35">
         <v>1.7246668072078175</v>
       </c>
-      <c r="K17" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="L17" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="M17" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="N17" s="39">
+      <c r="K17" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="L17" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="M17" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="N17" s="35">
         <v>0.22995557429437566</v>
       </c>
-      <c r="O17" s="40">
+      <c r="O17" s="36">
         <v>0.3449333614415635</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="42"/>
+      <c r="A18" s="41"/>
     </row>
     <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="B19" s="9"/>
@@ -2174,6 +2162,30 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="L4:L16">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="formula" val="1.18"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M4:M5">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="formula" val="1.18"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="M6">
     <cfRule type="colorScale" priority="4">
       <colorScale>
@@ -2203,6 +2215,18 @@
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M7:M16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="formula" val="1.18"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -2287,42 +2311,6 @@
         <color rgb="FF63BE7B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L16">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="1.18"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M4:M5">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="1.18"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M7:M16">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="1.18"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>

--- a/data/Heat map 3.xlsx
+++ b/data/Heat map 3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/s_lewis_cgiar_org/Documents/TAAT/R4D/KPIS/Alekeh/for uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2081A6-1E57-4649-98D1-6554BDADCE2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{2B4ECC56-BA7D-46F8-B270-6AB9D06BE5A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BEF5C4D2-D501-4FB7-B34B-8B748B8E84E5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{45B3C54E-DB58-4340-A914-7AEE103F004F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{45B3C54E-DB58-4340-A914-7AEE103F004F}"/>
   </bookViews>
   <sheets>
     <sheet name="Res, Cap, Product" sheetId="1" r:id="rId1"/>
@@ -78,9 +78,6 @@
     <t>Mechanization</t>
   </si>
   <si>
-    <t>per Program Target (target/13)</t>
-  </si>
-  <si>
     <t>Thompson indexed publications</t>
   </si>
   <si>
@@ -148,6 +145,9 @@
   </si>
   <si>
     <t>N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per Program Target </t>
   </si>
 </sst>
 </file>
@@ -155,9 +155,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -283,7 +283,9 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
       <right style="medium">
         <color theme="1"/>
       </right>
@@ -305,78 +307,15 @@
       <top style="medium">
         <color theme="1"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color theme="1"/>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
@@ -387,60 +326,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -475,15 +360,6 @@
         <color indexed="64"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -626,28 +502,6 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -714,29 +568,168 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" readingOrder="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -747,78 +740,69 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="7" fillId="3" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="7" fillId="3" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,20 +811,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -848,44 +823,80 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1228,752 +1239,755 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8" style="12" customWidth="1"/>
-    <col min="2" max="2" width="37.109375" style="3" customWidth="1"/>
-    <col min="3" max="15" width="7.5546875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="8" style="9" customWidth="1"/>
+    <col min="2" max="2" width="37.08984375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="5.81640625" style="3" customWidth="1"/>
+    <col min="4" max="8" width="5.54296875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="6.7265625" style="3" customWidth="1"/>
+    <col min="10" max="15" width="5.54296875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="47"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="42"/>
     </row>
-    <row r="2" spans="1:15" s="39" customFormat="1" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="54"/>
-      <c r="B2" s="37" t="s">
+    <row r="2" spans="1:15" s="33" customFormat="1" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="38"/>
+      <c r="B2" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="32"/>
+      <c r="D2" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="44"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="47" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="47" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="49"/>
+    </row>
+    <row r="3" spans="1:15" s="4" customFormat="1" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="39"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="53" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="54" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="L3" s="56" t="s">
+        <v>5</v>
+      </c>
+      <c r="M3" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" s="54" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3" s="55" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="51" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="51" t="s">
-        <v>3</v>
-      </c>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="52"/>
-      <c r="O2" s="53"/>
+      <c r="C4" s="12">
+        <v>3.4135987800000001</v>
+      </c>
+      <c r="D4" s="16">
+        <v>6.4448113026335205</v>
+      </c>
+      <c r="E4" s="17">
+        <v>0.9185948577454921</v>
+      </c>
+      <c r="F4" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="16">
+        <v>0.2929459683015237</v>
+      </c>
+      <c r="H4" s="22">
+        <v>0.2929459683015237</v>
+      </c>
+      <c r="I4" s="22">
+        <v>19.920325844503608</v>
+      </c>
+      <c r="J4" s="23">
+        <v>53.902058167480362</v>
+      </c>
+      <c r="K4" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" s="22">
+        <v>0.2929459683015237</v>
+      </c>
+      <c r="O4" s="23">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:15" s="4" customFormat="1" ht="143.55000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="55"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="56" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="58" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="57" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="57" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="L3" s="59" t="s">
-        <v>5</v>
-      </c>
-      <c r="M3" s="59" t="s">
-        <v>20</v>
-      </c>
-      <c r="N3" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="O3" s="58" t="s">
+    <row r="5" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="51"/>
+      <c r="B5" s="59" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="13">
+        <v>12.720419820000002</v>
+      </c>
+      <c r="D5" s="18">
+        <v>4.0486085151865678</v>
+      </c>
+      <c r="E5" s="10">
+        <v>0.17585555770903244</v>
+      </c>
+      <c r="F5" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="18">
+        <v>1.8867301818345172</v>
+      </c>
+      <c r="H5" s="11">
+        <v>2.20118521214027</v>
+      </c>
+      <c r="I5" s="11">
+        <v>8.4902858182553285</v>
+      </c>
+      <c r="J5" s="24">
+        <v>16.823344121357778</v>
+      </c>
+      <c r="K5" s="18">
+        <v>3.62</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="N5" s="11">
+        <v>0.62891006061150567</v>
+      </c>
+      <c r="O5" s="24">
+        <v>0.39306878788219107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="51"/>
+      <c r="B6" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="13">
+        <v>3.5036499999999999</v>
+      </c>
+      <c r="D6" s="18">
+        <v>1.427083184678835</v>
+      </c>
+      <c r="E6" s="10">
+        <v>0.35677079616970875</v>
+      </c>
+      <c r="F6" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="18">
+        <v>7.4208325603299423</v>
+      </c>
+      <c r="H6" s="11">
+        <v>5.4229161017795731</v>
+      </c>
+      <c r="I6" s="11">
+        <v>1.427083184678835</v>
+      </c>
+      <c r="J6" s="24">
+        <v>32.252079973741665</v>
+      </c>
+      <c r="K6" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="N6" s="11">
+        <v>0</v>
+      </c>
+      <c r="O6" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="52"/>
+      <c r="B7" s="60" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="14">
+        <v>21.304912170000001</v>
+      </c>
+      <c r="D7" s="19">
+        <v>0.72283799515893521</v>
+      </c>
+      <c r="E7" s="20">
+        <v>4.8189199677262338E-2</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="19">
+        <v>0.23468766076588804</v>
+      </c>
+      <c r="H7" s="25">
+        <v>0.32856272507224321</v>
+      </c>
+      <c r="I7" s="25">
+        <v>105.46863474819008</v>
+      </c>
+      <c r="J7" s="26">
+        <v>14.50369743533188</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="M7" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="N7" s="25">
+        <v>0.79793804660401935</v>
+      </c>
+      <c r="O7" s="26">
+        <v>9.3875064306355213E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="12">
+        <v>7.721148311538462</v>
+      </c>
+      <c r="D8" s="16">
+        <v>5.3683724657972496</v>
+      </c>
+      <c r="E8" s="17">
+        <v>0.44736437214977082</v>
+      </c>
+      <c r="F8" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="16">
+        <v>1.1656297271936127</v>
+      </c>
+      <c r="H8" s="22">
+        <v>1.1656297271936127</v>
+      </c>
+      <c r="I8" s="22">
+        <v>13.210470241527611</v>
+      </c>
+      <c r="J8" s="23">
+        <v>1.2951441413262363</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="M8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="N8" s="22">
+        <v>0.77708648479574172</v>
+      </c>
+      <c r="O8" s="23">
+        <v>0.25902882826524726</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="51"/>
+      <c r="B9" s="59" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="13">
+        <v>12.273168915897436</v>
+      </c>
+      <c r="D9" s="18">
+        <v>1.7004573263036482</v>
+      </c>
+      <c r="E9" s="10">
+        <v>8.5022866315182424E-2</v>
+      </c>
+      <c r="F9" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="18">
+        <v>1.7925280871432805</v>
+      </c>
+      <c r="H9" s="11">
+        <v>1.1406996918184511</v>
+      </c>
+      <c r="I9" s="11">
+        <v>259.50917988869764</v>
+      </c>
+      <c r="J9" s="24">
+        <v>18.984502013835652</v>
+      </c>
+      <c r="K9" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="N9" s="11">
+        <v>8.147854941560366E-2</v>
+      </c>
+      <c r="O9" s="24">
+        <v>0.7333069447404329</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="51"/>
+      <c r="B10" s="59" t="s">
         <v>22</v>
       </c>
+      <c r="C10" s="13">
+        <v>7.1819852465641034</v>
+      </c>
+      <c r="D10" s="18">
+        <v>2.1581776441848408</v>
+      </c>
+      <c r="E10" s="10">
+        <v>0.30831109202640583</v>
+      </c>
+      <c r="F10" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="18">
+        <v>0.97466087156734749</v>
+      </c>
+      <c r="H10" s="11">
+        <v>0.4177118021002918</v>
+      </c>
+      <c r="I10" s="11">
+        <v>522.69670169483186</v>
+      </c>
+      <c r="J10" s="24">
+        <v>2.7847453473352788</v>
+      </c>
+      <c r="K10" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="N10" s="11">
+        <v>1.3923726736676394</v>
+      </c>
+      <c r="O10" s="24">
+        <v>0.27847453473352785</v>
+      </c>
     </row>
-    <row r="4" spans="1:15" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="42" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="15">
-        <v>3.4135987800000001</v>
-      </c>
-      <c r="D4" s="20">
-        <v>6.4448113026335205</v>
-      </c>
-      <c r="E4" s="21">
-        <v>0.9185948577454921</v>
-      </c>
-      <c r="F4" s="25" t="s">
+    <row r="11" spans="1:15" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="52"/>
+      <c r="B11" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="14">
+        <v>0.57107699999999995</v>
+      </c>
+      <c r="D11" s="19">
+        <v>0</v>
+      </c>
+      <c r="E11" s="20">
+        <v>0</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="19">
+        <v>3.5021547006795934</v>
+      </c>
+      <c r="H11" s="25">
+        <v>1.7510773503397967</v>
+      </c>
+      <c r="I11" s="25">
+        <v>0</v>
+      </c>
+      <c r="J11" s="26">
+        <v>0</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="M11" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="N11" s="25">
+        <v>5.2532320510193893</v>
+      </c>
+      <c r="O11" s="26">
+        <v>5.2532320510193893</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="61">
+        <v>1.3649733500000001</v>
+      </c>
+      <c r="D12" s="16">
+        <v>7.267541157488532</v>
+      </c>
+      <c r="E12" s="17">
+        <v>0.66068555977168475</v>
+      </c>
+      <c r="F12" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="16">
+        <v>3.6630751801857522</v>
+      </c>
+      <c r="H12" s="22">
+        <v>3.6630751801857522</v>
+      </c>
+      <c r="I12" s="22">
+        <v>68.865813387492139</v>
+      </c>
+      <c r="J12" s="23">
+        <v>79.855038928049396</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="M12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="N12" s="22">
+        <v>0</v>
+      </c>
+      <c r="O12" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="51"/>
+      <c r="B13" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="15">
+        <v>7.5363555180000006</v>
+      </c>
+      <c r="D13" s="18">
+        <v>0.8757548637715421</v>
+      </c>
+      <c r="E13" s="10">
+        <v>7.9614078524685647E-2</v>
+      </c>
+      <c r="F13" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="18">
+        <v>0.53076052349790426</v>
+      </c>
+      <c r="H13" s="11">
+        <v>0.39807039262342825</v>
+      </c>
+      <c r="I13" s="11">
+        <v>253.70353023199826</v>
+      </c>
+      <c r="J13" s="24">
+        <v>20.699660416418268</v>
+      </c>
+      <c r="K13" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="N13" s="11">
+        <v>0.33172532718619019</v>
+      </c>
+      <c r="O13" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="51"/>
+      <c r="B14" s="59" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="15">
+        <v>2.1255060000000001</v>
+      </c>
+      <c r="D14" s="18">
+        <v>6.2714478340686881</v>
+      </c>
+      <c r="E14" s="10">
+        <v>1.2542895668137375</v>
+      </c>
+      <c r="F14" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" s="18">
+        <v>0.47047620660680323</v>
+      </c>
+      <c r="H14" s="11">
+        <v>0.94095241321360645</v>
+      </c>
+      <c r="I14" s="11">
+        <v>0</v>
+      </c>
+      <c r="J14" s="24">
+        <v>0</v>
+      </c>
+      <c r="K14" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="N14" s="11">
+        <v>1.1761905165170081</v>
+      </c>
+      <c r="O14" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="51"/>
+      <c r="B15" s="59" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="15">
+        <v>1.4569589599999999</v>
+      </c>
+      <c r="D15" s="18">
+        <v>8.5795141408787519</v>
+      </c>
+      <c r="E15" s="10">
+        <v>2.144878535219688</v>
+      </c>
+      <c r="F15" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="18">
+        <v>1.3727222625406004</v>
+      </c>
+      <c r="H15" s="11">
+        <v>5.4908890501624015</v>
+      </c>
+      <c r="I15" s="11">
+        <v>89.226947065139029</v>
+      </c>
+      <c r="J15" s="24">
+        <v>10.295416969054504</v>
+      </c>
+      <c r="K15" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="N15" s="11">
+        <v>0</v>
+      </c>
+      <c r="O15" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="52"/>
+      <c r="B16" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="62">
+        <v>5.7995670199999996</v>
+      </c>
+      <c r="D16" s="19">
+        <v>0.51727999515384515</v>
+      </c>
+      <c r="E16" s="20">
+        <v>5.1727999515384517E-2</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" s="19">
+        <v>0.86213332525640862</v>
+      </c>
+      <c r="H16" s="25">
+        <v>0.51727999515384515</v>
+      </c>
+      <c r="I16" s="25">
+        <v>173.63365170664068</v>
+      </c>
+      <c r="J16" s="26">
+        <v>13.966559869153819</v>
+      </c>
+      <c r="K16" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="M16" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="N16" s="25">
+        <v>0</v>
+      </c>
+      <c r="O16" s="26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="34"/>
+      <c r="B17" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="20">
-        <v>0.2929459683015237</v>
-      </c>
-      <c r="H4" s="26">
-        <v>0.2929459683015237</v>
-      </c>
-      <c r="I4" s="26">
-        <v>19.920325844503608</v>
-      </c>
-      <c r="J4" s="27">
-        <v>53.902058167480362</v>
-      </c>
-      <c r="K4" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="N4" s="26">
-        <v>0.2929459683015237</v>
-      </c>
-      <c r="O4" s="27">
-        <v>0</v>
+      <c r="C17" s="28">
+        <v>86.97332109200002</v>
+      </c>
+      <c r="D17" s="29">
+        <v>3.1273958104035091</v>
+      </c>
+      <c r="E17" s="29">
+        <v>2.2995557429437565E-2</v>
+      </c>
+      <c r="F17" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="29">
+        <v>1.7246668072078175</v>
+      </c>
+      <c r="H17" s="29">
+        <v>0.689866722883127</v>
+      </c>
+      <c r="I17" s="29">
+        <v>137.97334457662541</v>
+      </c>
+      <c r="J17" s="29">
+        <v>1.7246668072078175</v>
+      </c>
+      <c r="K17" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="M17" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="N17" s="29">
+        <v>0.22995557429437566</v>
+      </c>
+      <c r="O17" s="30">
+        <v>0.3449333614415635</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="43"/>
-      <c r="B5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="16">
-        <v>12.720419820000002</v>
-      </c>
-      <c r="D5" s="22">
-        <v>4.0486085151865678</v>
-      </c>
-      <c r="E5" s="13">
-        <v>0.17585555770903244</v>
-      </c>
-      <c r="F5" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="22">
-        <v>1.8867301818345172</v>
-      </c>
-      <c r="H5" s="14">
-        <v>2.20118521214027</v>
-      </c>
-      <c r="I5" s="14">
-        <v>8.4902858182553285</v>
-      </c>
-      <c r="J5" s="28">
-        <v>16.823344121357778</v>
-      </c>
-      <c r="K5" s="22">
-        <v>1.18</v>
-      </c>
-      <c r="L5" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M5" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="N5" s="14">
-        <v>0.62891006061150567</v>
-      </c>
-      <c r="O5" s="28">
-        <v>0.39306878788219107</v>
-      </c>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A18" s="35"/>
     </row>
-    <row r="6" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="43"/>
-      <c r="B6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="16">
-        <v>3.5036499999999999</v>
-      </c>
-      <c r="D6" s="22">
-        <v>1.427083184678835</v>
-      </c>
-      <c r="E6" s="13">
-        <v>0.35677079616970875</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="22">
-        <v>7.4208325603299423</v>
-      </c>
-      <c r="H6" s="14">
-        <v>5.4229161017795731</v>
-      </c>
-      <c r="I6" s="14">
-        <v>1.427083184678835</v>
-      </c>
-      <c r="J6" s="28">
-        <v>32.252079973741665</v>
-      </c>
-      <c r="K6" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="L6" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M6" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="N6" s="14">
-        <v>0</v>
-      </c>
-      <c r="O6" s="28">
-        <v>0</v>
-      </c>
+    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
     </row>
-    <row r="7" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="44"/>
-      <c r="B7" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="17">
-        <v>21.304912170000001</v>
-      </c>
-      <c r="D7" s="22">
-        <v>0.72283799515893521</v>
-      </c>
-      <c r="E7" s="13">
-        <v>4.8189199677262338E-2</v>
-      </c>
-      <c r="F7" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="22">
-        <v>0.23468766076588804</v>
-      </c>
-      <c r="H7" s="14">
-        <v>0.32856272507224321</v>
-      </c>
-      <c r="I7" s="14">
-        <v>105.46863474819008</v>
-      </c>
-      <c r="J7" s="28">
-        <v>14.50369743533188</v>
-      </c>
-      <c r="K7" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M7" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="N7" s="14">
-        <v>0.79793804660401935</v>
-      </c>
-      <c r="O7" s="28">
-        <v>9.3875064306355213E-2</v>
-      </c>
+    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
     </row>
-    <row r="8" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="42" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="15">
-        <v>7.721148311538462</v>
-      </c>
-      <c r="D8" s="22">
-        <v>5.3683724657972496</v>
-      </c>
-      <c r="E8" s="13">
-        <v>0.44736437214977082</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="22">
-        <v>1.1656297271936127</v>
-      </c>
-      <c r="H8" s="14">
-        <v>1.1656297271936127</v>
-      </c>
-      <c r="I8" s="14">
-        <v>13.210470241527611</v>
-      </c>
-      <c r="J8" s="28">
-        <v>1.2951441413262363</v>
-      </c>
-      <c r="K8" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="L8" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M8" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="N8" s="14">
-        <v>0.77708648479574172</v>
-      </c>
-      <c r="O8" s="28">
-        <v>0.25902882826524726</v>
-      </c>
+    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
     </row>
-    <row r="9" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="43"/>
-      <c r="B9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="16">
-        <v>12.273168915897436</v>
-      </c>
-      <c r="D9" s="22">
-        <v>1.7004573263036482</v>
-      </c>
-      <c r="E9" s="13">
-        <v>8.5022866315182424E-2</v>
-      </c>
-      <c r="F9" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="22">
-        <v>1.7925280871432805</v>
-      </c>
-      <c r="H9" s="14">
-        <v>1.1406996918184511</v>
-      </c>
-      <c r="I9" s="14">
-        <v>259.50917988869764</v>
-      </c>
-      <c r="J9" s="28">
-        <v>18.984502013835652</v>
-      </c>
-      <c r="K9" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="L9" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M9" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="N9" s="14">
-        <v>8.147854941560366E-2</v>
-      </c>
-      <c r="O9" s="28">
-        <v>0.7333069447404329</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="43"/>
-      <c r="B10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="16">
-        <v>7.1819852465641034</v>
-      </c>
-      <c r="D10" s="22">
-        <v>2.1581776441848408</v>
-      </c>
-      <c r="E10" s="13">
-        <v>0.30831109202640583</v>
-      </c>
-      <c r="F10" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="22">
-        <v>0.97466087156734749</v>
-      </c>
-      <c r="H10" s="14">
-        <v>0.4177118021002918</v>
-      </c>
-      <c r="I10" s="14">
-        <v>522.69670169483186</v>
-      </c>
-      <c r="J10" s="28">
-        <v>2.7847453473352788</v>
-      </c>
-      <c r="K10" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="L10" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M10" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="N10" s="14">
-        <v>1.3923726736676394</v>
-      </c>
-      <c r="O10" s="28">
-        <v>0.27847453473352785</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="44"/>
-      <c r="B11" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="17">
-        <v>0.57107699999999995</v>
-      </c>
-      <c r="D11" s="22">
-        <v>0</v>
-      </c>
-      <c r="E11" s="13">
-        <v>0</v>
-      </c>
-      <c r="F11" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" s="22">
-        <v>3.5021547006795934</v>
-      </c>
-      <c r="H11" s="14">
-        <v>1.7510773503397967</v>
-      </c>
-      <c r="I11" s="14">
-        <v>0</v>
-      </c>
-      <c r="J11" s="28">
-        <v>0</v>
-      </c>
-      <c r="K11" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="L11" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M11" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="N11" s="14">
-        <v>5.2532320510193893</v>
-      </c>
-      <c r="O11" s="28">
-        <v>5.2532320510193893</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="42" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="18">
-        <v>1.3649733500000001</v>
-      </c>
-      <c r="D12" s="22">
-        <v>7.267541157488532</v>
-      </c>
-      <c r="E12" s="13">
-        <v>0.66068555977168475</v>
-      </c>
-      <c r="F12" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12" s="22">
-        <v>3.6630751801857522</v>
-      </c>
-      <c r="H12" s="14">
-        <v>3.6630751801857522</v>
-      </c>
-      <c r="I12" s="14">
-        <v>68.865813387492139</v>
-      </c>
-      <c r="J12" s="28">
-        <v>79.855038928049396</v>
-      </c>
-      <c r="K12" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="L12" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M12" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="N12" s="14">
-        <v>0</v>
-      </c>
-      <c r="O12" s="28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="43"/>
-      <c r="B13" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="19">
-        <v>7.5363555180000006</v>
-      </c>
-      <c r="D13" s="22">
-        <v>0.8757548637715421</v>
-      </c>
-      <c r="E13" s="13">
-        <v>7.9614078524685647E-2</v>
-      </c>
-      <c r="F13" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="22">
-        <v>0.53076052349790426</v>
-      </c>
-      <c r="H13" s="14">
-        <v>0.39807039262342825</v>
-      </c>
-      <c r="I13" s="14">
-        <v>253.70353023199826</v>
-      </c>
-      <c r="J13" s="28">
-        <v>20.699660416418268</v>
-      </c>
-      <c r="K13" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="L13" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M13" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="N13" s="14">
-        <v>0.33172532718619019</v>
-      </c>
-      <c r="O13" s="28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="43"/>
-      <c r="B14" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="19">
-        <v>2.1255060000000001</v>
-      </c>
-      <c r="D14" s="22">
-        <v>6.2714478340686881</v>
-      </c>
-      <c r="E14" s="13">
-        <v>1.2542895668137375</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="22">
-        <v>0.47047620660680323</v>
-      </c>
-      <c r="H14" s="14">
-        <v>0.94095241321360645</v>
-      </c>
-      <c r="I14" s="14">
-        <v>0</v>
-      </c>
-      <c r="J14" s="28">
-        <v>0</v>
-      </c>
-      <c r="K14" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="L14" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M14" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="N14" s="14">
-        <v>1.1761905165170081</v>
-      </c>
-      <c r="O14" s="28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="43"/>
-      <c r="B15" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="19">
-        <v>1.4569589599999999</v>
-      </c>
-      <c r="D15" s="22">
-        <v>8.5795141408787519</v>
-      </c>
-      <c r="E15" s="13">
-        <v>2.144878535219688</v>
-      </c>
-      <c r="F15" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15" s="22">
-        <v>1.3727222625406004</v>
-      </c>
-      <c r="H15" s="14">
-        <v>5.4908890501624015</v>
-      </c>
-      <c r="I15" s="14">
-        <v>89.226947065139029</v>
-      </c>
-      <c r="J15" s="28">
-        <v>10.295416969054504</v>
-      </c>
-      <c r="K15" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="L15" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M15" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="N15" s="14">
-        <v>0</v>
-      </c>
-      <c r="O15" s="28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="44"/>
-      <c r="B16" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="32">
-        <v>5.7995670199999996</v>
-      </c>
-      <c r="D16" s="23">
-        <v>0.51727999515384515</v>
-      </c>
-      <c r="E16" s="24">
-        <v>5.1727999515384517E-2</v>
-      </c>
-      <c r="F16" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" s="23">
-        <v>0.86213332525640862</v>
-      </c>
-      <c r="H16" s="29">
-        <v>0.51727999515384515</v>
-      </c>
-      <c r="I16" s="29">
-        <v>173.63365170664068</v>
-      </c>
-      <c r="J16" s="30">
-        <v>13.966559869153819</v>
-      </c>
-      <c r="K16" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="L16" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M16" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="N16" s="29">
-        <v>0</v>
-      </c>
-      <c r="O16" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" s="8" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="40"/>
-      <c r="B17" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="34">
-        <v>86.97332109200002</v>
-      </c>
-      <c r="D17" s="35">
-        <v>3.1273958104035091</v>
-      </c>
-      <c r="E17" s="35">
-        <v>2.2995557429437565E-2</v>
-      </c>
-      <c r="F17" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" s="35">
-        <v>1.7246668072078175</v>
-      </c>
-      <c r="H17" s="35">
-        <v>0.689866722883127</v>
-      </c>
-      <c r="I17" s="35">
-        <v>137.97334457662541</v>
-      </c>
-      <c r="J17" s="35">
-        <v>1.7246668072078175</v>
-      </c>
-      <c r="K17" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="L17" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="M17" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="N17" s="35">
-        <v>0.22995557429437566</v>
-      </c>
-      <c r="O17" s="36">
-        <v>0.3449333614415635</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="41"/>
-    </row>
-    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-    </row>
-    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-    </row>
-    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-    </row>
-    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A17:A18"/>

--- a/data/Heat map 3.xlsx
+++ b/data/Heat map 3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/s_lewis_cgiar_org/Documents/TAAT/R4D/KPIS/Alekeh/for uploads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{2B4ECC56-BA7D-46F8-B270-6AB9D06BE5A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BEF5C4D2-D501-4FB7-B34B-8B748B8E84E5}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="8_{2B4ECC56-BA7D-46F8-B270-6AB9D06BE5A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD1DBB7A-63BE-4C7E-949A-324EC5EAF093}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{45B3C54E-DB58-4340-A914-7AEE103F004F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{45B3C54E-DB58-4340-A914-7AEE103F004F}"/>
   </bookViews>
   <sheets>
     <sheet name="Res, Cap, Product" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="36">
   <si>
     <t>KPI by $</t>
   </si>
@@ -155,9 +155,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -719,16 +719,16 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -740,68 +740,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="43" fontId="7" fillId="3" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="43" fontId="7" fillId="3" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -811,11 +753,114 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -823,15 +868,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -847,9 +883,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -859,44 +892,11 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1239,755 +1239,753 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" style="9" customWidth="1"/>
-    <col min="2" max="2" width="37.08984375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="5.81640625" style="3" customWidth="1"/>
-    <col min="4" max="8" width="5.54296875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="6.7265625" style="3" customWidth="1"/>
-    <col min="10" max="15" width="5.54296875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="37.109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="5.77734375" style="3" customWidth="1"/>
+    <col min="4" max="15" width="6.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
-      <c r="B1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="37"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="42"/>
+      <c r="B1" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="52"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="54"/>
     </row>
-    <row r="2" spans="1:15" s="33" customFormat="1" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="38"/>
-      <c r="B2" s="31" t="s">
+    <row r="2" spans="1:15" s="13" customFormat="1" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="61"/>
+      <c r="B2" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="43" t="s">
+      <c r="C2" s="12"/>
+      <c r="D2" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="44"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="47" t="s">
+      <c r="E2" s="56"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="47" t="s">
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="49"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="60"/>
     </row>
-    <row r="3" spans="1:15" s="4" customFormat="1" ht="115.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="39"/>
+    <row r="3" spans="1:15" s="4" customFormat="1" ht="103.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="62"/>
       <c r="B3" s="2"/>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="53" t="s">
+      <c r="D3" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="54" t="s">
+      <c r="E3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="55" t="s">
+      <c r="F3" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="53" t="s">
+      <c r="G3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="54" t="s">
+      <c r="H3" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="54" t="s">
+      <c r="I3" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="55" t="s">
+      <c r="J3" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="53" t="s">
+      <c r="K3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="56" t="s">
+      <c r="L3" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="56" t="s">
+      <c r="M3" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="N3" s="54" t="s">
+      <c r="N3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="O3" s="55" t="s">
+      <c r="O3" s="17" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="50" t="s">
+    <row r="4" spans="1:15" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="22">
         <v>3.4135987800000001</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="29">
         <v>6.4448113026335205</v>
       </c>
-      <c r="E4" s="17">
-        <v>0.9185948577454921</v>
-      </c>
-      <c r="F4" s="58" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="16">
+      <c r="E4" s="30">
+        <v>3.1357142857142857</v>
+      </c>
+      <c r="F4" s="31">
         <v>0.2929459683015237</v>
       </c>
-      <c r="H4" s="22">
+      <c r="G4" s="29">
         <v>0.2929459683015237</v>
       </c>
-      <c r="I4" s="22">
+      <c r="H4" s="32">
+        <v>0.2929459683015237</v>
+      </c>
+      <c r="I4" s="32">
         <v>19.920325844503608</v>
       </c>
-      <c r="J4" s="23">
+      <c r="J4" s="33">
         <v>53.902058167480362</v>
       </c>
-      <c r="K4" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="M4" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="N4" s="22">
+      <c r="K4" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" s="32">
         <v>0.2929459683015237</v>
       </c>
-      <c r="O4" s="23">
+      <c r="O4" s="33">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="51"/>
-      <c r="B5" s="59" t="s">
+    <row r="5" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="23">
         <v>12.720419820000002</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="34">
         <v>4.0486085151865678</v>
       </c>
-      <c r="E5" s="10">
-        <v>0.17585555770903244</v>
-      </c>
-      <c r="F5" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="18">
+      <c r="E5" s="35">
+        <v>2.2369565217391307</v>
+      </c>
+      <c r="F5" s="36">
+        <v>0</v>
+      </c>
+      <c r="G5" s="34">
         <v>1.8867301818345172</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="37">
         <v>2.20118521214027</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="37">
         <v>8.4902858182553285</v>
       </c>
-      <c r="J5" s="24">
+      <c r="J5" s="38">
         <v>16.823344121357778</v>
       </c>
-      <c r="K5" s="18">
+      <c r="K5" s="34">
         <v>3.62</v>
       </c>
-      <c r="L5" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="N5" s="11">
+      <c r="L5" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="N5" s="37">
         <v>0.62891006061150567</v>
       </c>
-      <c r="O5" s="24">
+      <c r="O5" s="38">
         <v>0.39306878788219107</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="51"/>
-      <c r="B6" s="59" t="s">
+    <row r="6" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="49"/>
+      <c r="B6" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="23">
         <v>3.5036499999999999</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="34">
         <v>1.427083184678835</v>
       </c>
-      <c r="E6" s="10">
-        <v>0.35677079616970875</v>
-      </c>
-      <c r="F6" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="18">
+      <c r="E6" s="35">
+        <v>1.25</v>
+      </c>
+      <c r="F6" s="36">
+        <v>0</v>
+      </c>
+      <c r="G6" s="34">
         <v>7.4208325603299423</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="37">
         <v>5.4229161017795731</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="37">
         <v>1.427083184678835</v>
       </c>
-      <c r="J6" s="24">
+      <c r="J6" s="38">
         <v>32.252079973741665</v>
       </c>
-      <c r="K6" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="N6" s="11">
-        <v>0</v>
-      </c>
-      <c r="O6" s="24">
+      <c r="K6" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="N6" s="37">
+        <v>0</v>
+      </c>
+      <c r="O6" s="38">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="52"/>
-      <c r="B7" s="60" t="s">
+    <row r="7" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="50"/>
+      <c r="B7" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="24">
         <v>21.304912170000001</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="39">
         <v>0.72283799515893521</v>
       </c>
-      <c r="E7" s="20">
-        <v>4.8189199677262338E-2</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="19">
+      <c r="E7" s="40">
+        <v>1.0266666666666666</v>
+      </c>
+      <c r="F7" s="41">
+        <v>0</v>
+      </c>
+      <c r="G7" s="39">
         <v>0.23468766076588804</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="42">
         <v>0.32856272507224321</v>
       </c>
-      <c r="I7" s="25">
+      <c r="I7" s="42">
         <v>105.46863474819008</v>
       </c>
-      <c r="J7" s="26">
+      <c r="J7" s="43">
         <v>14.50369743533188</v>
       </c>
-      <c r="K7" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M7" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="N7" s="25">
+      <c r="K7" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="M7" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="N7" s="42">
         <v>0.79793804660401935</v>
       </c>
-      <c r="O7" s="26">
+      <c r="O7" s="43">
         <v>9.3875064306355213E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="50" t="s">
+    <row r="8" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="57" t="s">
+      <c r="B8" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="22">
         <v>7.721148311538462</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="29">
         <v>5.3683724657972496</v>
       </c>
-      <c r="E8" s="17">
-        <v>0.44736437214977082</v>
-      </c>
-      <c r="F8" s="58" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="16">
+      <c r="E8" s="30">
+        <v>3.4541666666666671</v>
+      </c>
+      <c r="F8" s="31">
+        <v>0.12951441413262363</v>
+      </c>
+      <c r="G8" s="29">
         <v>1.1656297271936127</v>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="32">
         <v>1.1656297271936127</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="32">
         <v>13.210470241527611</v>
       </c>
-      <c r="J8" s="23">
+      <c r="J8" s="33">
         <v>1.2951441413262363</v>
       </c>
-      <c r="K8" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="L8" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="M8" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="N8" s="22">
+      <c r="K8" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="M8" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="N8" s="32">
         <v>0.77708648479574172</v>
       </c>
-      <c r="O8" s="23">
+      <c r="O8" s="33">
         <v>0.25902882826524726</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="51"/>
-      <c r="B9" s="59" t="s">
+    <row r="9" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="49"/>
+      <c r="B9" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="23">
         <v>12.273168915897436</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="34">
         <v>1.7004573263036482</v>
       </c>
-      <c r="E9" s="10">
-        <v>8.5022866315182424E-2</v>
-      </c>
-      <c r="F9" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="18">
+      <c r="E9" s="35">
+        <v>1.0435000000000001</v>
+      </c>
+      <c r="F9" s="36">
+        <v>6.7627196014951027E-2</v>
+      </c>
+      <c r="G9" s="34">
         <v>1.7925280871432805</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="37">
         <v>1.1406996918184511</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="37">
         <v>259.50917988869764</v>
       </c>
-      <c r="J9" s="24">
+      <c r="J9" s="38">
         <v>18.984502013835652</v>
       </c>
-      <c r="K9" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="L9" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="N9" s="11">
+      <c r="K9" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="M9" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="N9" s="37">
         <v>8.147854941560366E-2</v>
       </c>
-      <c r="O9" s="24">
+      <c r="O9" s="38">
         <v>0.7333069447404329</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="51"/>
-      <c r="B10" s="59" t="s">
+    <row r="10" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="49"/>
+      <c r="B10" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="23">
         <v>7.1819852465641034</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="34">
         <v>2.1581776441848408</v>
       </c>
-      <c r="E10" s="10">
-        <v>0.30831109202640583</v>
-      </c>
-      <c r="F10" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="18">
+      <c r="E10" s="35">
+        <v>2.2142857142857144</v>
+      </c>
+      <c r="F10" s="36">
+        <v>0.27847453473352785</v>
+      </c>
+      <c r="G10" s="34">
         <v>0.97466087156734749</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="37">
         <v>0.4177118021002918</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="37">
         <v>522.69670169483186</v>
       </c>
-      <c r="J10" s="24">
+      <c r="J10" s="38">
         <v>2.7847453473352788</v>
       </c>
-      <c r="K10" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="L10" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="N10" s="11">
+      <c r="K10" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="M10" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="N10" s="37">
         <v>1.3923726736676394</v>
       </c>
-      <c r="O10" s="24">
+      <c r="O10" s="38">
         <v>0.27847453473352785</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="52"/>
-      <c r="B11" s="60" t="s">
+    <row r="11" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="50"/>
+      <c r="B11" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="24">
         <v>0.57107699999999995</v>
       </c>
-      <c r="D11" s="19">
-        <v>0</v>
-      </c>
-      <c r="E11" s="20">
-        <v>0</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" s="19">
+      <c r="D11" s="39">
+        <v>0</v>
+      </c>
+      <c r="E11" s="40">
+        <v>0</v>
+      </c>
+      <c r="F11" s="41">
+        <v>0</v>
+      </c>
+      <c r="G11" s="39">
         <v>3.5021547006795934</v>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="42">
         <v>1.7510773503397967</v>
       </c>
-      <c r="I11" s="25">
-        <v>0</v>
-      </c>
-      <c r="J11" s="26">
-        <v>0</v>
-      </c>
-      <c r="K11" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="L11" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M11" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="N11" s="25">
+      <c r="I11" s="42">
+        <v>0</v>
+      </c>
+      <c r="J11" s="43">
+        <v>0</v>
+      </c>
+      <c r="K11" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="M11" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="N11" s="42">
         <v>5.2532320510193893</v>
       </c>
-      <c r="O11" s="26">
+      <c r="O11" s="43">
         <v>5.2532320510193893</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="50" t="s">
+    <row r="12" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="57" t="s">
+      <c r="B12" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="61">
+      <c r="C12" s="25">
         <v>1.3649733500000001</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="29">
         <v>7.267541157488532</v>
       </c>
-      <c r="E12" s="17">
-        <v>0.66068555977168475</v>
-      </c>
-      <c r="F12" s="58" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="16">
+      <c r="E12" s="30">
+        <v>0.90181818181818185</v>
+      </c>
+      <c r="F12" s="31">
+        <v>0</v>
+      </c>
+      <c r="G12" s="29">
         <v>3.6630751801857522</v>
       </c>
-      <c r="H12" s="22">
+      <c r="H12" s="32">
         <v>3.6630751801857522</v>
       </c>
-      <c r="I12" s="22">
+      <c r="I12" s="32">
         <v>68.865813387492139</v>
       </c>
-      <c r="J12" s="23">
+      <c r="J12" s="33">
         <v>79.855038928049396</v>
       </c>
-      <c r="K12" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="L12" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="M12" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="N12" s="22">
-        <v>0</v>
-      </c>
-      <c r="O12" s="23">
+      <c r="K12" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="M12" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="N12" s="32">
+        <v>0</v>
+      </c>
+      <c r="O12" s="33">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="51"/>
-      <c r="B13" s="59" t="s">
+    <row r="13" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="49"/>
+      <c r="B13" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="26">
         <v>7.5363555180000006</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="34">
         <v>0.8757548637715421</v>
       </c>
-      <c r="E13" s="10">
-        <v>7.9614078524685647E-2</v>
-      </c>
-      <c r="F13" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" s="18">
+      <c r="E13" s="35">
+        <v>0.6</v>
+      </c>
+      <c r="F13" s="36">
+        <v>0</v>
+      </c>
+      <c r="G13" s="34">
         <v>0.53076052349790426</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="37">
         <v>0.39807039262342825</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="37">
         <v>253.70353023199826</v>
       </c>
-      <c r="J13" s="24">
+      <c r="J13" s="38">
         <v>20.699660416418268</v>
       </c>
-      <c r="K13" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="L13" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="N13" s="11">
+      <c r="K13" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="M13" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="N13" s="37">
         <v>0.33172532718619019</v>
       </c>
-      <c r="O13" s="24">
+      <c r="O13" s="38">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="51"/>
-      <c r="B14" s="59" t="s">
+    <row r="14" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="49"/>
+      <c r="B14" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="26">
         <v>2.1255060000000001</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="34">
         <v>6.2714478340686881</v>
       </c>
-      <c r="E14" s="10">
-        <v>1.2542895668137375</v>
-      </c>
-      <c r="F14" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="G14" s="18">
+      <c r="E14" s="35">
+        <v>2.6659999999999999</v>
+      </c>
+      <c r="F14" s="36">
         <v>0.47047620660680323</v>
       </c>
-      <c r="H14" s="11">
+      <c r="G14" s="34">
+        <v>0.47047620660680323</v>
+      </c>
+      <c r="H14" s="37">
         <v>0.94095241321360645</v>
       </c>
-      <c r="I14" s="11">
-        <v>0</v>
-      </c>
-      <c r="J14" s="24">
-        <v>0</v>
-      </c>
-      <c r="K14" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="L14" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M14" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="N14" s="11">
+      <c r="I14" s="37">
+        <v>0</v>
+      </c>
+      <c r="J14" s="38">
+        <v>0</v>
+      </c>
+      <c r="K14" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="M14" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="N14" s="37">
         <v>1.1761905165170081</v>
       </c>
-      <c r="O14" s="24">
+      <c r="O14" s="38">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="51"/>
-      <c r="B15" s="59" t="s">
+    <row r="15" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="49"/>
+      <c r="B15" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="26">
         <v>1.4569589599999999</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="34">
         <v>8.5795141408787519</v>
       </c>
-      <c r="E15" s="10">
-        <v>2.144878535219688</v>
-      </c>
-      <c r="F15" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="G15" s="18">
+      <c r="E15" s="35">
+        <v>3.125</v>
+      </c>
+      <c r="F15" s="36">
+        <v>0</v>
+      </c>
+      <c r="G15" s="34">
         <v>1.3727222625406004</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="37">
         <v>5.4908890501624015</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="37">
         <v>89.226947065139029</v>
       </c>
-      <c r="J15" s="24">
+      <c r="J15" s="38">
         <v>10.295416969054504</v>
       </c>
-      <c r="K15" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="L15" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M15" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="N15" s="11">
-        <v>0</v>
-      </c>
-      <c r="O15" s="24">
+      <c r="K15" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="M15" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="N15" s="37">
+        <v>0</v>
+      </c>
+      <c r="O15" s="38">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="52"/>
-      <c r="B16" s="60" t="s">
+    <row r="16" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="50"/>
+      <c r="B16" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="62">
+      <c r="C16" s="27">
         <v>5.7995670199999996</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="39">
         <v>0.51727999515384515</v>
       </c>
-      <c r="E16" s="20">
-        <v>5.1727999515384517E-2</v>
-      </c>
-      <c r="F16" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" s="19">
+      <c r="E16" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="F16" s="41">
+        <v>0</v>
+      </c>
+      <c r="G16" s="39">
         <v>0.86213332525640862</v>
       </c>
-      <c r="H16" s="25">
+      <c r="H16" s="42">
         <v>0.51727999515384515</v>
       </c>
-      <c r="I16" s="25">
+      <c r="I16" s="42">
         <v>173.63365170664068</v>
       </c>
-      <c r="J16" s="26">
+      <c r="J16" s="43">
         <v>13.966559869153819</v>
       </c>
-      <c r="K16" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="L16" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M16" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="N16" s="25">
-        <v>0</v>
-      </c>
-      <c r="O16" s="26">
+      <c r="K16" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="M16" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="N16" s="42">
+        <v>0</v>
+      </c>
+      <c r="O16" s="43">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:15" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="34"/>
-      <c r="B17" s="27" t="s">
+    <row r="17" spans="1:15" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="46"/>
+      <c r="B17" s="10" t="s">
         <v>35</v>
       </c>
       <c r="C17" s="28">
         <v>86.97332109200002</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="44">
         <v>3.1273958104035091</v>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="44">
         <v>2.2995557429437565E-2</v>
       </c>
-      <c r="F17" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" s="29">
+      <c r="F17" s="44">
+        <v>7.5187969924812026E-3</v>
+      </c>
+      <c r="G17" s="44">
         <v>1.7246668072078175</v>
       </c>
-      <c r="H17" s="29">
+      <c r="H17" s="44">
         <v>0.689866722883127</v>
       </c>
-      <c r="I17" s="29">
+      <c r="I17" s="44">
         <v>137.97334457662541</v>
       </c>
-      <c r="J17" s="29">
+      <c r="J17" s="44">
         <v>1.7246668072078175</v>
       </c>
-      <c r="K17" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="L17" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="M17" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="N17" s="29">
+      <c r="K17" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="M17" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="N17" s="44">
         <v>0.22995557429437566</v>
       </c>
-      <c r="O17" s="30">
+      <c r="O17" s="45">
         <v>0.3449333614415635</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A18" s="35"/>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" s="47"/>
     </row>
-    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
     </row>
-    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
     </row>
-    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
     </row>
-    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A17:A18"/>

--- a/data/Heat map 3.xlsx
+++ b/data/Heat map 3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="8_{2B4ECC56-BA7D-46F8-B270-6AB9D06BE5A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD1DBB7A-63BE-4C7E-949A-324EC5EAF093}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA8F969-9AD8-44C6-AE5E-5331BD6B91A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{45B3C54E-DB58-4340-A914-7AEE103F004F}"/>
   </bookViews>
@@ -57,9 +57,6 @@
     <t>Varieties released</t>
   </si>
   <si>
-    <t>Annual rate of genetic gain, by crop (%)</t>
-  </si>
-  <si>
     <t>Breeding</t>
   </si>
   <si>
@@ -148,6 +145,9 @@
   </si>
   <si>
     <t xml:space="preserve">per Program Target </t>
+  </si>
+  <si>
+    <t>Average (across crops) percentage yield-related genetic gain</t>
   </si>
 </sst>
 </file>
@@ -1244,7 +1244,9 @@
     <col min="1" max="1" width="8" style="9" customWidth="1"/>
     <col min="2" max="2" width="37.109375" style="3" customWidth="1"/>
     <col min="3" max="3" width="5.77734375" style="3" customWidth="1"/>
-    <col min="4" max="15" width="6.33203125" style="3" customWidth="1"/>
+    <col min="4" max="11" width="6.33203125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="7.44140625" style="3" customWidth="1"/>
+    <col min="13" max="15" width="6.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1269,7 +1271,7 @@
     <row r="2" spans="1:15" s="13" customFormat="1" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="61"/>
       <c r="B2" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="55" t="s">
@@ -1295,51 +1297,51 @@
       <c r="A3" s="62"/>
       <c r="B3" s="2"/>
       <c r="C3" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="F3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="G3" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="H3" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="I3" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="J3" s="17" t="s">
         <v>17</v>
-      </c>
-      <c r="J3" s="17" t="s">
-        <v>18</v>
       </c>
       <c r="K3" s="15" t="s">
         <v>4</v>
       </c>
       <c r="L3" s="18" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="M3" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="N3" s="16" t="s">
+      <c r="O3" s="17" t="s">
         <v>20</v>
-      </c>
-      <c r="O3" s="17" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4" s="22">
         <v>3.4135987800000001</v>
@@ -1366,13 +1368,13 @@
         <v>53.902058167480362</v>
       </c>
       <c r="K4" s="29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L4" s="32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M4" s="32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N4" s="32">
         <v>0.2929459683015237</v>
@@ -1384,7 +1386,7 @@
     <row r="5" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
       <c r="B5" s="20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="23">
         <v>12.720419820000002</v>
@@ -1414,10 +1416,10 @@
         <v>3.62</v>
       </c>
       <c r="L5" s="37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M5" s="37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N5" s="37">
         <v>0.62891006061150567</v>
@@ -1429,7 +1431,7 @@
     <row r="6" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="49"/>
       <c r="B6" s="20" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="23">
         <v>3.5036499999999999</v>
@@ -1456,13 +1458,13 @@
         <v>32.252079973741665</v>
       </c>
       <c r="K6" s="34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L6" s="37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M6" s="37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N6" s="37">
         <v>0</v>
@@ -1474,7 +1476,7 @@
     <row r="7" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="50"/>
       <c r="B7" s="21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="24">
         <v>21.304912170000001</v>
@@ -1501,13 +1503,13 @@
         <v>14.50369743533188</v>
       </c>
       <c r="K7" s="39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L7" s="42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M7" s="42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N7" s="42">
         <v>0.79793804660401935</v>
@@ -1518,10 +1520,10 @@
     </row>
     <row r="8" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="48" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="22">
         <v>7.721148311538462</v>
@@ -1548,13 +1550,13 @@
         <v>1.2951441413262363</v>
       </c>
       <c r="K8" s="29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L8" s="32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M8" s="32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N8" s="32">
         <v>0.77708648479574172</v>
@@ -1566,7 +1568,7 @@
     <row r="9" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="49"/>
       <c r="B9" s="20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" s="23">
         <v>12.273168915897436</v>
@@ -1593,13 +1595,13 @@
         <v>18.984502013835652</v>
       </c>
       <c r="K9" s="34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L9" s="37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M9" s="37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N9" s="37">
         <v>8.147854941560366E-2</v>
@@ -1611,7 +1613,7 @@
     <row r="10" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="49"/>
       <c r="B10" s="20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="23">
         <v>7.1819852465641034</v>
@@ -1638,13 +1640,13 @@
         <v>2.7847453473352788</v>
       </c>
       <c r="K10" s="34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L10" s="37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M10" s="37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N10" s="37">
         <v>1.3923726736676394</v>
@@ -1656,7 +1658,7 @@
     <row r="11" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="50"/>
       <c r="B11" s="21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" s="24">
         <v>0.57107699999999995</v>
@@ -1683,13 +1685,13 @@
         <v>0</v>
       </c>
       <c r="K11" s="39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L11" s="42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M11" s="42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N11" s="42">
         <v>5.2532320510193893</v>
@@ -1700,10 +1702,10 @@
     </row>
     <row r="12" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="48" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" s="25">
         <v>1.3649733500000001</v>
@@ -1730,13 +1732,13 @@
         <v>79.855038928049396</v>
       </c>
       <c r="K12" s="29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L12" s="32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M12" s="32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N12" s="32">
         <v>0</v>
@@ -1748,7 +1750,7 @@
     <row r="13" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="49"/>
       <c r="B13" s="20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" s="26">
         <v>7.5363555180000006</v>
@@ -1775,13 +1777,13 @@
         <v>20.699660416418268</v>
       </c>
       <c r="K13" s="34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L13" s="37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M13" s="37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N13" s="37">
         <v>0.33172532718619019</v>
@@ -1793,7 +1795,7 @@
     <row r="14" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="49"/>
       <c r="B14" s="20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14" s="26">
         <v>2.1255060000000001</v>
@@ -1820,13 +1822,13 @@
         <v>0</v>
       </c>
       <c r="K14" s="34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L14" s="37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M14" s="37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N14" s="37">
         <v>1.1761905165170081</v>
@@ -1838,7 +1840,7 @@
     <row r="15" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="49"/>
       <c r="B15" s="20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="26">
         <v>1.4569589599999999</v>
@@ -1865,13 +1867,13 @@
         <v>10.295416969054504</v>
       </c>
       <c r="K15" s="34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L15" s="37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M15" s="37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N15" s="37">
         <v>0</v>
@@ -1883,7 +1885,7 @@
     <row r="16" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="50"/>
       <c r="B16" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C16" s="27">
         <v>5.7995670199999996</v>
@@ -1910,13 +1912,13 @@
         <v>13.966559869153819</v>
       </c>
       <c r="K16" s="39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L16" s="42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M16" s="42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N16" s="42">
         <v>0</v>
@@ -1928,7 +1930,7 @@
     <row r="17" spans="1:15" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="46"/>
       <c r="B17" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C17" s="28">
         <v>86.97332109200002</v>
@@ -1955,13 +1957,13 @@
         <v>1.7246668072078175</v>
       </c>
       <c r="K17" s="44" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L17" s="44" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M17" s="44" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N17" s="44">
         <v>0.22995557429437566</v>

--- a/data/Heat map 3.xlsx
+++ b/data/Heat map 3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/s_lewis_cgiar_org/Documents/TAAT/R4D/KPIS/Alekeh/for uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA8F969-9AD8-44C6-AE5E-5331BD6B91A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="8_{2B4ECC56-BA7D-46F8-B270-6AB9D06BE5A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B256D2E6-073B-457B-8A14-A0F0BFAA905C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{45B3C54E-DB58-4340-A914-7AEE103F004F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{45B3C54E-DB58-4340-A914-7AEE103F004F}"/>
   </bookViews>
   <sheets>
     <sheet name="Res, Cap, Product" sheetId="1" r:id="rId1"/>
@@ -57,6 +57,9 @@
     <t>Varieties released</t>
   </si>
   <si>
+    <t>Annual rate of genetic gain, by crop (%)</t>
+  </si>
+  <si>
     <t>Breeding</t>
   </si>
   <si>
@@ -145,9 +148,6 @@
   </si>
   <si>
     <t xml:space="preserve">per Program Target </t>
-  </si>
-  <si>
-    <t>Average (across crops) percentage yield-related genetic gain</t>
   </si>
 </sst>
 </file>
@@ -155,9 +155,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -719,16 +719,16 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" readingOrder="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -740,7 +740,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -777,6 +777,108 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -796,108 +898,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1239,755 +1239,753 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" style="9" customWidth="1"/>
-    <col min="2" max="2" width="37.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="5.77734375" style="3" customWidth="1"/>
-    <col min="4" max="11" width="6.33203125" style="3" customWidth="1"/>
-    <col min="12" max="12" width="7.44140625" style="3" customWidth="1"/>
-    <col min="13" max="15" width="6.33203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="37.08984375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="5.81640625" style="3" customWidth="1"/>
+    <col min="4" max="15" width="6.36328125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
-      <c r="B1" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="52"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="54"/>
+      <c r="B1" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="45"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="47"/>
     </row>
-    <row r="2" spans="1:15" s="13" customFormat="1" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="61"/>
+    <row r="2" spans="1:15" s="13" customFormat="1" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="54"/>
       <c r="B2" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="12"/>
-      <c r="D2" s="55" t="s">
+      <c r="D2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="56"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="58" t="s">
+      <c r="E2" s="49"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="58" t="s">
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="60"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="53"/>
     </row>
-    <row r="3" spans="1:15" s="4" customFormat="1" ht="103.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="62"/>
+    <row r="3" spans="1:15" s="4" customFormat="1" ht="104" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="55"/>
       <c r="B3" s="2"/>
       <c r="C3" s="14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K3" s="15" t="s">
         <v>4</v>
       </c>
       <c r="L3" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="M3" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3" s="17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="56">
+        <v>3.4135987800000001</v>
+      </c>
+      <c r="D4" s="22">
+        <v>6.4448113026335205</v>
+      </c>
+      <c r="E4" s="23">
+        <v>3.1357142857142857</v>
+      </c>
+      <c r="F4" s="24">
+        <v>0.2929459683015237</v>
+      </c>
+      <c r="G4" s="22">
+        <v>0.2929459683015237</v>
+      </c>
+      <c r="H4" s="25">
+        <v>0.2929459683015237</v>
+      </c>
+      <c r="I4" s="25">
+        <v>19.920325844503608</v>
+      </c>
+      <c r="J4" s="26">
+        <v>53.902058167480362</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" s="25">
+        <v>0.2929459683015237</v>
+      </c>
+      <c r="O4" s="26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="42"/>
+      <c r="B5" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="57">
+        <v>12.720419820000002</v>
+      </c>
+      <c r="D5" s="27">
+        <v>4.0486085151865678</v>
+      </c>
+      <c r="E5" s="28">
+        <v>2.2369565217391307</v>
+      </c>
+      <c r="F5" s="29">
+        <v>0</v>
+      </c>
+      <c r="G5" s="27">
+        <v>1.8867301818345172</v>
+      </c>
+      <c r="H5" s="30">
+        <v>2.20118521214027</v>
+      </c>
+      <c r="I5" s="30">
+        <v>8.4902858182553285</v>
+      </c>
+      <c r="J5" s="31">
+        <v>16.823344121357778</v>
+      </c>
+      <c r="K5" s="27">
+        <v>3.62</v>
+      </c>
+      <c r="L5" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="N5" s="30">
+        <v>0.62891006061150567</v>
+      </c>
+      <c r="O5" s="31">
+        <v>0.39306878788219107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="42"/>
+      <c r="B6" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="57">
+        <v>3.5036499999999999</v>
+      </c>
+      <c r="D6" s="27">
+        <v>1.427083184678835</v>
+      </c>
+      <c r="E6" s="28">
+        <v>1.25</v>
+      </c>
+      <c r="F6" s="29">
+        <v>0</v>
+      </c>
+      <c r="G6" s="27">
+        <v>7.4208325603299423</v>
+      </c>
+      <c r="H6" s="30">
+        <v>5.4229161017795731</v>
+      </c>
+      <c r="I6" s="30">
+        <v>1.427083184678835</v>
+      </c>
+      <c r="J6" s="31">
+        <v>32.252079973741665</v>
+      </c>
+      <c r="K6" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="N6" s="30">
+        <v>0</v>
+      </c>
+      <c r="O6" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="43"/>
+      <c r="B7" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="58">
+        <v>21.304912170000001</v>
+      </c>
+      <c r="D7" s="32">
+        <v>0.72283799515893521</v>
+      </c>
+      <c r="E7" s="33">
+        <v>1.0266666666666666</v>
+      </c>
+      <c r="F7" s="34">
+        <v>0</v>
+      </c>
+      <c r="G7" s="32">
+        <v>0.23468766076588804</v>
+      </c>
+      <c r="H7" s="35">
+        <v>0.32856272507224321</v>
+      </c>
+      <c r="I7" s="35">
+        <v>105.46863474819008</v>
+      </c>
+      <c r="J7" s="36">
+        <v>14.50369743533188</v>
+      </c>
+      <c r="K7" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="M7" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="N7" s="35">
+        <v>0.79793804660401935</v>
+      </c>
+      <c r="O7" s="36">
+        <v>9.3875064306355213E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="56">
+        <v>7.721148311538462</v>
+      </c>
+      <c r="D8" s="22">
+        <v>5.3683724657972496</v>
+      </c>
+      <c r="E8" s="23">
+        <v>3.4541666666666671</v>
+      </c>
+      <c r="F8" s="24">
+        <v>0.12951441413262363</v>
+      </c>
+      <c r="G8" s="22">
+        <v>1.1656297271936127</v>
+      </c>
+      <c r="H8" s="25">
+        <v>1.1656297271936127</v>
+      </c>
+      <c r="I8" s="25">
+        <v>13.210470241527611</v>
+      </c>
+      <c r="J8" s="26">
+        <v>1.2951441413262363</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="M8" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="N8" s="25">
+        <v>0.77708648479574172</v>
+      </c>
+      <c r="O8" s="26">
+        <v>0.25902882826524726</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="42"/>
+      <c r="B9" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="57">
+        <v>12.273168915897436</v>
+      </c>
+      <c r="D9" s="27">
+        <v>1.7004573263036482</v>
+      </c>
+      <c r="E9" s="28">
+        <v>1.0435000000000001</v>
+      </c>
+      <c r="F9" s="29">
+        <v>6.7627196014951027E-2</v>
+      </c>
+      <c r="G9" s="27">
+        <v>1.7925280871432805</v>
+      </c>
+      <c r="H9" s="30">
+        <v>1.1406996918184511</v>
+      </c>
+      <c r="I9" s="30">
+        <v>259.50917988869764</v>
+      </c>
+      <c r="J9" s="31">
+        <v>18.984502013835652</v>
+      </c>
+      <c r="K9" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="N9" s="30">
+        <v>8.147854941560366E-2</v>
+      </c>
+      <c r="O9" s="31">
+        <v>0.7333069447404329</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="42"/>
+      <c r="B10" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="57">
+        <v>7.1819852465641034</v>
+      </c>
+      <c r="D10" s="27">
+        <v>2.1581776441848408</v>
+      </c>
+      <c r="E10" s="28">
+        <v>2.2142857142857144</v>
+      </c>
+      <c r="F10" s="29">
+        <v>0.27847453473352785</v>
+      </c>
+      <c r="G10" s="27">
+        <v>0.97466087156734749</v>
+      </c>
+      <c r="H10" s="30">
+        <v>0.4177118021002918</v>
+      </c>
+      <c r="I10" s="30">
+        <v>522.69670169483186</v>
+      </c>
+      <c r="J10" s="31">
+        <v>2.7847453473352788</v>
+      </c>
+      <c r="K10" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="M10" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="N10" s="30">
+        <v>1.3923726736676394</v>
+      </c>
+      <c r="O10" s="31">
+        <v>0.27847453473352785</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="43"/>
+      <c r="B11" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="58">
+        <v>0.57107699999999995</v>
+      </c>
+      <c r="D11" s="32">
+        <v>0</v>
+      </c>
+      <c r="E11" s="33">
+        <v>0</v>
+      </c>
+      <c r="F11" s="34">
+        <v>0</v>
+      </c>
+      <c r="G11" s="32">
+        <v>3.5021547006795934</v>
+      </c>
+      <c r="H11" s="35">
+        <v>1.7510773503397967</v>
+      </c>
+      <c r="I11" s="35">
+        <v>0</v>
+      </c>
+      <c r="J11" s="36">
+        <v>0</v>
+      </c>
+      <c r="K11" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="M11" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="N11" s="35">
+        <v>5.2532320510193893</v>
+      </c>
+      <c r="O11" s="36">
+        <v>5.2532320510193893</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="59">
+        <v>1.3649733500000001</v>
+      </c>
+      <c r="D12" s="22">
+        <v>7.267541157488532</v>
+      </c>
+      <c r="E12" s="23">
+        <v>0.90181818181818185</v>
+      </c>
+      <c r="F12" s="24">
+        <v>0</v>
+      </c>
+      <c r="G12" s="22">
+        <v>3.6630751801857522</v>
+      </c>
+      <c r="H12" s="25">
+        <v>3.6630751801857522</v>
+      </c>
+      <c r="I12" s="25">
+        <v>68.865813387492139</v>
+      </c>
+      <c r="J12" s="26">
+        <v>79.855038928049396</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="M12" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="N12" s="25">
+        <v>0</v>
+      </c>
+      <c r="O12" s="26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="42"/>
+      <c r="B13" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="60">
+        <v>7.5363555180000006</v>
+      </c>
+      <c r="D13" s="27">
+        <v>0.8757548637715421</v>
+      </c>
+      <c r="E13" s="28">
+        <v>0.6</v>
+      </c>
+      <c r="F13" s="29">
+        <v>0</v>
+      </c>
+      <c r="G13" s="27">
+        <v>0.53076052349790426</v>
+      </c>
+      <c r="H13" s="30">
+        <v>0.39807039262342825</v>
+      </c>
+      <c r="I13" s="30">
+        <v>253.70353023199826</v>
+      </c>
+      <c r="J13" s="31">
+        <v>20.699660416418268</v>
+      </c>
+      <c r="K13" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="M13" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="N13" s="30">
+        <v>0.33172532718619019</v>
+      </c>
+      <c r="O13" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="42"/>
+      <c r="B14" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="60">
+        <v>2.1255060000000001</v>
+      </c>
+      <c r="D14" s="27">
+        <v>6.2714478340686881</v>
+      </c>
+      <c r="E14" s="28">
+        <v>2.6659999999999999</v>
+      </c>
+      <c r="F14" s="29">
+        <v>0.47047620660680323</v>
+      </c>
+      <c r="G14" s="27">
+        <v>0.47047620660680323</v>
+      </c>
+      <c r="H14" s="30">
+        <v>0.94095241321360645</v>
+      </c>
+      <c r="I14" s="30">
+        <v>0</v>
+      </c>
+      <c r="J14" s="31">
+        <v>0</v>
+      </c>
+      <c r="K14" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="M14" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="N14" s="30">
+        <v>1.1761905165170081</v>
+      </c>
+      <c r="O14" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="42"/>
+      <c r="B15" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="60">
+        <v>1.4569589599999999</v>
+      </c>
+      <c r="D15" s="27">
+        <v>8.5795141408787519</v>
+      </c>
+      <c r="E15" s="28">
+        <v>3.125</v>
+      </c>
+      <c r="F15" s="29">
+        <v>0</v>
+      </c>
+      <c r="G15" s="27">
+        <v>1.3727222625406004</v>
+      </c>
+      <c r="H15" s="30">
+        <v>5.4908890501624015</v>
+      </c>
+      <c r="I15" s="30">
+        <v>89.226947065139029</v>
+      </c>
+      <c r="J15" s="31">
+        <v>10.295416969054504</v>
+      </c>
+      <c r="K15" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="M15" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="N15" s="30">
+        <v>0</v>
+      </c>
+      <c r="O15" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="43"/>
+      <c r="B16" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="61">
+        <v>5.7995670199999996</v>
+      </c>
+      <c r="D16" s="32">
+        <v>0.51727999515384515</v>
+      </c>
+      <c r="E16" s="33">
+        <v>0.3</v>
+      </c>
+      <c r="F16" s="34">
+        <v>0</v>
+      </c>
+      <c r="G16" s="32">
+        <v>0.86213332525640862</v>
+      </c>
+      <c r="H16" s="35">
+        <v>0.51727999515384515</v>
+      </c>
+      <c r="I16" s="35">
+        <v>173.63365170664068</v>
+      </c>
+      <c r="J16" s="36">
+        <v>13.966559869153819</v>
+      </c>
+      <c r="K16" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="M16" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="N16" s="35">
+        <v>0</v>
+      </c>
+      <c r="O16" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="39"/>
+      <c r="B17" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="M3" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="N3" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="O3" s="17" t="s">
-        <v>20</v>
+      <c r="C17" s="62">
+        <v>86.97332109200002</v>
+      </c>
+      <c r="D17" s="37">
+        <v>3.1273958104035091</v>
+      </c>
+      <c r="E17" s="37">
+        <v>2.2995557429437565E-2</v>
+      </c>
+      <c r="F17" s="37">
+        <v>7.5187969924812026E-3</v>
+      </c>
+      <c r="G17" s="37">
+        <v>1.7246668072078175</v>
+      </c>
+      <c r="H17" s="37">
+        <v>0.689866722883127</v>
+      </c>
+      <c r="I17" s="37">
+        <v>137.97334457662541</v>
+      </c>
+      <c r="J17" s="37">
+        <v>1.7246668072078175</v>
+      </c>
+      <c r="K17" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="M17" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="N17" s="37">
+        <v>0.22995557429437566</v>
+      </c>
+      <c r="O17" s="38">
+        <v>0.3449333614415635</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="22">
-        <v>3.4135987800000001</v>
-      </c>
-      <c r="D4" s="29">
-        <v>6.4448113026335205</v>
-      </c>
-      <c r="E4" s="30">
-        <v>3.1357142857142857</v>
-      </c>
-      <c r="F4" s="31">
-        <v>0.2929459683015237</v>
-      </c>
-      <c r="G4" s="29">
-        <v>0.2929459683015237</v>
-      </c>
-      <c r="H4" s="32">
-        <v>0.2929459683015237</v>
-      </c>
-      <c r="I4" s="32">
-        <v>19.920325844503608</v>
-      </c>
-      <c r="J4" s="33">
-        <v>53.902058167480362</v>
-      </c>
-      <c r="K4" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="M4" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="N4" s="32">
-        <v>0.2929459683015237</v>
-      </c>
-      <c r="O4" s="33">
-        <v>0</v>
-      </c>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A18" s="40"/>
     </row>
-    <row r="5" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="49"/>
-      <c r="B5" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="23">
-        <v>12.720419820000002</v>
-      </c>
-      <c r="D5" s="34">
-        <v>4.0486085151865678</v>
-      </c>
-      <c r="E5" s="35">
-        <v>2.2369565217391307</v>
-      </c>
-      <c r="F5" s="36">
-        <v>0</v>
-      </c>
-      <c r="G5" s="34">
-        <v>1.8867301818345172</v>
-      </c>
-      <c r="H5" s="37">
-        <v>2.20118521214027</v>
-      </c>
-      <c r="I5" s="37">
-        <v>8.4902858182553285</v>
-      </c>
-      <c r="J5" s="38">
-        <v>16.823344121357778</v>
-      </c>
-      <c r="K5" s="34">
-        <v>3.62</v>
-      </c>
-      <c r="L5" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="M5" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="N5" s="37">
-        <v>0.62891006061150567</v>
-      </c>
-      <c r="O5" s="38">
-        <v>0.39306878788219107</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="49"/>
-      <c r="B6" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="23">
-        <v>3.5036499999999999</v>
-      </c>
-      <c r="D6" s="34">
-        <v>1.427083184678835</v>
-      </c>
-      <c r="E6" s="35">
-        <v>1.25</v>
-      </c>
-      <c r="F6" s="36">
-        <v>0</v>
-      </c>
-      <c r="G6" s="34">
-        <v>7.4208325603299423</v>
-      </c>
-      <c r="H6" s="37">
-        <v>5.4229161017795731</v>
-      </c>
-      <c r="I6" s="37">
-        <v>1.427083184678835</v>
-      </c>
-      <c r="J6" s="38">
-        <v>32.252079973741665</v>
-      </c>
-      <c r="K6" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="L6" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="M6" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="N6" s="37">
-        <v>0</v>
-      </c>
-      <c r="O6" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="50"/>
-      <c r="B7" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="24">
-        <v>21.304912170000001</v>
-      </c>
-      <c r="D7" s="39">
-        <v>0.72283799515893521</v>
-      </c>
-      <c r="E7" s="40">
-        <v>1.0266666666666666</v>
-      </c>
-      <c r="F7" s="41">
-        <v>0</v>
-      </c>
-      <c r="G7" s="39">
-        <v>0.23468766076588804</v>
-      </c>
-      <c r="H7" s="42">
-        <v>0.32856272507224321</v>
-      </c>
-      <c r="I7" s="42">
-        <v>105.46863474819008</v>
-      </c>
-      <c r="J7" s="43">
-        <v>14.50369743533188</v>
-      </c>
-      <c r="K7" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="L7" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="M7" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="N7" s="42">
-        <v>0.79793804660401935</v>
-      </c>
-      <c r="O7" s="43">
-        <v>9.3875064306355213E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="48" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="22">
-        <v>7.721148311538462</v>
-      </c>
-      <c r="D8" s="29">
-        <v>5.3683724657972496</v>
-      </c>
-      <c r="E8" s="30">
-        <v>3.4541666666666671</v>
-      </c>
-      <c r="F8" s="31">
-        <v>0.12951441413262363</v>
-      </c>
-      <c r="G8" s="29">
-        <v>1.1656297271936127</v>
-      </c>
-      <c r="H8" s="32">
-        <v>1.1656297271936127</v>
-      </c>
-      <c r="I8" s="32">
-        <v>13.210470241527611</v>
-      </c>
-      <c r="J8" s="33">
-        <v>1.2951441413262363</v>
-      </c>
-      <c r="K8" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="L8" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="M8" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="N8" s="32">
-        <v>0.77708648479574172</v>
-      </c>
-      <c r="O8" s="33">
-        <v>0.25902882826524726</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="49"/>
-      <c r="B9" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="23">
-        <v>12.273168915897436</v>
-      </c>
-      <c r="D9" s="34">
-        <v>1.7004573263036482</v>
-      </c>
-      <c r="E9" s="35">
-        <v>1.0435000000000001</v>
-      </c>
-      <c r="F9" s="36">
-        <v>6.7627196014951027E-2</v>
-      </c>
-      <c r="G9" s="34">
-        <v>1.7925280871432805</v>
-      </c>
-      <c r="H9" s="37">
-        <v>1.1406996918184511</v>
-      </c>
-      <c r="I9" s="37">
-        <v>259.50917988869764</v>
-      </c>
-      <c r="J9" s="38">
-        <v>18.984502013835652</v>
-      </c>
-      <c r="K9" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="L9" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="M9" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="N9" s="37">
-        <v>8.147854941560366E-2</v>
-      </c>
-      <c r="O9" s="38">
-        <v>0.7333069447404329</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="49"/>
-      <c r="B10" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="23">
-        <v>7.1819852465641034</v>
-      </c>
-      <c r="D10" s="34">
-        <v>2.1581776441848408</v>
-      </c>
-      <c r="E10" s="35">
-        <v>2.2142857142857144</v>
-      </c>
-      <c r="F10" s="36">
-        <v>0.27847453473352785</v>
-      </c>
-      <c r="G10" s="34">
-        <v>0.97466087156734749</v>
-      </c>
-      <c r="H10" s="37">
-        <v>0.4177118021002918</v>
-      </c>
-      <c r="I10" s="37">
-        <v>522.69670169483186</v>
-      </c>
-      <c r="J10" s="38">
-        <v>2.7847453473352788</v>
-      </c>
-      <c r="K10" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="L10" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="M10" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="N10" s="37">
-        <v>1.3923726736676394</v>
-      </c>
-      <c r="O10" s="38">
-        <v>0.27847453473352785</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="50"/>
-      <c r="B11" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="24">
-        <v>0.57107699999999995</v>
-      </c>
-      <c r="D11" s="39">
-        <v>0</v>
-      </c>
-      <c r="E11" s="40">
-        <v>0</v>
-      </c>
-      <c r="F11" s="41">
-        <v>0</v>
-      </c>
-      <c r="G11" s="39">
-        <v>3.5021547006795934</v>
-      </c>
-      <c r="H11" s="42">
-        <v>1.7510773503397967</v>
-      </c>
-      <c r="I11" s="42">
-        <v>0</v>
-      </c>
-      <c r="J11" s="43">
-        <v>0</v>
-      </c>
-      <c r="K11" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="L11" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="M11" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="N11" s="42">
-        <v>5.2532320510193893</v>
-      </c>
-      <c r="O11" s="43">
-        <v>5.2532320510193893</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="48" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="25">
-        <v>1.3649733500000001</v>
-      </c>
-      <c r="D12" s="29">
-        <v>7.267541157488532</v>
-      </c>
-      <c r="E12" s="30">
-        <v>0.90181818181818185</v>
-      </c>
-      <c r="F12" s="31">
-        <v>0</v>
-      </c>
-      <c r="G12" s="29">
-        <v>3.6630751801857522</v>
-      </c>
-      <c r="H12" s="32">
-        <v>3.6630751801857522</v>
-      </c>
-      <c r="I12" s="32">
-        <v>68.865813387492139</v>
-      </c>
-      <c r="J12" s="33">
-        <v>79.855038928049396</v>
-      </c>
-      <c r="K12" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="L12" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="M12" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="N12" s="32">
-        <v>0</v>
-      </c>
-      <c r="O12" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49"/>
-      <c r="B13" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="26">
-        <v>7.5363555180000006</v>
-      </c>
-      <c r="D13" s="34">
-        <v>0.8757548637715421</v>
-      </c>
-      <c r="E13" s="35">
-        <v>0.6</v>
-      </c>
-      <c r="F13" s="36">
-        <v>0</v>
-      </c>
-      <c r="G13" s="34">
-        <v>0.53076052349790426</v>
-      </c>
-      <c r="H13" s="37">
-        <v>0.39807039262342825</v>
-      </c>
-      <c r="I13" s="37">
-        <v>253.70353023199826</v>
-      </c>
-      <c r="J13" s="38">
-        <v>20.699660416418268</v>
-      </c>
-      <c r="K13" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="L13" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="M13" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="N13" s="37">
-        <v>0.33172532718619019</v>
-      </c>
-      <c r="O13" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="49"/>
-      <c r="B14" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="26">
-        <v>2.1255060000000001</v>
-      </c>
-      <c r="D14" s="34">
-        <v>6.2714478340686881</v>
-      </c>
-      <c r="E14" s="35">
-        <v>2.6659999999999999</v>
-      </c>
-      <c r="F14" s="36">
-        <v>0.47047620660680323</v>
-      </c>
-      <c r="G14" s="34">
-        <v>0.47047620660680323</v>
-      </c>
-      <c r="H14" s="37">
-        <v>0.94095241321360645</v>
-      </c>
-      <c r="I14" s="37">
-        <v>0</v>
-      </c>
-      <c r="J14" s="38">
-        <v>0</v>
-      </c>
-      <c r="K14" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="L14" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="M14" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="N14" s="37">
-        <v>1.1761905165170081</v>
-      </c>
-      <c r="O14" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="49"/>
-      <c r="B15" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="26">
-        <v>1.4569589599999999</v>
-      </c>
-      <c r="D15" s="34">
-        <v>8.5795141408787519</v>
-      </c>
-      <c r="E15" s="35">
-        <v>3.125</v>
-      </c>
-      <c r="F15" s="36">
-        <v>0</v>
-      </c>
-      <c r="G15" s="34">
-        <v>1.3727222625406004</v>
-      </c>
-      <c r="H15" s="37">
-        <v>5.4908890501624015</v>
-      </c>
-      <c r="I15" s="37">
-        <v>89.226947065139029</v>
-      </c>
-      <c r="J15" s="38">
-        <v>10.295416969054504</v>
-      </c>
-      <c r="K15" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="L15" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="M15" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="N15" s="37">
-        <v>0</v>
-      </c>
-      <c r="O15" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="50"/>
-      <c r="B16" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="27">
-        <v>5.7995670199999996</v>
-      </c>
-      <c r="D16" s="39">
-        <v>0.51727999515384515</v>
-      </c>
-      <c r="E16" s="40">
-        <v>0.3</v>
-      </c>
-      <c r="F16" s="41">
-        <v>0</v>
-      </c>
-      <c r="G16" s="39">
-        <v>0.86213332525640862</v>
-      </c>
-      <c r="H16" s="42">
-        <v>0.51727999515384515</v>
-      </c>
-      <c r="I16" s="42">
-        <v>173.63365170664068</v>
-      </c>
-      <c r="J16" s="43">
-        <v>13.966559869153819</v>
-      </c>
-      <c r="K16" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="L16" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="M16" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="N16" s="42">
-        <v>0</v>
-      </c>
-      <c r="O16" s="43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="46"/>
-      <c r="B17" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="28">
-        <v>86.97332109200002</v>
-      </c>
-      <c r="D17" s="44">
-        <v>3.1273958104035091</v>
-      </c>
-      <c r="E17" s="44">
-        <v>2.2995557429437565E-2</v>
-      </c>
-      <c r="F17" s="44">
-        <v>7.5187969924812026E-3</v>
-      </c>
-      <c r="G17" s="44">
-        <v>1.7246668072078175</v>
-      </c>
-      <c r="H17" s="44">
-        <v>0.689866722883127</v>
-      </c>
-      <c r="I17" s="44">
-        <v>137.97334457662541</v>
-      </c>
-      <c r="J17" s="44">
-        <v>1.7246668072078175</v>
-      </c>
-      <c r="K17" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="L17" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="M17" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="N17" s="44">
-        <v>0.22995557429437566</v>
-      </c>
-      <c r="O17" s="45">
-        <v>0.3449333614415635</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="47"/>
-    </row>
-    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
     </row>
-    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
     </row>
-    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
     </row>
-    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A17:A18"/>
